--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -12294,7 +12294,7 @@
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>2026-10-03 02:17</t>
+          <t>2026-10-03 02:22</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>db9d588</t>
+          <t>cdc5392</t>
         </is>
       </c>
       <c r="D6" s="35" t="n">
@@ -12326,7 +12326,7 @@
         <v>260</v>
       </c>
       <c r="J6" s="35" t="n">
-        <v>14.5</v>
+        <v>17.8</v>
       </c>
       <c r="K6" s="36">
         <f>IFERROR(E6/(E6+F6+G6),0)</f>

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="실행이력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$6</f>
+              <f>'실행이력'!$A$4:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$6</f>
+              <f>'실행이력'!$E$4:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$6</f>
+              <f>'실행이력'!$A$4:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$6</f>
+              <f>'실행이력'!$F$4:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$6</f>
+              <f>'실행이력'!$A$4:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$6</f>
+              <f>'실행이력'!$G$4:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -2146,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2378,22 +2378,22 @@
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>IT-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 동일 아이디 2회 요청</t>
+          <t>브라우저 E2E: 대시보드 KPI·최근 신청·알림 표시</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>1차 201, 2차 409(DUPLICATE_USERNAME), users 1건</t>
+          <t>로그인 후 인사말, KPI 4종 수치, 최근 신청 행과 상태 배지, 알림 문구 표시</t>
         </is>
       </c>
       <c r="H8" s="28" t="inlineStr">
@@ -2425,37 +2425,37 @@
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>IT-02</t>
+          <t>ST-02-N1</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 정상 가입 응답</t>
+          <t>브라우저 E2E: 신규 사용자(데이터 없음) 빈 상태</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>201, 응답에 id/username/user_type, 비밀번호·해시 미포함, DB 에는 bcrypt 해시</t>
+          <t>KPI 모두 0, '아직 신청 내역이 없습니다' 안내 표시</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
@@ -2472,37 +2472,37 @@
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>IT-03</t>
+          <t>ST-02-N2</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 잘못된 입력</t>
+          <t>브라우저 E2E: 위변조 의심 검증서 강조</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR, users 0건</t>
+          <t>위변조 의심 KPI 가 1, 경고 알림과 검증서 번호(CV-)가 표시되고 경고 스타일 적용</t>
         </is>
       </c>
       <c r="H10" s="28" t="inlineStr">
@@ -2519,37 +2519,37 @@
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>IT-04</t>
+          <t>ST-02-N3</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 본문 없음/JSON 아님</t>
+          <t>브라우저 E2E: 대시보드에서 로그아웃</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>400 (500 이 아님)</t>
+          <t>로그아웃 후 로그인 화면 복귀, 뒤로가기/재접근 시 대시보드 접근 불가</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>IT-05</t>
+          <t>IT-01</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: 로그인 후 세션 유지</t>
+          <t>POST /api/auth/signup: 동일 아이디 2회 요청</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>200 → GET /api/auth/me 가 본인 정보 반환</t>
+          <t>1차 201, 2차 409(DUPLICATE_USERNAME), users 1건</t>
         </is>
       </c>
       <c r="H12" s="28" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>IT-06</t>
+          <t>IT-02</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: 세션 쿠키 보안 속성</t>
+          <t>POST /api/auth/signup: 정상 가입 응답</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>Set-Cookie 에 HttpOnly 와 SameSite 포함</t>
+          <t>201, 응답에 id/username/user_type, 비밀번호·해시 미포함, DB 에는 bcrypt 해시</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
@@ -2660,7 +2660,7 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>IT-07</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -2680,17 +2680,17 @@
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: 실패 시 401, 계정 존재 여부 비노출</t>
+          <t>POST /api/auth/signup: 잘못된 입력</t>
         </is>
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>없는 아이디/틀린 비밀번호의 응답 본문 동일, 이후에도 /me 는 401</t>
+          <t>400 VALIDATION_ERROR, users 0건</t>
         </is>
       </c>
       <c r="H14" s="28" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>IT-08</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: SQL 인젝션/빈 값</t>
+          <t>POST /api/auth/signup: 본문 없음/JSON 아님</t>
         </is>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>401 또는 400, 500 없음</t>
+          <t>400 (500 이 아님)</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>IT-09</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="F16" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/logout: 세션 종료</t>
+          <t>POST /api/auth/login: 로그인 후 세션 유지</t>
         </is>
       </c>
       <c r="G16" s="29" t="inlineStr">
         <is>
-          <t>204 이후 /me 401, 재로그아웃도 오류 없음</t>
+          <t>200 → GET /api/auth/me 가 본인 정보 반환</t>
         </is>
       </c>
       <c r="H16" s="28" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>IT-10</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>세션: 서로 다른 클라이언트 격리 / 위조 쿠키</t>
+          <t>POST /api/auth/login: 세션 쿠키 보안 속성</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>A 로그인이 B 에 영향 없음, 임의 쿠키는 401</t>
+          <t>Set-Cookie 에 HttpOnly 와 SameSite 포함</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>IT-11</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D18" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>보호 API: 미로그인 호출</t>
+          <t>POST /api/auth/login: 실패 시 401, 계정 존재 여부 비노출</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>401 반환, 어떤 레코드도 생성되지 않음</t>
+          <t>없는 아이디/틀린 비밀번호의 응답 본문 동일, 이후에도 /me 는 401</t>
         </is>
       </c>
       <c r="H18" s="28" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>IT-12</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="D19" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>오류 응답 형식 일관성</t>
+          <t>POST /api/auth/login: SQL 인젝션/빈 값</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>존재하지 않는 /api 경로 404, 잘못된 메서드 405 모두 JSON {error:{code,message}}</t>
+          <t>401 또는 400, 500 없음</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>IT-13</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>POST /api/privacy/process: 가명/익명 각 1회</t>
+          <t>POST /api/auth/logout: 세션 종료</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>level별 personal_info 가 올바른 값으로 저장 (가명=PSN-…, 익명=None/'익명')</t>
+          <t>204 이후 /me 401, 재로그아웃도 오류 없음</t>
         </is>
       </c>
       <c r="H20" s="28" t="inlineStr">
@@ -2989,7 +2989,7 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>IT-14</t>
+          <t>IT-10</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>가명·익명 처리: 원본 개인정보 비저장·비노출</t>
+          <t>세션: 서로 다른 클라이언트 격리 / 위조 쿠키</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>응답과 DB 전 테이블 어디에도 '홍길동' / '1990-04-12' 없음</t>
+          <t>A 로그인이 B 에 영향 없음, 임의 쿠키는 401</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>IT-15</t>
+          <t>IT-11</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -3046,27 +3046,27 @@
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>POST /api/privacy/process: 잘못된 입력</t>
+          <t>보호 API: 미로그인 호출</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR, personal_info 0건</t>
+          <t>401 반환, 어떤 레코드도 생성되지 않음</t>
         </is>
       </c>
       <c r="H22" s="28" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>IT-16</t>
+          <t>IT-12</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
@@ -3093,27 +3093,27 @@
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>GET /api/privacy/me: 처리 전 404, 처리 후 200</t>
+          <t>오류 응답 형식 일관성</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>404 NOT_FOUND → 200 {level, display, pseudonym_id}</t>
+          <t>존재하지 않는 /api 경로 404, 잘못된 메서드 405 모두 JSON {error:{code,message}}</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>IT-17</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
@@ -3150,17 +3150,17 @@
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>개인정보 처리 결과는 본인 것만 조회</t>
+          <t>POST /api/privacy/process: 가명/익명 각 1회</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>A 의 처리 결과가 B 의 /privacy/me 에 노출되지 않음</t>
+          <t>level별 personal_info 가 올바른 값으로 저장 (가명=PSN-…, 익명=None/'익명')</t>
         </is>
       </c>
       <c r="H24" s="28" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>IT-18</t>
+          <t>IT-14</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
@@ -3187,27 +3187,27 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
-          <t>POST /api/cavp/applications → GET 목록</t>
+          <t>가명·익명 처리: 원본 개인정보 비저장·비노출</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
         <is>
-          <t>201 status=submitted, 목록 응답에 방금 신청 포함</t>
+          <t>응답과 DB 전 테이블 어디에도 '홍길동' / '1990-04-12' 없음</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
@@ -3224,7 +3224,7 @@
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>IT-19</t>
+          <t>IT-15</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>신청 입력 오류/중복</t>
+          <t>POST /api/privacy/process: 잘못된 입력</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>미허용 알고리즘 400, 진행 중 중복 409(DUPLICATE_APPLICATION), 레코드 증가 없음</t>
+          <t>400 VALIDATION_ERROR, personal_info 0건</t>
         </is>
       </c>
       <c r="H26" s="28" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>IT-20</t>
+          <t>IT-16</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
@@ -3281,27 +3281,27 @@
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>신청 목록: 상태 필터·페이지네이션 쿼리</t>
+          <t>GET /api/privacy/me: 처리 전 404, 처리 후 200</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>status/page/per_page 가 반영되고 total 이 필터 기준</t>
+          <t>404 NOT_FOUND → 200 {level, display, pseudonym_id}</t>
         </is>
       </c>
       <c r="H27" s="28" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>IT-21</t>
+          <t>IT-17</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
@@ -3328,27 +3328,27 @@
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>신청 목록: 잘못된 쿼리 파라미터</t>
+          <t>개인정보 처리 결과는 본인 것만 조회</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>page=0, per_page=51, per_page=abc, status=weird → 400</t>
+          <t>A 의 처리 결과가 B 의 /privacy/me 에 노출되지 않음</t>
         </is>
       </c>
       <c r="H28" s="28" t="inlineStr">
@@ -3365,7 +3365,7 @@
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>IT-22</t>
+          <t>IT-18</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
@@ -3385,17 +3385,17 @@
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>신청 조회 격리: 타인 신청 목록/상세</t>
+          <t>POST /api/cavp/applications → GET 목록</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>목록에 타인 건 없음, 타인 상세 403 FORBIDDEN, 없는 id 404</t>
+          <t>201 status=submitted, 목록 응답에 방금 신청 포함</t>
         </is>
       </c>
       <c r="H29" s="28" t="inlineStr">
@@ -3412,7 +3412,7 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>IT-23</t>
+          <t>IT-19</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
-          <t>PATCH /api/cavp/applications/{id}/status: 기관 심사 흐름</t>
+          <t>신청 입력 오류/중복</t>
         </is>
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>submitted→reviewing→approved 200, 잘못된 전이 409 INVALID_TRANSITION, 기관은 타인 신청 상세 조회 가능</t>
+          <t>미허용 알고리즘 400, 진행 중 중복 409(DUPLICATE_APPLICATION), 레코드 증가 없음</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>IT-24</t>
+          <t>IT-20</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
@@ -3479,17 +3479,17 @@
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>PATCH status: 기관이 아닌 사용자 / 알 수 없는 상태</t>
+          <t>신청 목록: 상태 필터·페이지네이션 쿼리</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>403 FORBIDDEN / 400 VALIDATION_ERROR, 상태 불변</t>
+          <t>status/page/per_page 가 반영되고 total 이 필터 기준</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>IT-25</t>
+          <t>IT-21</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
@@ -3516,32 +3516,32 @@
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>POST /api/cavp/applications/{id}/certificate: 승인 건 발급</t>
+          <t>신청 목록: 잘못된 쿼리 파라미터</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>201, tamper_status=normal, 소유자의 /api/certificates 목록·상세에 노출</t>
+          <t>page=0, per_page=51, per_page=abc, status=weird → 400</t>
         </is>
       </c>
       <c r="H32" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I32" s="30" t="n"/>
@@ -3553,7 +3553,7 @@
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
         <is>
-          <t>IT-26</t>
+          <t>IT-22</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
@@ -3563,32 +3563,32 @@
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>검증서 발급 오류 경로</t>
+          <t>신청 조회 격리: 타인 신청 목록/상세</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>미승인 신청 409, 중복 발급 409, 비기관 403, 잘못된 cert_type 400, 레코드 증가 없음</t>
+          <t>목록에 타인 건 없음, 타인 상세 403 FORBIDDEN, 없는 id 404</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I33" s="30" t="n"/>
@@ -3600,7 +3600,7 @@
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>IT-27</t>
+          <t>IT-23</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E34" s="27" t="inlineStr">
@@ -3625,17 +3625,17 @@
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>GET /api/certificates/{id}/verify: 정상 건 / 위변조 의심 건</t>
+          <t>PATCH /api/cavp/applications/{id}/status: 기관 심사 흐름</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>tamper_status 값에 따라 판정 필드 일치(normal / suspected)</t>
+          <t>submitted→reviewing→approved 200, 잘못된 전이 409 INVALID_TRANSITION, 기관은 타인 신청 상세 조회 가능</t>
         </is>
       </c>
       <c r="H34" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I34" s="30" t="n"/>
@@ -3647,7 +3647,7 @@
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>IT-28</t>
+          <t>IT-24</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>검증서 파일 삭제 후 verify</t>
+          <t>PATCH status: 기관이 아닌 사용자 / 알 수 없는 상태</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>200 + suspected (서버 오류 500 아님)</t>
+          <t>403 FORBIDDEN / 400 VALIDATION_ERROR, 상태 불변</t>
         </is>
       </c>
       <c r="H35" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I35" s="30" t="n"/>
@@ -3694,7 +3694,7 @@
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>IT-29</t>
+          <t>IT-25</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
@@ -3714,17 +3714,17 @@
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>검증서 조회 격리</t>
+          <t>POST /api/cavp/applications/{id}/certificate: 승인 건 발급</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>타인의 검증서 상세·verify 403, 목록에 타인 건 없음, 없는 id 404</t>
+          <t>201, tamper_status=normal, 소유자의 /api/certificates 목록·상세에 노출</t>
         </is>
       </c>
       <c r="H36" s="28" t="inlineStr">
@@ -3741,7 +3741,7 @@
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>IT-30</t>
+          <t>IT-26</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
@@ -3751,27 +3751,27 @@
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>검증서 응답 보안: 서버 파일 경로·해시 원문 비노출</t>
+          <t>검증서 발급 오류 경로</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>응답 본문에 저장 디렉터리 경로 없음</t>
+          <t>미승인 신청 409, 중복 발급 409, 비기관 403, 잘못된 cert_type 400, 레코드 증가 없음</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
@@ -3788,7 +3788,7 @@
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>IT-31</t>
+          <t>IT-27</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>FR-14</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E38" s="27" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>E2E: 가입→로그인→가명처리→신청→심사→발급→조회→변조탐지</t>
+          <t>GET /api/certificates/{id}/verify: 정상 건 / 위변조 의심 건</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>전 단계 성공, 변조 후 suspected</t>
+          <t>tamper_status 값에 따라 판정 필드 일치(normal / suspected)</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
@@ -3835,7 +3835,7 @@
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
         <is>
-          <t>IT-32</t>
+          <t>IT-28</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
@@ -3845,27 +3845,27 @@
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>초기데이터(seed) 적재 후 데모 계정으로 화면 데이터 조회</t>
+          <t>검증서 파일 삭제 후 verify</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>demo_individual 로그인 → 신청/검증서 목록 존재, 위변조 의심 건 1건 확인(기관 계정)</t>
+          <t>200 + suspected (서버 오류 500 아님)</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
@@ -3882,42 +3882,42 @@
     <row r="40">
       <c r="A40" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-29</t>
         </is>
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 원문과 다른 bcrypt 해시</t>
+          <t>검증서 조회 격리</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
+          <t>타인의 검증서 상세·verify 403, 목록에 타인 건 없음, 없는 id 404</t>
         </is>
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I40" s="30" t="n"/>
@@ -3929,42 +3929,42 @@
     <row r="41">
       <c r="A41" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>IT-30</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
+          <t>검증서 응답 보안: 서버 파일 경로·해시 원문 비노출</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>두 번 호출한 해시가 서로 다름</t>
+          <t>응답 본문에 저장 디렉터리 경로 없음</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I41" s="30" t="n"/>
@@ -3976,22 +3976,22 @@
     <row r="42">
       <c r="A42" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>IT-31</t>
         </is>
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-14</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E42" s="27" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 올바른 평문</t>
+          <t>E2E: 가입→로그인→가명처리→신청→심사→발급→조회→변조탐지</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>전 단계 성공, 변조 후 suspected</t>
         </is>
       </c>
       <c r="H42" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I42" s="30" t="n"/>
@@ -4023,42 +4023,42 @@
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>IT-32</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D43" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 잘못된 평문</t>
+          <t>초기데이터(seed) 적재 후 데모 계정으로 화면 데이터 조회</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>demo_individual 로그인 → 신청/검증서 목록 존재, 위변조 의심 건 1건 확인(기관 계정)</t>
         </is>
       </c>
       <c r="H43" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I43" s="30" t="n"/>
@@ -4070,37 +4070,37 @@
     <row r="44">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>IT-33</t>
         </is>
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 대소문자 구분</t>
+          <t>GET /api/dashboard: 로그인 사용자의 요약 구조</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>대소문자만 다른 평문은 False</t>
+          <t>200, scope/user/applications/certificates/privacy/recent_applications/notifications 키 포함</t>
         </is>
       </c>
       <c r="H44" s="28" t="inlineStr">
@@ -4117,37 +4117,37 @@
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>IT-34</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D45" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
+          <t>GET /api/dashboard: 비로그인 접근</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>예외 없이 False</t>
+          <t>401 AUTHENTICATION_FAILED</t>
         </is>
       </c>
       <c r="H45" s="28" t="inlineStr">
@@ -4164,37 +4164,37 @@
     <row r="46">
       <c r="A46" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>IT-35</t>
         </is>
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
+          <t>GET /api/dashboard: 사용자 간 데이터 격리</t>
         </is>
       </c>
       <c r="G46" s="29" t="inlineStr">
         <is>
-          <t>해시 생성 후 verify 가 True</t>
+          <t>A 의 신청/검증서 건수가 B 의 응답에 포함되지 않음</t>
         </is>
       </c>
       <c r="H46" s="28" t="inlineStr">
@@ -4211,22 +4211,22 @@
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>IT-36</t>
         </is>
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E47" s="27" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자 가입</t>
+          <t>GET /api/dashboard: 기관 사용자는 전체 범위</t>
         </is>
       </c>
       <c r="G47" s="29" t="inlineStr">
         <is>
-          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
+          <t>scope=all, 타 사용자 신청도 집계에 포함</t>
         </is>
       </c>
       <c r="H47" s="28" t="inlineStr">
@@ -4258,37 +4258,37 @@
     <row r="48">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>IT-37</t>
         </is>
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
+          <t>GET /api/dashboard: 비밀번호/해시 비노출</t>
         </is>
       </c>
       <c r="G48" s="29" t="inlineStr">
         <is>
-          <t>user_type·org_code 가 그대로 저장</t>
+          <t>응답 본문에 password / hash 문자열 없음</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
@@ -4305,37 +4305,37 @@
     <row r="49">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>IT-38</t>
         </is>
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E49" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관인데 org_code 누락</t>
+          <t>GET /api/dashboard: 데이터 변경 즉시 반영</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 사용자 미생성</t>
+          <t>신청·위변조 의심 검증서 추가 후 재호출 시 건수·알림 증가</t>
         </is>
       </c>
       <c r="H49" s="28" t="inlineStr">
@@ -4352,37 +4352,37 @@
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>IT-39</t>
         </is>
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
+          <t>GET /dashboard 페이지: 접근 제어와 화면 요소</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>org_code 는 None</t>
+          <t>비로그인 302 → /, 로그인 시 #welcome/#kpi-in-progress/#recent-body/#notifications/#logout 포함</t>
         </is>
       </c>
       <c r="H50" s="28" t="inlineStr">
@@ -4399,22 +4399,22 @@
     <row r="51">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>IT-40</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D51" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E51" s="27" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>signup: 중복 username</t>
+          <t>POST /api/dashboard: 허용되지 않은 메서드</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
+          <t>405 METHOD_NOT_ALLOWED JSON</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B52" s="27" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
+          <t>hash_password: 원문과 다른 bcrypt 해시</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
-          <t>두 계정 모두 생성</t>
+          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>signup: username 길이 경계 3/4/20/21자</t>
+          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
         <is>
-          <t>4~20자만 허용, 나머지 ValidationError</t>
+          <t>두 번 호출한 해시가 서로 다름</t>
         </is>
       </c>
       <c r="H53" s="28" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="54">
       <c r="A54" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B54" s="27" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
+          <t>verify_password: 올바른 평문</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
@@ -4607,17 +4607,17 @@
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
+          <t>verify_password: 잘못된 평문</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>8~64자만 허용</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H55" s="28" t="inlineStr">
@@ -4634,7 +4634,7 @@
     <row r="56">
       <c r="A56" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B56" s="27" t="inlineStr">
@@ -4654,17 +4654,17 @@
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
+          <t>verify_password: 대소문자 구분</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>숫자만/영문만/공백만 → ValidationError</t>
+          <t>대소문자만 다른 평문은 False</t>
         </is>
       </c>
       <c r="H56" s="28" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="57">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B57" s="27" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>signup: 허용되지 않는 user_type</t>
+          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>예외 없이 False</t>
         </is>
       </c>
       <c r="H57" s="28" t="inlineStr">
@@ -4728,7 +4728,7 @@
     <row r="58">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B58" s="27" t="inlineStr">
@@ -4748,17 +4748,17 @@
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
+          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>예외 후 users 0건</t>
+          <t>해시 생성 후 verify 가 True</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="59">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>login: 올바른 자격 증명</t>
+          <t>signup: 개인 사용자 가입</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>해당 User 반환</t>
+          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
         </is>
       </c>
       <c r="H59" s="28" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B60" s="27" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>login: 비밀번호 불일치</t>
+          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError</t>
+          <t>user_type·org_code 가 그대로 저장</t>
         </is>
       </c>
       <c r="H60" s="28" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="61">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="E61" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F61" s="29" t="inlineStr">
         <is>
-          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
+          <t>signup: 기업/기관인데 org_code 누락</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
+          <t>ValidationError, 사용자 미생성</t>
         </is>
       </c>
       <c r="H61" s="28" t="inlineStr">
@@ -4916,7 +4916,7 @@
     <row r="62">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B62" s="27" t="inlineStr">
@@ -4936,17 +4936,17 @@
       </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>login: 빈 입력/인젝션 문자열</t>
+          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
         </is>
       </c>
       <c r="G62" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError (예외 유형 일관)</t>
+          <t>org_code 는 None</t>
         </is>
       </c>
       <c r="H62" s="28" t="inlineStr">
@@ -4963,7 +4963,7 @@
     <row r="63">
       <c r="A63" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
@@ -4983,17 +4983,17 @@
       </c>
       <c r="E63" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>get_user: 존재하는 id / 없는 id</t>
+          <t>signup: 중복 username</t>
         </is>
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>존재하면 User, 없으면 NotFoundError</t>
+          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
         </is>
       </c>
       <c r="H63" s="28" t="inlineStr">
@@ -5010,7 +5010,7 @@
     <row r="64">
       <c r="A64" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B64" s="27" t="inlineStr">
@@ -5020,27 +5020,27 @@
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>create_application: 유효한 알고리즘</t>
+          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>status='submitted', submitted_at 설정, 본인 소유</t>
+          <t>두 계정 모두 생성</t>
         </is>
       </c>
       <c r="H64" s="28" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="65">
       <c r="A65" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B65" s="27" t="inlineStr">
@@ -5067,27 +5067,27 @@
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D65" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E65" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>create_application: 허용 알고리즘 전체</t>
+          <t>signup: username 길이 경계 3/4/20/21자</t>
         </is>
       </c>
       <c r="G65" s="29" t="inlineStr">
         <is>
-          <t>ALGORITHMS 의 모든 값 신청 가능</t>
+          <t>4~20자만 허용, 나머지 ValidationError</t>
         </is>
       </c>
       <c r="H65" s="28" t="inlineStr">
@@ -5104,7 +5104,7 @@
     <row r="66">
       <c r="A66" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B66" s="27" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="C66" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E66" s="27" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="F66" s="29" t="inlineStr">
         <is>
-          <t>create_application: 빈 값/미허용 알고리즘</t>
+          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
         </is>
       </c>
       <c r="G66" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 레코드 미생성</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="67">
       <c r="A67" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B67" s="27" t="inlineStr">
@@ -5161,27 +5161,27 @@
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E67" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>create_application: 없는 사용자</t>
+          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>8~64자만 허용</t>
         </is>
       </c>
       <c r="H67" s="28" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="68">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B68" s="27" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="C68" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E68" s="27" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
-          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
+          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
         </is>
       </c>
       <c r="G68" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
+          <t>숫자만/영문만/공백만 → ValidationError</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="69">
       <c r="A69" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B69" s="27" t="inlineStr">
@@ -5255,27 +5255,27 @@
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E69" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
+          <t>signup: 허용되지 않는 user_type</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>허용</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H69" s="28" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="70">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B70" s="27" t="inlineStr">
@@ -5302,27 +5302,27 @@
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E70" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용 전이 3종</t>
+          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
+          <t>예외 후 users 0건</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="71">
       <c r="A71" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B71" s="27" t="inlineStr">
@@ -5349,27 +5349,27 @@
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D71" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E71" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F71" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
+          <t>login: 올바른 자격 증명</t>
         </is>
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 상태 불변</t>
+          <t>해당 User 반환</t>
         </is>
       </c>
       <c r="H71" s="28" t="inlineStr">
@@ -5386,7 +5386,7 @@
     <row r="72">
       <c r="A72" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B72" s="27" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="C72" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E72" s="27" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>update_status: 존재하지 않는 상태값</t>
+          <t>login: 비밀번호 불일치</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>AuthenticationError</t>
         </is>
       </c>
       <c r="H72" s="28" t="inlineStr">
@@ -5433,7 +5433,7 @@
     <row r="73">
       <c r="A73" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B73" s="27" t="inlineStr">
@@ -5443,27 +5443,27 @@
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D73" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E73" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>update_status: 전이 시 updated_at 갱신</t>
+          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>updated_at 이 이전보다 이후</t>
+          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
         </is>
       </c>
       <c r="H73" s="28" t="inlineStr">
@@ -5480,7 +5480,7 @@
     <row r="74">
       <c r="A74" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B74" s="27" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E74" s="27" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
+          <t>login: 빈 입력/인젝션 문자열</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError, 상태 불변</t>
+          <t>AuthenticationError (예외 유형 일관)</t>
         </is>
       </c>
       <c r="H74" s="28" t="inlineStr">
@@ -5527,7 +5527,7 @@
     <row r="75">
       <c r="A75" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B75" s="27" t="inlineStr">
@@ -5537,27 +5537,27 @@
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D75" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E75" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>update_status: 없는 신청/없는 사용자</t>
+          <t>get_user: 존재하는 id / 없는 id</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>존재하면 User, 없으면 NotFoundError</t>
         </is>
       </c>
       <c r="H75" s="28" t="inlineStr">
@@ -5574,7 +5574,7 @@
     <row r="76">
       <c r="A76" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B76" s="27" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 본인 신청만, 최신순</t>
+          <t>create_application: 유효한 알고리즘</t>
         </is>
       </c>
       <c r="G76" s="29" t="inlineStr">
         <is>
-          <t>타인 신청 제외, submitted_at 내림차순</t>
+          <t>status='submitted', submitted_at 설정, 본인 소유</t>
         </is>
       </c>
       <c r="H76" s="28" t="inlineStr">
@@ -5621,7 +5621,7 @@
     <row r="77">
       <c r="A77" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B77" s="27" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="F77" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 상태 필터</t>
+          <t>create_application: 허용 알고리즘 전체</t>
         </is>
       </c>
       <c r="G77" s="29" t="inlineStr">
         <is>
-          <t>해당 상태만 반환, total 도 필터 기준</t>
+          <t>ALGORITHMS 의 모든 값 신청 가능</t>
         </is>
       </c>
       <c r="H77" s="28" t="inlineStr">
@@ -5668,7 +5668,7 @@
     <row r="78">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 잘못된 상태 필터</t>
+          <t>create_application: 빈 값/미허용 알고리즘</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>ValidationError, 레코드 미생성</t>
         </is>
       </c>
       <c r="H78" s="28" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="79">
       <c r="A79" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
@@ -5735,17 +5735,17 @@
       </c>
       <c r="E79" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F79" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
+          <t>create_application: 없는 사용자</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
         <is>
-          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H79" s="28" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="80">
       <c r="A80" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B80" s="27" t="inlineStr">
@@ -5782,17 +5782,17 @@
       </c>
       <c r="E80" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F80" s="29" t="inlineStr">
         <is>
-          <t>list_applications: page/per_page 경계값</t>
+          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
         </is>
       </c>
       <c r="G80" s="29" t="inlineStr">
         <is>
-          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
+          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
         </is>
       </c>
       <c r="H80" s="28" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="81">
       <c r="A81" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
@@ -5829,17 +5829,17 @@
       </c>
       <c r="E81" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F81" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 신청이 없으면 빈 목록</t>
+          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
         </is>
       </c>
       <c r="G81" s="29" t="inlineStr">
         <is>
-          <t>items=[], total=0</t>
+          <t>허용</t>
         </is>
       </c>
       <c r="H81" s="28" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="82">
       <c r="A82" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>get_application: 본인 / 타인 / 없는 id</t>
+          <t>update_status: 허용 전이 3종</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
         </is>
       </c>
       <c r="H82" s="28" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="83">
       <c r="A83" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="E83" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>get_application: institution 은 모든 신청 조회 가능</t>
+          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>타인 신청도 반환</t>
+          <t>InvalidTransitionError, 상태 불변</t>
         </is>
       </c>
       <c r="H83" s="28" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="84">
       <c r="A84" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
@@ -5960,32 +5960,32 @@
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E84" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: SHA-256 hex</t>
+          <t>update_status: 존재하지 않는 상태값</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I84" s="30" t="n"/>
@@ -5997,7 +5997,7 @@
     <row r="85">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D85" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
@@ -6022,17 +6022,17 @@
       </c>
       <c r="F85" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
+          <t>update_status: 전이 시 updated_at 갱신</t>
         </is>
       </c>
       <c r="G85" s="29" t="inlineStr">
         <is>
-          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
+          <t>updated_at 이 이전보다 이후</t>
         </is>
       </c>
       <c r="H85" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I85" s="30" t="n"/>
@@ -6044,7 +6044,7 @@
     <row r="86">
       <c r="A86" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
@@ -6054,32 +6054,32 @@
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E86" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 동일 해시</t>
+          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>'normal'</t>
+          <t>PermissionDeniedError, 상태 불변</t>
         </is>
       </c>
       <c r="H86" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I86" s="30" t="n"/>
@@ -6091,7 +6091,7 @@
     <row r="87">
       <c r="A87" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E87" s="27" t="inlineStr">
@@ -6116,17 +6116,17 @@
       </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 상이한 해시</t>
+          <t>update_status: 없는 신청/없는 사용자</t>
         </is>
       </c>
       <c r="G87" s="29" t="inlineStr">
         <is>
-          <t>'suspected'</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H87" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I87" s="30" t="n"/>
@@ -6138,7 +6138,7 @@
     <row r="88">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
@@ -6148,32 +6148,32 @@
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E88" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 대소문자만 다른 hex</t>
+          <t>list_applications: 본인 신청만, 최신순</t>
         </is>
       </c>
       <c r="G88" s="29" t="inlineStr">
         <is>
-          <t>동일 값으로 보고 'normal'</t>
+          <t>타인 신청 제외, submitted_at 내림차순</t>
         </is>
       </c>
       <c r="H88" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I88" s="30" t="n"/>
@@ -6185,7 +6185,7 @@
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
@@ -6210,17 +6210,17 @@
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인된 신청에 발급</t>
+          <t>list_applications: 상태 필터</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
+          <t>해당 상태만 반환, total 도 필터 기준</t>
         </is>
       </c>
       <c r="H89" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I89" s="30" t="n"/>
@@ -6232,7 +6232,7 @@
     <row r="90">
       <c r="A90" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E90" s="27" t="inlineStr">
@@ -6257,17 +6257,17 @@
       </c>
       <c r="F90" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인 이전/반려 상태</t>
+          <t>list_applications: 잘못된 상태 필터</t>
         </is>
       </c>
       <c r="G90" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 검증서 미생성</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I90" s="30" t="n"/>
@@ -6279,7 +6279,7 @@
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F91" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 신청당 1건(중복 발급)</t>
+          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError</t>
+          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
         </is>
       </c>
       <c r="H91" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I91" s="30" t="n"/>
@@ -6326,7 +6326,7 @@
     <row r="92">
       <c r="A92" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B92" s="27" t="inlineStr">
@@ -6336,32 +6336,32 @@
       </c>
       <c r="C92" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E92" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: institution 이 아니면 발급 불가</t>
+          <t>list_applications: page/per_page 경계값</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError</t>
+          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
         </is>
       </c>
       <c r="H92" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I92" s="30" t="n"/>
@@ -6373,7 +6373,7 @@
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
@@ -6383,32 +6383,32 @@
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D93" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
+          <t>list_applications: 신청이 없으면 빈 목록</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>ValidationError / ValidationError / NotFoundError</t>
+          <t>items=[], total=0</t>
         </is>
       </c>
       <c r="H93" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I93" s="30" t="n"/>
@@ -6420,7 +6420,7 @@
     <row r="94">
       <c r="A94" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
@@ -6430,32 +6430,32 @@
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: KCMVP 유형도 발급</t>
+          <t>get_application: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>cert_type='KCMVP'</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I94" s="30" t="n"/>
@@ -6467,7 +6467,7 @@
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D95" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
+          <t>get_application: institution 은 모든 신청 조회 가능</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>타인 검증서 제외, issued_at 내림차순</t>
+          <t>타인 신청도 반환</t>
         </is>
       </c>
       <c r="H95" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I95" s="30" t="n"/>
@@ -6514,7 +6514,7 @@
     <row r="96">
       <c r="A96" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
@@ -6524,27 +6524,27 @@
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
+          <t>compute_hash: SHA-256 hex</t>
         </is>
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
+          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
@@ -6571,27 +6571,27 @@
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D97" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E97" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>get_certificate: 본인 / 타인 / 없는 id</t>
+          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
         </is>
       </c>
       <c r="H97" s="28" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="98">
       <c r="A98" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 무결 → normal</t>
+          <t>compare_hash: 동일 해시</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
         <is>
-          <t>tamper_status='normal'</t>
+          <t>'normal'</t>
         </is>
       </c>
       <c r="H98" s="28" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="99">
       <c r="A99" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
@@ -6675,17 +6675,17 @@
       </c>
       <c r="E99" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
+          <t>compare_hash: 상이한 해시</t>
         </is>
       </c>
       <c r="G99" s="29" t="inlineStr">
         <is>
-          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
+          <t>'suspected'</t>
         </is>
       </c>
       <c r="H99" s="28" t="inlineStr">
@@ -6702,7 +6702,7 @@
     <row r="100">
       <c r="A100" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
@@ -6722,17 +6722,17 @@
       </c>
       <c r="E100" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
+          <t>compare_hash: 대소문자만 다른 hex</t>
         </is>
       </c>
       <c r="G100" s="29" t="inlineStr">
         <is>
-          <t>'suspected' (예외 아님)</t>
+          <t>동일 값으로 보고 'normal'</t>
         </is>
       </c>
       <c r="H100" s="28" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="101">
       <c r="A101" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
@@ -6759,27 +6759,27 @@
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D101" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E101" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F101" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 원복 후 재검증 시 normal</t>
+          <t>issue_certificate: 승인된 신청에 발급</t>
         </is>
       </c>
       <c r="G101" s="29" t="inlineStr">
         <is>
-          <t>변조 → suspected, 원복 → normal</t>
+          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
         </is>
       </c>
       <c r="H101" s="28" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="102">
       <c r="A102" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E102" s="27" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="F102" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 존재하지 않는 cert_id</t>
+          <t>issue_certificate: 승인 이전/반려 상태</t>
         </is>
       </c>
       <c r="G102" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>InvalidTransitionError, 검증서 미생성</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
@@ -6843,7 +6843,7 @@
     <row r="103">
       <c r="A103" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
@@ -6853,27 +6853,27 @@
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D103" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E103" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F103" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
+          <t>issue_certificate: 신청당 1건(중복 발급)</t>
         </is>
       </c>
       <c r="G103" s="29" t="inlineStr">
         <is>
-          <t>검증 후에도 integrity_hash 불변</t>
+          <t>DuplicateApplicationError</t>
         </is>
       </c>
       <c r="H103" s="28" t="inlineStr">
@@ -6890,7 +6890,7 @@
     <row r="104">
       <c r="A104" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
@@ -6900,27 +6900,27 @@
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E104" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F104" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
+          <t>issue_certificate: institution 이 아니면 발급 불가</t>
         </is>
       </c>
       <c r="G104" s="29" t="inlineStr">
         <is>
-          <t>파일이 없으면 suspected 유지</t>
+          <t>PermissionDeniedError</t>
         </is>
       </c>
       <c r="H104" s="28" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="105">
       <c r="A105" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B105" s="27" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D105" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E105" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
+          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
         </is>
       </c>
       <c r="G105" s="29" t="inlineStr">
         <is>
-          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
+          <t>ValidationError / ValidationError / NotFoundError</t>
         </is>
       </c>
       <c r="H105" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I105" s="30" t="n"/>
@@ -6984,7 +6984,7 @@
     <row r="106">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
@@ -6994,32 +6994,32 @@
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E106" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F106" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 호출마다 다른 값</t>
+          <t>issue_certificate: KCMVP 유형도 발급</t>
         </is>
       </c>
       <c r="G106" s="29" t="inlineStr">
         <is>
-          <t>1000회 호출 모두 유일</t>
+          <t>cert_type='KCMVP'</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I106" s="30" t="n"/>
@@ -7031,7 +7031,7 @@
     <row r="107">
       <c r="A107" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D107" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E107" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 길이별 마스킹 규칙</t>
+          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
+          <t>타인 검증서 제외, issued_at 내림차순</t>
         </is>
       </c>
       <c r="H107" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I107" s="30" t="n"/>
@@ -7078,7 +7078,7 @@
     <row r="108">
       <c r="A108" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B108" s="27" t="inlineStr">
@@ -7088,32 +7088,32 @@
       </c>
       <c r="C108" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F108" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 빈 값/공백만</t>
+          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
         </is>
       </c>
       <c r="G108" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
         </is>
       </c>
       <c r="H108" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I108" s="30" t="n"/>
@@ -7125,7 +7125,7 @@
     <row r="109">
       <c r="A109" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B109" s="27" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D109" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
+          <t>get_certificate: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>' 홍길동 ' → '홍*동'</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H109" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I109" s="30" t="n"/>
@@ -7172,7 +7172,7 @@
     <row r="110">
       <c r="A110" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B110" s="27" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C110" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E110" s="27" t="inlineStr">
@@ -7197,17 +7197,17 @@
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 하이픈 유/무 입력</t>
+          <t>verify_integrity: 파일 무결 → normal</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>모두 '010-****-5678'</t>
+          <t>tamper_status='normal'</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I110" s="30" t="n"/>
@@ -7219,7 +7219,7 @@
     <row r="111">
       <c r="A111" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B111" s="27" t="inlineStr">
@@ -7229,32 +7229,32 @@
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D111" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E111" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
+          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
         </is>
       </c>
       <c r="G111" s="29" t="inlineStr">
         <is>
-          <t>'010-***-4567'</t>
+          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
         </is>
       </c>
       <c r="H111" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I111" s="30" t="n"/>
@@ -7266,7 +7266,7 @@
     <row r="112">
       <c r="A112" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B112" s="27" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="C112" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E112" s="27" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 형식 오류</t>
+          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>'suspected' (예외 아님)</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I112" s="30" t="n"/>
@@ -7313,7 +7313,7 @@
     <row r="113">
       <c r="A113" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B113" s="27" t="inlineStr">
@@ -7323,32 +7323,32 @@
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D113" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 대표 연령대</t>
+          <t>verify_integrity: 원복 후 재검증 시 normal</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
+          <t>변조 → suspected, 원복 → normal</t>
         </is>
       </c>
       <c r="H113" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I113" s="30" t="n"/>
@@ -7360,7 +7360,7 @@
     <row r="114">
       <c r="A114" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B114" s="27" t="inlineStr">
@@ -7370,32 +7370,32 @@
       </c>
       <c r="C114" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F114" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
+          <t>verify_integrity: 존재하지 않는 cert_id</t>
         </is>
       </c>
       <c r="G114" s="29" t="inlineStr">
         <is>
-          <t>생일 당일부터 다음 연령대</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I114" s="30" t="n"/>
@@ -7407,7 +7407,7 @@
     <row r="115">
       <c r="A115" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B115" s="27" t="inlineStr">
@@ -7417,32 +7417,32 @@
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D115" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
+          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
         </is>
       </c>
       <c r="G115" s="29" t="inlineStr">
         <is>
-          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
+          <t>검증 후에도 integrity_hash 불변</t>
         </is>
       </c>
       <c r="H115" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I115" s="30" t="n"/>
@@ -7454,7 +7454,7 @@
     <row r="116">
       <c r="A116" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B116" s="27" t="inlineStr">
@@ -7464,32 +7464,32 @@
       </c>
       <c r="C116" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D116" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F116" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 미래 날짜</t>
+          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>파일이 없으면 suspected 유지</t>
         </is>
       </c>
       <c r="H116" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I116" s="30" t="n"/>
@@ -7501,7 +7501,7 @@
     <row r="117">
       <c r="A117" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B117" s="27" t="inlineStr">
@@ -7511,27 +7511,27 @@
       </c>
       <c r="C117" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D117" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E117" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F117" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
+          <t>get_summary: 본인 신청만 집계</t>
         </is>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>연·월·일 숫자열이 결과에 없음</t>
+          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
         </is>
       </c>
       <c r="H117" s="28" t="inlineStr">
@@ -7548,7 +7548,7 @@
     <row r="118">
       <c r="A118" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B118" s="27" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="C118" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D118" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E118" s="27" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="F118" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 결과 객체</t>
+          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
         </is>
       </c>
       <c r="G118" s="29" t="inlineStr">
         <is>
-          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
+          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
         </is>
       </c>
       <c r="H118" s="28" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="119">
       <c r="A119" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B119" s="27" t="inlineStr">
@@ -7605,27 +7605,27 @@
       </c>
       <c r="C119" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D119" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E119" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F119" s="29" t="inlineStr">
         <is>
-          <t>process(anonymous): 식별자 없음</t>
+          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
         </is>
       </c>
       <c r="G119" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
+          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
         </is>
       </c>
       <c r="H119" s="28" t="inlineStr">
@@ -7642,7 +7642,7 @@
     <row r="120">
       <c r="A120" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B120" s="27" t="inlineStr">
@@ -7652,27 +7652,27 @@
       </c>
       <c r="C120" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D120" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E120" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F120" s="29" t="inlineStr">
         <is>
-          <t>process: 허용되지 않는 mode</t>
+          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
         </is>
       </c>
       <c r="G120" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="H120" s="28" t="inlineStr">
@@ -7689,7 +7689,7 @@
     <row r="121">
       <c r="A121" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B121" s="27" t="inlineStr">
@@ -7699,27 +7699,27 @@
       </c>
       <c r="C121" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D121" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E121" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F121" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
+          <t>get_summary: 상태 라벨 매핑</t>
         </is>
       </c>
       <c r="G121" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
         </is>
       </c>
       <c r="H121" s="28" t="inlineStr">
@@ -7736,7 +7736,7 @@
     <row r="122">
       <c r="A122" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B122" s="27" t="inlineStr">
@@ -7746,27 +7746,27 @@
       </c>
       <c r="C122" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D122" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E122" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F122" s="29" t="inlineStr">
         <is>
-          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
+          <t>get_summary: 최근 7일 신규 신청 경계</t>
         </is>
       </c>
       <c r="G122" s="29" t="inlineStr">
         <is>
-          <t>표시값/식별자에 '홍길동' 미포함</t>
+          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
         </is>
       </c>
       <c r="H122" s="28" t="inlineStr">
@@ -7783,7 +7783,7 @@
     <row r="123">
       <c r="A123" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B123" s="27" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="C123" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D123" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E123" s="27" t="inlineStr">
@@ -7808,17 +7808,17 @@
       </c>
       <c r="F123" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: personal_info 저장</t>
+          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
         </is>
       </c>
       <c r="G123" s="29" t="inlineStr">
         <is>
-          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
+          <t>total·suspected 가 본인 건만 반영</t>
         </is>
       </c>
       <c r="H123" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I123" s="30" t="n"/>
@@ -7830,7 +7830,7 @@
     <row r="124">
       <c r="A124" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B124" s="27" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="F124" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
+          <t>get_summary: 가명·익명 처리 상태</t>
         </is>
       </c>
       <c r="G124" s="29" t="inlineStr">
         <is>
-          <t>행 1건, pseudonym_id 동일</t>
+          <t>처리 전 processed=False, 처리 후 level 반영</t>
         </is>
       </c>
       <c r="H124" s="28" t="inlineStr">
@@ -7877,7 +7877,7 @@
     <row r="125">
       <c r="A125" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B125" s="27" t="inlineStr">
@@ -7887,12 +7887,12 @@
       </c>
       <c r="C125" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D125" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E125" s="27" t="inlineStr">
@@ -7902,17 +7902,17 @@
       </c>
       <c r="F125" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
+          <t>get_summary: 위변조 의심 알림이 최우선</t>
         </is>
       </c>
       <c r="G125" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None</t>
+          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
         </is>
       </c>
       <c r="H125" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I125" s="30" t="n"/>
@@ -7924,7 +7924,7 @@
     <row r="126">
       <c r="A126" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B126" s="27" t="inlineStr">
@@ -7934,27 +7934,27 @@
       </c>
       <c r="C126" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D126" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E126" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F126" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 없는 사용자</t>
+          <t>get_summary: 신청 진행/결과 알림 문구</t>
         </is>
       </c>
       <c r="G126" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError, 행 미생성</t>
+          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
         </is>
       </c>
       <c r="H126" s="28" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="127">
       <c r="A127" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B127" s="27" t="inlineStr">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="C127" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D127" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E127" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F127" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+          <t>get_summary: 알림은 최대 5건</t>
         </is>
       </c>
       <c r="G127" s="29" t="inlineStr">
         <is>
-          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
         </is>
       </c>
       <c r="H127" s="28" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="128">
       <c r="A128" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B128" s="27" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="C128" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D128" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E128" s="27" t="inlineStr">
@@ -8043,17 +8043,17 @@
       </c>
       <c r="F128" s="29" t="inlineStr">
         <is>
-          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
         </is>
       </c>
       <c r="G128" s="29" t="inlineStr">
         <is>
-          <t>저장된 행 반환, 없으면 NotFoundError</t>
+          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
         </is>
       </c>
       <c r="H128" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I128" s="30" t="n"/>
@@ -8065,7 +8065,7 @@
     <row r="129">
       <c r="A129" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B129" s="27" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D129" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E129" s="27" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="F129" s="29" t="inlineStr">
         <is>
-          <t>seed: 사용자 3종 생성</t>
+          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
         </is>
       </c>
       <c r="G129" s="29" t="inlineStr">
         <is>
-          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+          <t>scope='own'</t>
         </is>
       </c>
       <c r="H129" s="28" t="inlineStr">
@@ -8112,7 +8112,7 @@
     <row r="130">
       <c r="A130" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B130" s="27" t="inlineStr">
@@ -8127,22 +8127,22 @@
       </c>
       <c r="D130" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E130" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F130" s="29" t="inlineStr">
         <is>
-          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+          <t>get_summary: 없는 사용자</t>
         </is>
       </c>
       <c r="G130" s="29" t="inlineStr">
         <is>
-          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H130" s="28" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="131">
       <c r="A131" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B131" s="27" t="inlineStr">
@@ -8169,27 +8169,27 @@
       </c>
       <c r="C131" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D131" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E131" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F131" s="29" t="inlineStr">
         <is>
-          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
         </is>
       </c>
       <c r="G131" s="29" t="inlineStr">
         <is>
-          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+          <t>결과 전체에 password/hash 키 없음</t>
         </is>
       </c>
       <c r="H131" s="28" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="132">
       <c r="A132" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B132" s="27" t="inlineStr">
@@ -8216,32 +8216,32 @@
       </c>
       <c r="C132" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D132" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E132" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F132" s="29" t="inlineStr">
         <is>
-          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
         <is>
-          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
         </is>
       </c>
       <c r="H132" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I132" s="30" t="n"/>
@@ -8253,7 +8253,7 @@
     <row r="133">
       <c r="A133" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B133" s="27" t="inlineStr">
@@ -8268,22 +8268,22 @@
       </c>
       <c r="D133" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E133" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F133" s="29" t="inlineStr">
         <is>
-          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
         </is>
       </c>
       <c r="G133" s="29" t="inlineStr">
         <is>
-          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
         </is>
       </c>
       <c r="H133" s="28" t="inlineStr">
@@ -8300,7 +8300,7 @@
     <row r="134">
       <c r="A134" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B134" s="27" t="inlineStr">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="C134" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D134" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E134" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F134" s="29" t="inlineStr">
         <is>
-          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+          <t>issue_pseudonym_id: 호출마다 다른 값</t>
         </is>
       </c>
       <c r="G134" s="29" t="inlineStr">
         <is>
-          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+          <t>1000회 호출 모두 유일</t>
         </is>
       </c>
       <c r="H134" s="28" t="inlineStr">
@@ -8344,9 +8344,1325 @@
         <v/>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-03</t>
+        </is>
+      </c>
+      <c r="B135" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C135" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D135" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E135" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F135" s="29" t="inlineStr">
+        <is>
+          <t>mask_name: 길이별 마스킹 규칙</t>
+        </is>
+      </c>
+      <c r="G135" s="29" t="inlineStr">
+        <is>
+          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
+        </is>
+      </c>
+      <c r="H135" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I135" s="30" t="n"/>
+      <c r="J135" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A135,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-04</t>
+        </is>
+      </c>
+      <c r="B136" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C136" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D136" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E136" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F136" s="29" t="inlineStr">
+        <is>
+          <t>mask_name: 빈 값/공백만</t>
+        </is>
+      </c>
+      <c r="G136" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H136" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I136" s="30" t="n"/>
+      <c r="J136" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A136,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-05</t>
+        </is>
+      </c>
+      <c r="B137" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C137" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D137" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E137" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F137" s="29" t="inlineStr">
+        <is>
+          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
+        </is>
+      </c>
+      <c r="G137" s="29" t="inlineStr">
+        <is>
+          <t>' 홍길동 ' → '홍*동'</t>
+        </is>
+      </c>
+      <c r="H137" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I137" s="30" t="n"/>
+      <c r="J137" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A137,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-06</t>
+        </is>
+      </c>
+      <c r="B138" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C138" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D138" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E138" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F138" s="29" t="inlineStr">
+        <is>
+          <t>mask_phone: 하이픈 유/무 입력</t>
+        </is>
+      </c>
+      <c r="G138" s="29" t="inlineStr">
+        <is>
+          <t>모두 '010-****-5678'</t>
+        </is>
+      </c>
+      <c r="H138" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I138" s="30" t="n"/>
+      <c r="J138" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A138,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-07</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C139" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D139" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E139" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F139" s="29" t="inlineStr">
+        <is>
+          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
+        </is>
+      </c>
+      <c r="G139" s="29" t="inlineStr">
+        <is>
+          <t>'010-***-4567'</t>
+        </is>
+      </c>
+      <c r="H139" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I139" s="30" t="n"/>
+      <c r="J139" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A139,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-08</t>
+        </is>
+      </c>
+      <c r="B140" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C140" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D140" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E140" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F140" s="29" t="inlineStr">
+        <is>
+          <t>mask_phone: 형식 오류</t>
+        </is>
+      </c>
+      <c r="G140" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H140" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I140" s="30" t="n"/>
+      <c r="J140" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A140,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-09</t>
+        </is>
+      </c>
+      <c r="B141" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C141" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D141" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E141" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F141" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 대표 연령대</t>
+        </is>
+      </c>
+      <c r="G141" s="29" t="inlineStr">
+        <is>
+          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="H141" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I141" s="30" t="n"/>
+      <c r="J141" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A141,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-10</t>
+        </is>
+      </c>
+      <c r="B142" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C142" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D142" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E142" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F142" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
+        </is>
+      </c>
+      <c r="G142" s="29" t="inlineStr">
+        <is>
+          <t>생일 당일부터 다음 연령대</t>
+        </is>
+      </c>
+      <c r="H142" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I142" s="30" t="n"/>
+      <c r="J142" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A142,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-11</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C143" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D143" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E143" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F143" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
+        </is>
+      </c>
+      <c r="G143" s="29" t="inlineStr">
+        <is>
+          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
+        </is>
+      </c>
+      <c r="H143" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I143" s="30" t="n"/>
+      <c r="J143" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A143,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-12</t>
+        </is>
+      </c>
+      <c r="B144" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C144" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D144" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E144" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F144" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 미래 날짜</t>
+        </is>
+      </c>
+      <c r="G144" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H144" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I144" s="30" t="n"/>
+      <c r="J144" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A144,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-13</t>
+        </is>
+      </c>
+      <c r="B145" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C145" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D145" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E145" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F145" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
+        </is>
+      </c>
+      <c r="G145" s="29" t="inlineStr">
+        <is>
+          <t>연·월·일 숫자열이 결과에 없음</t>
+        </is>
+      </c>
+      <c r="H145" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I145" s="30" t="n"/>
+      <c r="J145" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A145,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-14</t>
+        </is>
+      </c>
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C146" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D146" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E146" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F146" s="29" t="inlineStr">
+        <is>
+          <t>process(pseudonym): 결과 객체</t>
+        </is>
+      </c>
+      <c r="G146" s="29" t="inlineStr">
+        <is>
+          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
+        </is>
+      </c>
+      <c r="H146" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I146" s="30" t="n"/>
+      <c r="J146" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A146,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-15</t>
+        </is>
+      </c>
+      <c r="B147" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C147" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D147" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E147" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F147" s="29" t="inlineStr">
+        <is>
+          <t>process(anonymous): 식별자 없음</t>
+        </is>
+      </c>
+      <c r="G147" s="29" t="inlineStr">
+        <is>
+          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
+        </is>
+      </c>
+      <c r="H147" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I147" s="30" t="n"/>
+      <c r="J147" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A147,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-16</t>
+        </is>
+      </c>
+      <c r="B148" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C148" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D148" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E148" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F148" s="29" t="inlineStr">
+        <is>
+          <t>process: 허용되지 않는 mode</t>
+        </is>
+      </c>
+      <c r="G148" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H148" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I148" s="30" t="n"/>
+      <c r="J148" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A148,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-17</t>
+        </is>
+      </c>
+      <c r="B149" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C149" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D149" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E149" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F149" s="29" t="inlineStr">
+        <is>
+          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
+        </is>
+      </c>
+      <c r="G149" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H149" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I149" s="30" t="n"/>
+      <c r="J149" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A149,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-18</t>
+        </is>
+      </c>
+      <c r="B150" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C150" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D150" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E150" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F150" s="29" t="inlineStr">
+        <is>
+          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
+        </is>
+      </c>
+      <c r="G150" s="29" t="inlineStr">
+        <is>
+          <t>표시값/식별자에 '홍길동' 미포함</t>
+        </is>
+      </c>
+      <c r="H150" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I150" s="30" t="n"/>
+      <c r="J150" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A150,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-19</t>
+        </is>
+      </c>
+      <c r="B151" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C151" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D151" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E151" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F151" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: personal_info 저장</t>
+        </is>
+      </c>
+      <c r="G151" s="29" t="inlineStr">
+        <is>
+          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
+        </is>
+      </c>
+      <c r="H151" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I151" s="30" t="n"/>
+      <c r="J151" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A151,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-20</t>
+        </is>
+      </c>
+      <c r="B152" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C152" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D152" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E152" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F152" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
+        </is>
+      </c>
+      <c r="G152" s="29" t="inlineStr">
+        <is>
+          <t>행 1건, pseudonym_id 동일</t>
+        </is>
+      </c>
+      <c r="H152" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I152" s="30" t="n"/>
+      <c r="J152" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A152,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-21</t>
+        </is>
+      </c>
+      <c r="B153" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C153" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D153" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E153" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F153" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
+        </is>
+      </c>
+      <c r="G153" s="29" t="inlineStr">
+        <is>
+          <t>level='anonymous', pseudonym_id=None</t>
+        </is>
+      </c>
+      <c r="H153" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I153" s="30" t="n"/>
+      <c r="J153" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A153,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-22</t>
+        </is>
+      </c>
+      <c r="B154" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C154" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D154" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E154" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F154" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 없는 사용자</t>
+        </is>
+      </c>
+      <c r="G154" s="29" t="inlineStr">
+        <is>
+          <t>NotFoundError, 행 미생성</t>
+        </is>
+      </c>
+      <c r="H154" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I154" s="30" t="n"/>
+      <c r="J154" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A154,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-23</t>
+        </is>
+      </c>
+      <c r="B155" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C155" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D155" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E155" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F155" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+        </is>
+      </c>
+      <c r="G155" s="29" t="inlineStr">
+        <is>
+          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+        </is>
+      </c>
+      <c r="H155" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I155" s="30" t="n"/>
+      <c r="J155" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A155,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-24</t>
+        </is>
+      </c>
+      <c r="B156" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C156" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D156" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E156" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F156" s="29" t="inlineStr">
+        <is>
+          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+        </is>
+      </c>
+      <c r="G156" s="29" t="inlineStr">
+        <is>
+          <t>저장된 행 반환, 없으면 NotFoundError</t>
+        </is>
+      </c>
+      <c r="H156" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I156" s="30" t="n"/>
+      <c r="J156" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A156,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-01</t>
+        </is>
+      </c>
+      <c r="B157" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C157" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D157" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E157" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F157" s="29" t="inlineStr">
+        <is>
+          <t>seed: 사용자 3종 생성</t>
+        </is>
+      </c>
+      <c r="G157" s="29" t="inlineStr">
+        <is>
+          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+        </is>
+      </c>
+      <c r="H157" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I157" s="30" t="n"/>
+      <c r="J157" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A157,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B158" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C158" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D158" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E158" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F158" s="29" t="inlineStr">
+        <is>
+          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+        </is>
+      </c>
+      <c r="G158" s="29" t="inlineStr">
+        <is>
+          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+        </is>
+      </c>
+      <c r="H158" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I158" s="30" t="n"/>
+      <c r="J158" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A158,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B159" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C159" s="27" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="D159" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E159" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F159" s="29" t="inlineStr">
+        <is>
+          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+        </is>
+      </c>
+      <c r="G159" s="29" t="inlineStr">
+        <is>
+          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+        </is>
+      </c>
+      <c r="H159" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I159" s="30" t="n"/>
+      <c r="J159" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A159,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B160" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C160" s="27" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="D160" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E160" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F160" s="29" t="inlineStr">
+        <is>
+          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+        </is>
+      </c>
+      <c r="G160" s="29" t="inlineStr">
+        <is>
+          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+        </is>
+      </c>
+      <c r="H160" s="28" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="I160" s="30" t="n"/>
+      <c r="J160" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A160,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B161" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C161" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D161" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E161" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F161" s="29" t="inlineStr">
+        <is>
+          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+        </is>
+      </c>
+      <c r="G161" s="29" t="inlineStr">
+        <is>
+          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+        </is>
+      </c>
+      <c r="H161" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I161" s="30" t="n"/>
+      <c r="J161" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A161,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B162" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C162" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D162" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E162" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F162" s="29" t="inlineStr">
+        <is>
+          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+        </is>
+      </c>
+      <c r="G162" s="29" t="inlineStr">
+        <is>
+          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+        </is>
+      </c>
+      <c r="H162" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I162" s="30" t="n"/>
+      <c r="J162" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A162,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J134"/>
-  <conditionalFormatting sqref="J5:J134">
+  <autoFilter ref="A4:J162"/>
+  <conditionalFormatting sqref="J5:J162">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -8382,7 +9698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8538,7 +9854,7 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>IT-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="B7" s="32">
@@ -8550,13 +9866,13 @@
         <v/>
       </c>
       <c r="D7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>0</v>
@@ -8566,7 +9882,7 @@
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>IT-02</t>
+          <t>ST-02-N1</t>
         </is>
       </c>
       <c r="B8" s="32">
@@ -8578,13 +9894,13 @@
         <v/>
       </c>
       <c r="D8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>0</v>
@@ -8594,7 +9910,7 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>IT-03</t>
+          <t>ST-02-N2</t>
         </is>
       </c>
       <c r="B9" s="32">
@@ -8606,13 +9922,13 @@
         <v/>
       </c>
       <c r="D9" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>0</v>
@@ -8622,7 +9938,7 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>IT-04</t>
+          <t>ST-02-N3</t>
         </is>
       </c>
       <c r="B10" s="32">
@@ -8634,13 +9950,13 @@
         <v/>
       </c>
       <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>0</v>
@@ -8650,7 +9966,7 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>IT-05</t>
+          <t>IT-01</t>
         </is>
       </c>
       <c r="B11" s="32">
@@ -8678,7 +9994,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>IT-06</t>
+          <t>IT-02</t>
         </is>
       </c>
       <c r="B12" s="32">
@@ -8706,7 +10022,7 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>IT-07</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="B13" s="32">
@@ -8718,7 +10034,7 @@
         <v/>
       </c>
       <c r="D13" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0</v>
@@ -8734,7 +10050,7 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>IT-08</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="B14" s="32">
@@ -8746,7 +10062,7 @@
         <v/>
       </c>
       <c r="D14" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0</v>
@@ -8762,7 +10078,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>IT-09</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="B15" s="32">
@@ -8790,7 +10106,7 @@
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>IT-10</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="B16" s="32">
@@ -8818,7 +10134,7 @@
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>IT-11</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="B17" s="32">
@@ -8830,13 +10146,13 @@
         <v/>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>0</v>
@@ -8846,7 +10162,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>IT-12</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="B18" s="32">
@@ -8858,7 +10174,7 @@
         <v/>
       </c>
       <c r="D18" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>0</v>
@@ -8874,7 +10190,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>IT-13</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="B19" s="32">
@@ -8886,13 +10202,13 @@
         <v/>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>0</v>
@@ -8902,7 +10218,7 @@
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>IT-14</t>
+          <t>IT-10</t>
         </is>
       </c>
       <c r="B20" s="32">
@@ -8914,13 +10230,13 @@
         <v/>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>0</v>
@@ -8930,7 +10246,7 @@
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>IT-15</t>
+          <t>IT-11</t>
         </is>
       </c>
       <c r="B21" s="32">
@@ -8948,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>0</v>
@@ -8958,7 +10274,7 @@
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>IT-16</t>
+          <t>IT-12</t>
         </is>
       </c>
       <c r="B22" s="32">
@@ -8970,13 +10286,13 @@
         <v/>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>0</v>
@@ -8986,7 +10302,7 @@
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>IT-17</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="B23" s="32">
@@ -9014,7 +10330,7 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>IT-18</t>
+          <t>IT-14</t>
         </is>
       </c>
       <c r="B24" s="32">
@@ -9042,7 +10358,7 @@
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>IT-19</t>
+          <t>IT-15</t>
         </is>
       </c>
       <c r="B25" s="32">
@@ -9060,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>0</v>
@@ -9070,7 +10386,7 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>IT-20</t>
+          <t>IT-16</t>
         </is>
       </c>
       <c r="B26" s="32">
@@ -9098,7 +10414,7 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>IT-21</t>
+          <t>IT-17</t>
         </is>
       </c>
       <c r="B27" s="32">
@@ -9116,7 +10432,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>0</v>
@@ -9126,7 +10442,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>IT-22</t>
+          <t>IT-18</t>
         </is>
       </c>
       <c r="B28" s="32">
@@ -9154,7 +10470,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>IT-23</t>
+          <t>IT-19</t>
         </is>
       </c>
       <c r="B29" s="32">
@@ -9182,7 +10498,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>IT-24</t>
+          <t>IT-20</t>
         </is>
       </c>
       <c r="B30" s="32">
@@ -9210,7 +10526,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>IT-25</t>
+          <t>IT-21</t>
         </is>
       </c>
       <c r="B31" s="32">
@@ -9228,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>0</v>
@@ -9238,7 +10554,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>IT-26</t>
+          <t>IT-22</t>
         </is>
       </c>
       <c r="B32" s="32">
@@ -9266,7 +10582,7 @@
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>IT-27</t>
+          <t>IT-23</t>
         </is>
       </c>
       <c r="B33" s="32">
@@ -9294,7 +10610,7 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>IT-28</t>
+          <t>IT-24</t>
         </is>
       </c>
       <c r="B34" s="32">
@@ -9322,7 +10638,7 @@
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>IT-29</t>
+          <t>IT-25</t>
         </is>
       </c>
       <c r="B35" s="32">
@@ -9350,7 +10666,7 @@
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>IT-30</t>
+          <t>IT-26</t>
         </is>
       </c>
       <c r="B36" s="32">
@@ -9378,7 +10694,7 @@
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>IT-31</t>
+          <t>IT-27</t>
         </is>
       </c>
       <c r="B37" s="32">
@@ -9406,7 +10722,7 @@
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>IT-32</t>
+          <t>IT-28</t>
         </is>
       </c>
       <c r="B38" s="32">
@@ -9434,7 +10750,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-29</t>
         </is>
       </c>
       <c r="B39" s="32">
@@ -9446,13 +10762,13 @@
         <v/>
       </c>
       <c r="D39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>0</v>
@@ -9462,7 +10778,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>IT-30</t>
         </is>
       </c>
       <c r="B40" s="32">
@@ -9474,13 +10790,13 @@
         <v/>
       </c>
       <c r="D40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G40" s="23" t="n">
         <v>0</v>
@@ -9490,7 +10806,7 @@
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>IT-31</t>
         </is>
       </c>
       <c r="B41" s="32">
@@ -9502,13 +10818,13 @@
         <v/>
       </c>
       <c r="D41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G41" s="23" t="n">
         <v>0</v>
@@ -9518,7 +10834,7 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>IT-32</t>
         </is>
       </c>
       <c r="B42" s="32">
@@ -9530,13 +10846,13 @@
         <v/>
       </c>
       <c r="D42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G42" s="23" t="n">
         <v>0</v>
@@ -9546,7 +10862,7 @@
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>IT-33</t>
         </is>
       </c>
       <c r="B43" s="32">
@@ -9558,13 +10874,13 @@
         <v/>
       </c>
       <c r="D43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>0</v>
@@ -9574,7 +10890,7 @@
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>IT-34</t>
         </is>
       </c>
       <c r="B44" s="32">
@@ -9586,13 +10902,13 @@
         <v/>
       </c>
       <c r="D44" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E44" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>0</v>
@@ -9602,7 +10918,7 @@
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>IT-35</t>
         </is>
       </c>
       <c r="B45" s="32">
@@ -9614,13 +10930,13 @@
         <v/>
       </c>
       <c r="D45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E45" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>0</v>
@@ -9630,7 +10946,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>IT-36</t>
         </is>
       </c>
       <c r="B46" s="32">
@@ -9642,13 +10958,13 @@
         <v/>
       </c>
       <c r="D46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G46" s="23" t="n">
         <v>0</v>
@@ -9658,7 +10974,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>IT-37</t>
         </is>
       </c>
       <c r="B47" s="32">
@@ -9670,13 +10986,13 @@
         <v/>
       </c>
       <c r="D47" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E47" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="23" t="n">
         <v>0</v>
@@ -9686,7 +11002,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>IT-38</t>
         </is>
       </c>
       <c r="B48" s="32">
@@ -9698,13 +11014,13 @@
         <v/>
       </c>
       <c r="D48" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E48" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="23" t="n">
         <v>0</v>
@@ -9714,7 +11030,7 @@
     <row r="49">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>IT-39</t>
         </is>
       </c>
       <c r="B49" s="32">
@@ -9726,13 +11042,13 @@
         <v/>
       </c>
       <c r="D49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G49" s="23" t="n">
         <v>0</v>
@@ -9742,7 +11058,7 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>IT-40</t>
         </is>
       </c>
       <c r="B50" s="32">
@@ -9754,13 +11070,13 @@
         <v/>
       </c>
       <c r="D50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G50" s="23" t="n">
         <v>0</v>
@@ -9770,7 +11086,7 @@
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B51" s="32">
@@ -9798,7 +11114,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B52" s="32">
@@ -9810,7 +11126,7 @@
         <v/>
       </c>
       <c r="D52" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52" s="23" t="n">
         <v>0</v>
@@ -9826,7 +11142,7 @@
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B53" s="32">
@@ -9838,7 +11154,7 @@
         <v/>
       </c>
       <c r="D53" s="23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E53" s="23" t="n">
         <v>0</v>
@@ -9854,7 +11170,7 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B54" s="32">
@@ -9866,7 +11182,7 @@
         <v/>
       </c>
       <c r="D54" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E54" s="23" t="n">
         <v>0</v>
@@ -9882,7 +11198,7 @@
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B55" s="32">
@@ -9894,7 +11210,7 @@
         <v/>
       </c>
       <c r="D55" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E55" s="23" t="n">
         <v>0</v>
@@ -9910,7 +11226,7 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B56" s="32">
@@ -9938,7 +11254,7 @@
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B57" s="32">
@@ -9966,7 +11282,7 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B58" s="32">
@@ -9994,7 +11310,7 @@
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B59" s="32">
@@ -10006,7 +11322,7 @@
         <v/>
       </c>
       <c r="D59" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="23" t="n">
         <v>0</v>
@@ -10022,7 +11338,7 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B60" s="32">
@@ -10034,7 +11350,7 @@
         <v/>
       </c>
       <c r="D60" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" s="23" t="n">
         <v>0</v>
@@ -10050,7 +11366,7 @@
     <row r="61">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B61" s="32">
@@ -10062,7 +11378,7 @@
         <v/>
       </c>
       <c r="D61" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E61" s="23" t="n">
         <v>0</v>
@@ -10078,7 +11394,7 @@
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B62" s="32">
@@ -10106,7 +11422,7 @@
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B63" s="32">
@@ -10118,13 +11434,13 @@
         <v/>
       </c>
       <c r="D63" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="23" t="n">
         <v>0</v>
@@ -10134,7 +11450,7 @@
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B64" s="32">
@@ -10146,13 +11462,13 @@
         <v/>
       </c>
       <c r="D64" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E64" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G64" s="23" t="n">
         <v>0</v>
@@ -10162,7 +11478,7 @@
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B65" s="32">
@@ -10174,13 +11490,13 @@
         <v/>
       </c>
       <c r="D65" s="23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E65" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G65" s="23" t="n">
         <v>0</v>
@@ -10190,7 +11506,7 @@
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B66" s="32">
@@ -10202,13 +11518,13 @@
         <v/>
       </c>
       <c r="D66" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E66" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="23" t="n">
         <v>0</v>
@@ -10218,7 +11534,7 @@
     <row r="67">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B67" s="32">
@@ -10230,13 +11546,13 @@
         <v/>
       </c>
       <c r="D67" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E67" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" s="23" t="n">
         <v>0</v>
@@ -10246,7 +11562,7 @@
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B68" s="32">
@@ -10258,13 +11574,13 @@
         <v/>
       </c>
       <c r="D68" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E68" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" s="23" t="n">
         <v>0</v>
@@ -10274,7 +11590,7 @@
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B69" s="32">
@@ -10286,13 +11602,13 @@
         <v/>
       </c>
       <c r="D69" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G69" s="23" t="n">
         <v>0</v>
@@ -10302,7 +11618,7 @@
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B70" s="32">
@@ -10314,23 +11630,23 @@
         <v/>
       </c>
       <c r="D70" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G70" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H70" s="22" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B71" s="32">
@@ -10342,13 +11658,13 @@
         <v/>
       </c>
       <c r="D71" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G71" s="23" t="n">
         <v>0</v>
@@ -10358,7 +11674,7 @@
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B72" s="32">
@@ -10370,13 +11686,13 @@
         <v/>
       </c>
       <c r="D72" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="23" t="n">
         <v>0</v>
@@ -10386,7 +11702,7 @@
     <row r="73">
       <c r="A73" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B73" s="32">
@@ -10398,13 +11714,13 @@
         <v/>
       </c>
       <c r="D73" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E73" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="23" t="n">
         <v>0</v>
@@ -10414,7 +11730,7 @@
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B74" s="32">
@@ -10426,13 +11742,13 @@
         <v/>
       </c>
       <c r="D74" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="23" t="n">
         <v>0</v>
@@ -10442,7 +11758,7 @@
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B75" s="32">
@@ -10470,7 +11786,7 @@
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B76" s="32">
@@ -10488,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>0</v>
@@ -10498,7 +11814,7 @@
     <row r="77">
       <c r="A77" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B77" s="32">
@@ -10516,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>0</v>
@@ -10526,7 +11842,7 @@
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B78" s="32">
@@ -10554,7 +11870,7 @@
     <row r="79">
       <c r="A79" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B79" s="32">
@@ -10572,7 +11888,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G79" s="23" t="n">
         <v>0</v>
@@ -10582,7 +11898,7 @@
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B80" s="32">
@@ -10600,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" s="23" t="n">
         <v>0</v>
@@ -10610,7 +11926,7 @@
     <row r="81">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B81" s="32">
@@ -10628,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" s="23" t="n">
         <v>0</v>
@@ -10638,7 +11954,7 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B82" s="32">
@@ -10656,17 +11972,17 @@
         <v>0</v>
       </c>
       <c r="F82" s="23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G82" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H82" s="22" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B83" s="32">
@@ -10684,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G83" s="23" t="n">
         <v>0</v>
@@ -10694,7 +12010,7 @@
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B84" s="32">
@@ -10722,7 +12038,7 @@
     <row r="85">
       <c r="A85" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B85" s="32">
@@ -10740,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="23" t="n">
         <v>0</v>
@@ -10750,7 +12066,7 @@
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B86" s="32">
@@ -10778,7 +12094,7 @@
     <row r="87">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B87" s="32">
@@ -10806,7 +12122,7 @@
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B88" s="32">
@@ -10834,7 +12150,7 @@
     <row r="89">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B89" s="32">
@@ -10852,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" s="23" t="n">
         <v>0</v>
@@ -10862,7 +12178,7 @@
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B90" s="32">
@@ -10890,7 +12206,7 @@
     <row r="91">
       <c r="A91" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B91" s="32">
@@ -10908,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G91" s="23" t="n">
         <v>0</v>
@@ -10918,7 +12234,7 @@
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B92" s="32">
@@ -10946,7 +12262,7 @@
     <row r="93">
       <c r="A93" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B93" s="32">
@@ -10974,7 +12290,7 @@
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B94" s="32">
@@ -11002,7 +12318,7 @@
     <row r="95">
       <c r="A95" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B95" s="32">
@@ -11030,7 +12346,7 @@
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B96" s="32">
@@ -11058,7 +12374,7 @@
     <row r="97">
       <c r="A97" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B97" s="32">
@@ -11086,7 +12402,7 @@
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B98" s="32">
@@ -11114,7 +12430,7 @@
     <row r="99">
       <c r="A99" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B99" s="32">
@@ -11142,7 +12458,7 @@
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B100" s="32">
@@ -11170,7 +12486,7 @@
     <row r="101">
       <c r="A101" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B101" s="32">
@@ -11188,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G101" s="23" t="n">
         <v>0</v>
@@ -11198,7 +12514,7 @@
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B102" s="32">
@@ -11226,7 +12542,7 @@
     <row r="103">
       <c r="A103" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B103" s="32">
@@ -11244,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="23" t="n">
         <v>0</v>
@@ -11254,7 +12570,7 @@
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B104" s="32">
@@ -11282,7 +12598,7 @@
     <row r="105">
       <c r="A105" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B105" s="32">
@@ -11310,7 +12626,7 @@
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B106" s="32">
@@ -11328,7 +12644,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G106" s="23" t="n">
         <v>0</v>
@@ -11338,7 +12654,7 @@
     <row r="107">
       <c r="A107" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B107" s="32">
@@ -11356,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G107" s="23" t="n">
         <v>0</v>
@@ -11366,7 +12682,7 @@
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B108" s="32">
@@ -11394,7 +12710,7 @@
     <row r="109">
       <c r="A109" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B109" s="32">
@@ -11412,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G109" s="23" t="n">
         <v>0</v>
@@ -11422,7 +12738,7 @@
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B110" s="32">
@@ -11450,7 +12766,7 @@
     <row r="111">
       <c r="A111" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B111" s="32">
@@ -11468,7 +12784,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G111" s="23" t="n">
         <v>0</v>
@@ -11478,7 +12794,7 @@
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B112" s="32">
@@ -11506,7 +12822,7 @@
     <row r="113">
       <c r="A113" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B113" s="32">
@@ -11524,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G113" s="23" t="n">
         <v>0</v>
@@ -11534,7 +12850,7 @@
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B114" s="32">
@@ -11562,7 +12878,7 @@
     <row r="115">
       <c r="A115" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B115" s="32">
@@ -11590,7 +12906,7 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B116" s="32">
@@ -11618,7 +12934,7 @@
     <row r="117">
       <c r="A117" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B117" s="32">
@@ -11646,7 +12962,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B118" s="32">
@@ -11674,7 +12990,7 @@
     <row r="119">
       <c r="A119" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B119" s="32">
@@ -11692,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G119" s="23" t="n">
         <v>0</v>
@@ -11702,7 +13018,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B120" s="32">
@@ -11720,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G120" s="23" t="n">
         <v>0</v>
@@ -11730,7 +13046,7 @@
     <row r="121">
       <c r="A121" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B121" s="32">
@@ -11748,7 +13064,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" s="23" t="n">
         <v>0</v>
@@ -11758,7 +13074,7 @@
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B122" s="32">
@@ -11786,7 +13102,7 @@
     <row r="123">
       <c r="A123" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B123" s="32">
@@ -11804,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G123" s="23" t="n">
         <v>0</v>
@@ -11814,7 +13130,7 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B124" s="32">
@@ -11842,7 +13158,7 @@
     <row r="125">
       <c r="A125" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B125" s="32">
@@ -11870,7 +13186,7 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B126" s="32">
@@ -11898,7 +13214,7 @@
     <row r="127">
       <c r="A127" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B127" s="32">
@@ -11926,7 +13242,7 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B128" s="32">
@@ -11954,7 +13270,7 @@
     <row r="129">
       <c r="A129" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B129" s="32">
@@ -11982,7 +13298,7 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B130" s="32">
@@ -12010,7 +13326,7 @@
     <row r="131">
       <c r="A131" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B131" s="32">
@@ -12038,7 +13354,7 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B132" s="32">
@@ -12066,7 +13382,7 @@
     <row r="133">
       <c r="A133" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B133" s="32">
@@ -12090,6 +13406,790 @@
         <v>0</v>
       </c>
       <c r="H133" s="22" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-03</t>
+        </is>
+      </c>
+      <c r="B134" s="32">
+        <f>IF(E134&gt;0,"FAIL",IF(F134&gt;0,"RED",IF(D134&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C134" s="23">
+        <f>SUM(D134:G134)</f>
+        <v/>
+      </c>
+      <c r="D134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="22" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-04</t>
+        </is>
+      </c>
+      <c r="B135" s="32">
+        <f>IF(E135&gt;0,"FAIL",IF(F135&gt;0,"RED",IF(D135&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C135" s="23">
+        <f>SUM(D135:G135)</f>
+        <v/>
+      </c>
+      <c r="D135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="22" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-05</t>
+        </is>
+      </c>
+      <c r="B136" s="32">
+        <f>IF(E136&gt;0,"FAIL",IF(F136&gt;0,"RED",IF(D136&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C136" s="23">
+        <f>SUM(D136:G136)</f>
+        <v/>
+      </c>
+      <c r="D136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="22" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-06</t>
+        </is>
+      </c>
+      <c r="B137" s="32">
+        <f>IF(E137&gt;0,"FAIL",IF(F137&gt;0,"RED",IF(D137&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C137" s="23">
+        <f>SUM(D137:G137)</f>
+        <v/>
+      </c>
+      <c r="D137" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="22" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-07</t>
+        </is>
+      </c>
+      <c r="B138" s="32">
+        <f>IF(E138&gt;0,"FAIL",IF(F138&gt;0,"RED",IF(D138&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C138" s="23">
+        <f>SUM(D138:G138)</f>
+        <v/>
+      </c>
+      <c r="D138" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="22" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-08</t>
+        </is>
+      </c>
+      <c r="B139" s="32">
+        <f>IF(E139&gt;0,"FAIL",IF(F139&gt;0,"RED",IF(D139&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C139" s="23">
+        <f>SUM(D139:G139)</f>
+        <v/>
+      </c>
+      <c r="D139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="22" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-09</t>
+        </is>
+      </c>
+      <c r="B140" s="32">
+        <f>IF(E140&gt;0,"FAIL",IF(F140&gt;0,"RED",IF(D140&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C140" s="23">
+        <f>SUM(D140:G140)</f>
+        <v/>
+      </c>
+      <c r="D140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="22" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-10</t>
+        </is>
+      </c>
+      <c r="B141" s="32">
+        <f>IF(E141&gt;0,"FAIL",IF(F141&gt;0,"RED",IF(D141&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C141" s="23">
+        <f>SUM(D141:G141)</f>
+        <v/>
+      </c>
+      <c r="D141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="22" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-11</t>
+        </is>
+      </c>
+      <c r="B142" s="32">
+        <f>IF(E142&gt;0,"FAIL",IF(F142&gt;0,"RED",IF(D142&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C142" s="23">
+        <f>SUM(D142:G142)</f>
+        <v/>
+      </c>
+      <c r="D142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="22" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-12</t>
+        </is>
+      </c>
+      <c r="B143" s="32">
+        <f>IF(E143&gt;0,"FAIL",IF(F143&gt;0,"RED",IF(D143&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C143" s="23">
+        <f>SUM(D143:G143)</f>
+        <v/>
+      </c>
+      <c r="D143" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="22" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-13</t>
+        </is>
+      </c>
+      <c r="B144" s="32">
+        <f>IF(E144&gt;0,"FAIL",IF(F144&gt;0,"RED",IF(D144&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C144" s="23">
+        <f>SUM(D144:G144)</f>
+        <v/>
+      </c>
+      <c r="D144" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="22" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-14</t>
+        </is>
+      </c>
+      <c r="B145" s="32">
+        <f>IF(E145&gt;0,"FAIL",IF(F145&gt;0,"RED",IF(D145&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C145" s="23">
+        <f>SUM(D145:G145)</f>
+        <v/>
+      </c>
+      <c r="D145" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="22" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-15</t>
+        </is>
+      </c>
+      <c r="B146" s="32">
+        <f>IF(E146&gt;0,"FAIL",IF(F146&gt;0,"RED",IF(D146&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C146" s="23">
+        <f>SUM(D146:G146)</f>
+        <v/>
+      </c>
+      <c r="D146" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="22" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-16</t>
+        </is>
+      </c>
+      <c r="B147" s="32">
+        <f>IF(E147&gt;0,"FAIL",IF(F147&gt;0,"RED",IF(D147&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C147" s="23">
+        <f>SUM(D147:G147)</f>
+        <v/>
+      </c>
+      <c r="D147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="22" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-17</t>
+        </is>
+      </c>
+      <c r="B148" s="32">
+        <f>IF(E148&gt;0,"FAIL",IF(F148&gt;0,"RED",IF(D148&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C148" s="23">
+        <f>SUM(D148:G148)</f>
+        <v/>
+      </c>
+      <c r="D148" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="22" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-18</t>
+        </is>
+      </c>
+      <c r="B149" s="32">
+        <f>IF(E149&gt;0,"FAIL",IF(F149&gt;0,"RED",IF(D149&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C149" s="23">
+        <f>SUM(D149:G149)</f>
+        <v/>
+      </c>
+      <c r="D149" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="22" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-19</t>
+        </is>
+      </c>
+      <c r="B150" s="32">
+        <f>IF(E150&gt;0,"FAIL",IF(F150&gt;0,"RED",IF(D150&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C150" s="23">
+        <f>SUM(D150:G150)</f>
+        <v/>
+      </c>
+      <c r="D150" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="22" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-20</t>
+        </is>
+      </c>
+      <c r="B151" s="32">
+        <f>IF(E151&gt;0,"FAIL",IF(F151&gt;0,"RED",IF(D151&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C151" s="23">
+        <f>SUM(D151:G151)</f>
+        <v/>
+      </c>
+      <c r="D151" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="22" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-21</t>
+        </is>
+      </c>
+      <c r="B152" s="32">
+        <f>IF(E152&gt;0,"FAIL",IF(F152&gt;0,"RED",IF(D152&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C152" s="23">
+        <f>SUM(D152:G152)</f>
+        <v/>
+      </c>
+      <c r="D152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="22" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-22</t>
+        </is>
+      </c>
+      <c r="B153" s="32">
+        <f>IF(E153&gt;0,"FAIL",IF(F153&gt;0,"RED",IF(D153&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C153" s="23">
+        <f>SUM(D153:G153)</f>
+        <v/>
+      </c>
+      <c r="D153" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="22" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-23</t>
+        </is>
+      </c>
+      <c r="B154" s="32">
+        <f>IF(E154&gt;0,"FAIL",IF(F154&gt;0,"RED",IF(D154&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C154" s="23">
+        <f>SUM(D154:G154)</f>
+        <v/>
+      </c>
+      <c r="D154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="22" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-24</t>
+        </is>
+      </c>
+      <c r="B155" s="32">
+        <f>IF(E155&gt;0,"FAIL",IF(F155&gt;0,"RED",IF(D155&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C155" s="23">
+        <f>SUM(D155:G155)</f>
+        <v/>
+      </c>
+      <c r="D155" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="22" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-01</t>
+        </is>
+      </c>
+      <c r="B156" s="32">
+        <f>IF(E156&gt;0,"FAIL",IF(F156&gt;0,"RED",IF(D156&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C156" s="23">
+        <f>SUM(D156:G156)</f>
+        <v/>
+      </c>
+      <c r="D156" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="22" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B157" s="32">
+        <f>IF(E157&gt;0,"FAIL",IF(F157&gt;0,"RED",IF(D157&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C157" s="23">
+        <f>SUM(D157:G157)</f>
+        <v/>
+      </c>
+      <c r="D157" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="22" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B158" s="32">
+        <f>IF(E158&gt;0,"FAIL",IF(F158&gt;0,"RED",IF(D158&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C158" s="23">
+        <f>SUM(D158:G158)</f>
+        <v/>
+      </c>
+      <c r="D158" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="22" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B159" s="32">
+        <f>IF(E159&gt;0,"FAIL",IF(F159&gt;0,"RED",IF(D159&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C159" s="23">
+        <f>SUM(D159:G159)</f>
+        <v/>
+      </c>
+      <c r="D159" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="22" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B160" s="32">
+        <f>IF(E160&gt;0,"FAIL",IF(F160&gt;0,"RED",IF(D160&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C160" s="23">
+        <f>SUM(D160:G160)</f>
+        <v/>
+      </c>
+      <c r="D160" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="22" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B161" s="32">
+        <f>IF(E161&gt;0,"FAIL",IF(F161&gt;0,"RED",IF(D161&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C161" s="23">
+        <f>SUM(D161:G161)</f>
+        <v/>
+      </c>
+      <c r="D161" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="22" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B600">
@@ -12120,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12333,6 +14433,48 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-03 02:43</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>feature/sc02-dashboard-tests</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>9bf4a2e</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>292</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="K7" s="36">
+        <f>IFERROR(E7/(E7+F7+G7),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$7</f>
+              <f>'실행이력'!$A$4:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$7</f>
+              <f>'실행이력'!$E$4:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$7</f>
+              <f>'실행이력'!$A$4:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$7</f>
+              <f>'실행이력'!$F$4:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$7</f>
+              <f>'실행이력'!$A$4:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$7</f>
+              <f>'실행이력'!$G$4:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -9866,13 +9866,13 @@
         <v/>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>0</v>
@@ -9894,13 +9894,13 @@
         <v/>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>0</v>
@@ -9922,13 +9922,13 @@
         <v/>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>0</v>
@@ -9950,13 +9950,13 @@
         <v/>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>0</v>
@@ -10874,13 +10874,13 @@
         <v/>
       </c>
       <c r="D43" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>0</v>
@@ -10902,13 +10902,13 @@
         <v/>
       </c>
       <c r="D44" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>0</v>
@@ -10930,13 +10930,13 @@
         <v/>
       </c>
       <c r="D45" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>0</v>
@@ -10958,13 +10958,13 @@
         <v/>
       </c>
       <c r="D46" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="23" t="n">
         <v>0</v>
@@ -10986,13 +10986,13 @@
         <v/>
       </c>
       <c r="D47" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="23" t="n">
         <v>0</v>
@@ -11014,13 +11014,13 @@
         <v/>
       </c>
       <c r="D48" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="23" t="n">
         <v>0</v>
@@ -11042,13 +11042,13 @@
         <v/>
       </c>
       <c r="D49" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="23" t="n">
         <v>0</v>
@@ -11070,13 +11070,13 @@
         <v/>
       </c>
       <c r="D50" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="23" t="n">
         <v>0</v>
@@ -12918,13 +12918,13 @@
         <v/>
       </c>
       <c r="D116" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="23" t="n">
         <v>0</v>
@@ -12946,13 +12946,13 @@
         <v/>
       </c>
       <c r="D117" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="23" t="n">
         <v>0</v>
@@ -12974,13 +12974,13 @@
         <v/>
       </c>
       <c r="D118" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="23" t="n">
         <v>0</v>
@@ -13002,13 +13002,13 @@
         <v/>
       </c>
       <c r="D119" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="23" t="n">
         <v>0</v>
@@ -13030,13 +13030,13 @@
         <v/>
       </c>
       <c r="D120" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E120" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G120" s="23" t="n">
         <v>0</v>
@@ -13058,13 +13058,13 @@
         <v/>
       </c>
       <c r="D121" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="23" t="n">
         <v>0</v>
@@ -13086,13 +13086,13 @@
         <v/>
       </c>
       <c r="D122" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F122" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="23" t="n">
         <v>0</v>
@@ -13114,13 +13114,13 @@
         <v/>
       </c>
       <c r="D123" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E123" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" s="23" t="n">
         <v>0</v>
@@ -13142,13 +13142,13 @@
         <v/>
       </c>
       <c r="D124" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="23" t="n">
         <v>0</v>
@@ -13170,13 +13170,13 @@
         <v/>
       </c>
       <c r="D125" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="23" t="n">
         <v>0</v>
@@ -13198,13 +13198,13 @@
         <v/>
       </c>
       <c r="D126" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="23" t="n">
         <v>0</v>
@@ -13226,13 +13226,13 @@
         <v/>
       </c>
       <c r="D127" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="23" t="n">
         <v>0</v>
@@ -13254,13 +13254,13 @@
         <v/>
       </c>
       <c r="D128" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="23" t="n">
         <v>0</v>
@@ -13282,13 +13282,13 @@
         <v/>
       </c>
       <c r="D129" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" s="23" t="n">
         <v>0</v>
@@ -13310,13 +13310,13 @@
         <v/>
       </c>
       <c r="D130" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="23" t="n">
         <v>0</v>
@@ -13338,13 +13338,13 @@
         <v/>
       </c>
       <c r="D131" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" s="23" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14475,6 +14475,48 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-03 02:46</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>feature/sc02-dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>ebf33d6</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>292</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" s="36">
+        <f>IFERROR(E8/(E8+F8+G8),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$8</f>
+              <f>'실행이력'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$8</f>
+              <f>'실행이력'!$E$4:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$8</f>
+              <f>'실행이력'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$8</f>
+              <f>'실행이력'!$F$4:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$8</f>
+              <f>'실행이력'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$8</f>
+              <f>'실행이력'!$G$4:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="D10" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="D44" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D45" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="D46" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E46" s="27" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D47" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E47" s="27" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D48" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E48" s="27" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="D49" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E49" s="27" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D50" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E50" s="27" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="D51" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E51" s="27" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D117" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E117" s="27" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="D118" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E118" s="27" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D119" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E119" s="27" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D120" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E120" s="27" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D121" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E121" s="27" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D122" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E122" s="27" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D123" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E123" s="27" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D124" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E124" s="27" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D125" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E125" s="27" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D126" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E126" s="27" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D127" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E127" s="27" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="D128" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E128" s="27" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D129" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E129" s="27" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D130" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E130" s="27" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="D131" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E131" s="27" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="D132" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E132" s="27" t="inlineStr">
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14517,6 +14517,48 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-03 02:50</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>fix/sc02-screen-mapping</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>bc987b1</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>294</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="K9" s="36">
+        <f>IFERROR(E9/(E9+F9+G9),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$9</f>
+              <f>'실행이력'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$9</f>
+              <f>'실행이력'!$E$4:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$9</f>
+              <f>'실행이력'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$9</f>
+              <f>'실행이력'!$F$4:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$9</f>
+              <f>'실행이력'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$9</f>
+              <f>'실행이력'!$G$4:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14559,6 +14559,48 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-03 02:57</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>fix/tracker-cache-bust</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>dd69cfb</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>294</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="K10" s="36">
+        <f>IFERROR(E10/(E10+F10+G10),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$10</f>
+              <f>'실행이력'!$A$4:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$10</f>
+              <f>'실행이력'!$E$4:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$10</f>
+              <f>'실행이력'!$A$4:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$10</f>
+              <f>'실행이력'!$F$4:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$10</f>
+              <f>'실행이력'!$A$4:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$10</f>
+              <f>'실행이력'!$G$4:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14601,6 +14601,48 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:11</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>feature/aws-deploy</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>f3f397a</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>308</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K11" s="36">
+        <f>IFERROR(E11/(E11+F11+G11),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$11</f>
+              <f>'실행이력'!$A$4:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$11</f>
+              <f>'실행이력'!$E$4:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$11</f>
+              <f>'실행이력'!$A$4:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$11</f>
+              <f>'실행이력'!$F$4:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$11</f>
+              <f>'실행이력'!$A$4:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$11</f>
+              <f>'실행이력'!$G$4:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14643,6 +14643,48 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:11</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>feature/https-budget</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>1859e63</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>311</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K12" s="36">
+        <f>IFERROR(E12/(E12+F12+G12),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$12</f>
+              <f>'실행이력'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$12</f>
+              <f>'실행이력'!$E$4:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$12</f>
+              <f>'실행이력'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$12</f>
+              <f>'실행이력'!$F$4:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$12</f>
+              <f>'실행이력'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$12</f>
+              <f>'실행이력'!$G$4:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14685,6 +14685,48 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:29</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>feature/service-url</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>4b3607e</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>311</v>
+      </c>
+      <c r="J13" s="35" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K13" s="36">
+        <f>IFERROR(E13/(E13+F13+G13),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$13</f>
+              <f>'실행이력'!$A$4:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$13</f>
+              <f>'실행이력'!$E$4:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$13</f>
+              <f>'실행이력'!$A$4:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$13</f>
+              <f>'실행이력'!$F$4:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$13</f>
+              <f>'실행이력'!$A$4:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$13</f>
+              <f>'실행이력'!$G$4:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14727,6 +14727,48 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:29</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>feature/case-detail</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>e1f086b</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>312</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="K14" s="36">
+        <f>IFERROR(E14/(E14+F14+G14),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$14</f>
+              <f>'실행이력'!$A$4:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$14</f>
+              <f>'실행이력'!$E$4:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$14</f>
+              <f>'실행이력'!$A$4:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$14</f>
+              <f>'실행이력'!$F$4:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$14</f>
+              <f>'실행이력'!$A$4:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$14</f>
+              <f>'실행이력'!$G$4:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14769,6 +14769,48 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:32</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>feature/case-detail-prerun</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>811f445</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>312</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="K15" s="36">
+        <f>IFERROR(E15/(E15+F15+G15),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$15</f>
+              <f>'실행이력'!$A$4:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$15</f>
+              <f>'실행이력'!$E$4:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$15</f>
+              <f>'실행이력'!$A$4:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$15</f>
+              <f>'실행이력'!$F$4:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$15</f>
+              <f>'실행이력'!$A$4:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$15</f>
+              <f>'실행이력'!$G$4:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14811,6 +14811,48 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:42</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>fix/detail-layout</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>d6dc555</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <v>312</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K16" s="36">
+        <f>IFERROR(E16/(E16+F16+G16),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$16</f>
+              <f>'실행이력'!$A$4:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$16</f>
+              <f>'실행이력'!$E$4:$E$17</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$16</f>
+              <f>'실행이력'!$A$4:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$16</f>
+              <f>'실행이력'!$F$4:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$16</f>
+              <f>'실행이력'!$A$4:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$16</f>
+              <f>'실행이력'!$G$4:$G$17</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14853,6 +14853,48 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:43</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>fix/demo-deploy-files</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>7d6b8d9</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <v>313</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K17" s="36">
+        <f>IFERROR(E17/(E17+F17+G17),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$17</f>
+              <f>'실행이력'!$A$4:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$17</f>
+              <f>'실행이력'!$E$4:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$17</f>
+              <f>'실행이력'!$A$4:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$17</f>
+              <f>'실행이력'!$F$4:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$17</f>
+              <f>'실행이력'!$A$4:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$17</f>
+              <f>'실행이력'!$G$4:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14895,6 +14895,48 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:47</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>fix/lazy-case-info</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>4df1cfb</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>314</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K18" s="36">
+        <f>IFERROR(E18/(E18+F18+G18),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$18</f>
+              <f>'실행이력'!$A$4:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$18</f>
+              <f>'실행이력'!$E$4:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$18</f>
+              <f>'실행이력'!$A$4:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$18</f>
+              <f>'실행이력'!$F$4:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$18</f>
+              <f>'실행이력'!$A$4:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$18</f>
+              <f>'실행이력'!$G$4:$G$19</f>
             </numRef>
           </val>
         </ser>
@@ -14220,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14937,6 +14937,48 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:58</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>feature/run-one-case</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>fb4a312</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>317</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="K19" s="36">
+        <f>IFERROR(E19/(E19+F19+G19),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="실행이력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$19</f>
+              <f>'실행이력'!$A$4:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$19</f>
+              <f>'실행이력'!$E$4:$E$20</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$19</f>
+              <f>'실행이력'!$A$4:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$19</f>
+              <f>'실행이력'!$F$4:$F$20</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$19</f>
+              <f>'실행이력'!$A$4:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$19</f>
+              <f>'실행이력'!$G$4:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -2146,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4446,12 +4446,12 @@
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-ATK-01</t>
         </is>
       </c>
       <c r="B52" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 원문과 다른 bcrypt 해시</t>
+          <t>최대 길이(64자) 비밀번호에서 마지막 글자만 다른 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
-          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
+          <t>다른 비밀번호는 로그인 실패(401), 원래 비밀번호는 성공</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
@@ -4493,12 +4493,12 @@
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>IT-ATK-02</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
+          <t>한글 비밀번호의 바이트 한도(글자 수는 64자 이내지만 바이트는 72 초과)</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
         <is>
-          <t>두 번 호출한 해시가 서로 다름</t>
+          <t>잘려서 같은 비밀번호로 취급되지 않는다(가입 거부 또는 로그인 401)</t>
         </is>
       </c>
       <c r="H53" s="28" t="inlineStr">
@@ -4540,12 +4540,12 @@
     <row r="54">
       <c r="A54" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>IT-ATK-03</t>
         </is>
       </c>
       <c r="B54" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C54" s="27" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 올바른 평문</t>
+          <t>NUL 문자(\x00)가 든 비밀번호로 가입/로그인</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>서버 오류(500) 없이 가입 400, 로그인 401</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>IT-ATK-04</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
@@ -4607,17 +4607,17 @@
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 잘못된 평문</t>
+          <t>유니코드 숫자(아라비아-인도 숫자 등)만으로 '숫자 1자 이상' 규칙 통과 시도</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>ASCII 숫자가 없으면 400</t>
         </is>
       </c>
       <c r="H55" s="28" t="inlineStr">
@@ -4634,12 +4634,12 @@
     <row r="56">
       <c r="A56" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>IT-ATK-05</t>
         </is>
       </c>
       <c r="B56" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 대소문자 구분</t>
+          <t>아이디 변형 입력: 줄바꿈·공백·전각 문자·제로폭 문자·길이 초과/미달</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>대소문자만 다른 평문은 False</t>
+          <t>모두 400, 사용자 생성 없음</t>
         </is>
       </c>
       <c r="H56" s="28" t="inlineStr">
@@ -4681,12 +4681,12 @@
     <row r="57">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>IT-ATK-06</t>
         </is>
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="E57" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
+          <t>기관 코드에 비정상적으로 긴 문자열(1만 자)과 제어 문자</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>예외 없이 False</t>
+          <t>설계서 VARCHAR(50) 한도를 넘으면 400, 사용자 생성 없음</t>
         </is>
       </c>
       <c r="H57" s="28" t="inlineStr">
@@ -4728,12 +4728,12 @@
     <row r="58">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>IT-ATK-07</t>
         </is>
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
@@ -4748,17 +4748,17 @@
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
+          <t>SQL 인젝션 문자열을 아이디/비밀번호에 입력</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>해시 생성 후 verify 가 True</t>
+          <t>가입 400, 로그인 401, users 테이블 변화 없음</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="59">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>IT-ATK-08</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
@@ -4795,17 +4795,17 @@
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자 가입</t>
+          <t>필드 타입 혼동(문자열 자리에 배열·객체·숫자·null)</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
+          <t>서버 오류 없이 가입 400 / 로그인 401</t>
         </is>
       </c>
       <c r="H59" s="28" t="inlineStr">
@@ -4822,12 +4822,12 @@
     <row r="60">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>IT-ATK-09</t>
         </is>
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
+          <t>깊게 중첩된 JSON 본문(3만 단계, 크기 제한 이내)</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>user_type·org_code 가 그대로 저장</t>
+          <t>서버 오류(500) 없이 400</t>
         </is>
       </c>
       <c r="H60" s="28" t="inlineStr">
@@ -4869,12 +4869,12 @@
     <row r="61">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>IT-ATK-10</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="F61" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관인데 org_code 누락</t>
+          <t>JSON이 아닌 요청(form, 빈 본문, 배열, 문자열)</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 사용자 미생성</t>
+          <t>모두 400 JSON 오류 형식</t>
         </is>
       </c>
       <c r="H61" s="28" t="inlineStr">
@@ -4916,12 +4916,12 @@
     <row r="62">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>IT-ATK-11</t>
         </is>
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
+          <t>2MB 크기의 요청 본문</t>
         </is>
       </c>
       <c r="G62" s="29" t="inlineStr">
         <is>
-          <t>org_code 는 None</t>
+          <t>본문 크기 제한으로 413 거부</t>
         </is>
       </c>
       <c r="H62" s="28" t="inlineStr">
@@ -4963,12 +4963,12 @@
     <row r="63">
       <c r="A63" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>IT-ATK-12</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
@@ -4983,17 +4983,17 @@
       </c>
       <c r="E63" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>signup: 중복 username</t>
+          <t>같은 계정에 비밀번호를 연속으로 틀려 입력(무차별 대입)</t>
         </is>
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
+          <t>일정 횟수 뒤 429 등으로 제한되고, 제한 중에는 올바른 비밀번호도 거부</t>
         </is>
       </c>
       <c r="H63" s="28" t="inlineStr">
@@ -5010,12 +5010,12 @@
     <row r="64">
       <c r="A64" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>IT-ATK-13</t>
         </is>
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
+          <t>로그아웃 전에 훔친 세션 쿠키를 로그아웃 후 재사용</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>두 계정 모두 생성</t>
+          <t>로그아웃한 세션은 서버에서 무효 → 401</t>
         </is>
       </c>
       <c r="H64" s="28" t="inlineStr">
@@ -5057,12 +5057,12 @@
     <row r="65">
       <c r="A65" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>IT-ATK-14</t>
         </is>
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
@@ -5077,17 +5077,17 @@
       </c>
       <c r="E65" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>signup: username 길이 경계 3/4/20/21자</t>
+          <t>기본 비밀키(dev-secret-change-me)로 세션 쿠키 위조</t>
         </is>
       </c>
       <c r="G65" s="29" t="inlineStr">
         <is>
-          <t>4~20자만 허용, 나머지 ValidationError</t>
+          <t>운영 구성에서 기본 키로는 서버가 뜨지 않거나, 위조 쿠키는 거부(401)</t>
         </is>
       </c>
       <c r="H65" s="28" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="66">
       <c r="A66" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>IT-ATK-15</t>
         </is>
       </c>
       <c r="B66" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C66" s="27" t="inlineStr">
@@ -5124,17 +5124,17 @@
       </c>
       <c r="E66" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F66" s="29" t="inlineStr">
         <is>
-          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
+          <t>응답 보안 헤더(nosniff, 프레임 삽입 차단)</t>
         </is>
       </c>
       <c r="G66" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>X-Content-Type-Options: nosniff, X-Frame-Options 또는 CSP frame-ancestors</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
@@ -5151,12 +5151,12 @@
     <row r="67">
       <c r="A67" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>IT-ATK-16</t>
         </is>
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="E67" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
+          <t>세션 쿠키 속성: HttpOnly·SameSite·Secure</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>8~64자만 허용</t>
+          <t>운영 설정에서 세 속성이 모두 켜짐</t>
         </is>
       </c>
       <c r="H67" s="28" t="inlineStr">
@@ -5198,12 +5198,12 @@
     <row r="68">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>IT-ATK-17</t>
         </is>
       </c>
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C68" s="27" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="E68" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
+          <t>로그인 실패 응답의 계정 존재 여부 은닉</t>
         </is>
       </c>
       <c r="G68" s="29" t="inlineStr">
         <is>
-          <t>숫자만/영문만/공백만 → ValidationError</t>
+          <t>없는 아이디와 틀린 비밀번호의 응답(상태·본문)이 동일</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
@@ -5245,37 +5245,37 @@
     <row r="69">
       <c r="A69" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>IT-ATK-18</t>
         </is>
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E69" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>signup: 허용되지 않는 user_type</t>
+          <t>대시보드 요청에 user_id/scope 쿼리를 붙여 타인·전체 범위 요청</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>쿼리는 무시되고 로그인 사용자 본인 범위만 반환</t>
         </is>
       </c>
       <c r="H69" s="28" t="inlineStr">
@@ -5292,37 +5292,37 @@
     <row r="70">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>IT-ATK-19</t>
         </is>
       </c>
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E70" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
+          <t>대시보드 접근에 변조된 세션(존재하지 않는 user_id)</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>예외 후 users 0건</t>
+          <t>401 이고 세션이 정리됨</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
@@ -5339,12 +5339,12 @@
     <row r="71">
       <c r="A71" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>IT-ATK-20</t>
         </is>
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
@@ -5359,17 +5359,17 @@
       </c>
       <c r="E71" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F71" s="29" t="inlineStr">
         <is>
-          <t>login: 올바른 자격 증명</t>
+          <t>같은 아이디로 12개 요청을 동시에 가입</t>
         </is>
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>해당 User 반환</t>
+          <t>정확히 1건 201, 나머지 409, 서버 오류(500) 없음, users 1건</t>
         </is>
       </c>
       <c r="H71" s="28" t="inlineStr">
@@ -5386,7 +5386,7 @@
     <row r="72">
       <c r="A72" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-ATK-01</t>
         </is>
       </c>
       <c r="B72" s="27" t="inlineStr">
@@ -5406,17 +5406,17 @@
       </c>
       <c r="E72" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>login: 비밀번호 불일치</t>
+          <t>LoginThrottle: 5회 실패 전까지는 막지 않고 5회째부터 차단</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError</t>
+          <t>4회 실패 후 차단 아님, 5회 후 차단</t>
         </is>
       </c>
       <c r="H72" s="28" t="inlineStr">
@@ -5433,7 +5433,7 @@
     <row r="73">
       <c r="A73" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-ATK-02</t>
         </is>
       </c>
       <c r="B73" s="27" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="E73" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
+          <t>LoginThrottle: 시간이 지나면 풀리고, 성공하면 초기화되며, 아이디는 대소문자 무관/서로 독립</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
+          <t>15분 경과 후 해제, reset 후 해제, ALICE01 도 같은 계정으로 계산, 다른 아이디는 영향 없음</t>
         </is>
       </c>
       <c r="H73" s="28" t="inlineStr">
@@ -5480,7 +5480,7 @@
     <row r="74">
       <c r="A74" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-ATK-03</t>
         </is>
       </c>
       <c r="B74" s="27" t="inlineStr">
@@ -5500,17 +5500,17 @@
       </c>
       <c r="E74" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>login: 빈 입력/인젝션 문자열</t>
+          <t>LoginThrottle: 서로 다른 아이디를 대량으로 시도해도 기억하는 개수가 상한을 넘지 않음</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError (예외 유형 일관)</t>
+          <t>max_keys 이하로 유지</t>
         </is>
       </c>
       <c r="H74" s="28" t="inlineStr">
@@ -5527,7 +5527,7 @@
     <row r="75">
       <c r="A75" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B75" s="27" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>get_user: 존재하는 id / 없는 id</t>
+          <t>hash_password: 원문과 다른 bcrypt 해시</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>존재하면 User, 없으면 NotFoundError</t>
+          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
         </is>
       </c>
       <c r="H75" s="28" t="inlineStr">
@@ -5574,7 +5574,7 @@
     <row r="76">
       <c r="A76" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B76" s="27" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="C76" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E76" s="27" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
-          <t>create_application: 유효한 알고리즘</t>
+          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
         </is>
       </c>
       <c r="G76" s="29" t="inlineStr">
         <is>
-          <t>status='submitted', submitted_at 설정, 본인 소유</t>
+          <t>두 번 호출한 해시가 서로 다름</t>
         </is>
       </c>
       <c r="H76" s="28" t="inlineStr">
@@ -5621,7 +5621,7 @@
     <row r="77">
       <c r="A77" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B77" s="27" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D77" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E77" s="27" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="F77" s="29" t="inlineStr">
         <is>
-          <t>create_application: 허용 알고리즘 전체</t>
+          <t>verify_password: 올바른 평문</t>
         </is>
       </c>
       <c r="G77" s="29" t="inlineStr">
         <is>
-          <t>ALGORITHMS 의 모든 값 신청 가능</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H77" s="28" t="inlineStr">
@@ -5668,7 +5668,7 @@
     <row r="78">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E78" s="27" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>create_application: 빈 값/미허용 알고리즘</t>
+          <t>verify_password: 잘못된 평문</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 레코드 미생성</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H78" s="28" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="79">
       <c r="A79" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
@@ -5725,27 +5725,27 @@
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D79" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E79" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F79" s="29" t="inlineStr">
         <is>
-          <t>create_application: 없는 사용자</t>
+          <t>verify_password: 대소문자 구분</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>대소문자만 다른 평문은 False</t>
         </is>
       </c>
       <c r="H79" s="28" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="80">
       <c r="A80" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B80" s="27" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="C80" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E80" s="27" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="F80" s="29" t="inlineStr">
         <is>
-          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
+          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
         </is>
       </c>
       <c r="G80" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
+          <t>예외 없이 False</t>
         </is>
       </c>
       <c r="H80" s="28" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="81">
       <c r="A81" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D81" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E81" s="27" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="F81" s="29" t="inlineStr">
         <is>
-          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
+          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
         </is>
       </c>
       <c r="G81" s="29" t="inlineStr">
         <is>
-          <t>허용</t>
+          <t>해시 생성 후 verify 가 True</t>
         </is>
       </c>
       <c r="H81" s="28" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="82">
       <c r="A82" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E82" s="27" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용 전이 3종</t>
+          <t>signup: 개인 사용자 가입</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
+          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
         </is>
       </c>
       <c r="H82" s="28" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="83">
       <c r="A83" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
@@ -5913,27 +5913,27 @@
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D83" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E83" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
+          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 상태 불변</t>
+          <t>user_type·org_code 가 그대로 저장</t>
         </is>
       </c>
       <c r="H83" s="28" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="84">
       <c r="A84" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E84" s="27" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>update_status: 존재하지 않는 상태값</t>
+          <t>signup: 기업/기관인데 org_code 누락</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>ValidationError, 사용자 미생성</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
@@ -5997,7 +5997,7 @@
     <row r="85">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D85" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="F85" s="29" t="inlineStr">
         <is>
-          <t>update_status: 전이 시 updated_at 갱신</t>
+          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
         </is>
       </c>
       <c r="G85" s="29" t="inlineStr">
         <is>
-          <t>updated_at 이 이전보다 이후</t>
+          <t>org_code 는 None</t>
         </is>
       </c>
       <c r="H85" s="28" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="86">
       <c r="A86" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
@@ -6054,27 +6054,27 @@
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E86" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
+          <t>signup: 중복 username</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError, 상태 불변</t>
+          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
         </is>
       </c>
       <c r="H86" s="28" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="87">
       <c r="A87" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
@@ -6101,27 +6101,27 @@
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E87" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
-          <t>update_status: 없는 신청/없는 사용자</t>
+          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
         </is>
       </c>
       <c r="G87" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>두 계정 모두 생성</t>
         </is>
       </c>
       <c r="H87" s="28" t="inlineStr">
@@ -6138,7 +6138,7 @@
     <row r="88">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
@@ -6148,27 +6148,27 @@
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E88" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 본인 신청만, 최신순</t>
+          <t>signup: username 길이 경계 3/4/20/21자</t>
         </is>
       </c>
       <c r="G88" s="29" t="inlineStr">
         <is>
-          <t>타인 신청 제외, submitted_at 내림차순</t>
+          <t>4~20자만 허용, 나머지 ValidationError</t>
         </is>
       </c>
       <c r="H88" s="28" t="inlineStr">
@@ -6185,7 +6185,7 @@
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
@@ -6195,27 +6195,27 @@
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 상태 필터</t>
+          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>해당 상태만 반환, total 도 필터 기준</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H89" s="28" t="inlineStr">
@@ -6232,7 +6232,7 @@
     <row r="90">
       <c r="A90" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
@@ -6242,27 +6242,27 @@
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E90" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F90" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 잘못된 상태 필터</t>
+          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
         </is>
       </c>
       <c r="G90" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>8~64자만 허용</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
@@ -6279,7 +6279,7 @@
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
@@ -6289,27 +6289,27 @@
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F91" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
+          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
         <is>
-          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
+          <t>숫자만/영문만/공백만 → ValidationError</t>
         </is>
       </c>
       <c r="H91" s="28" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="92">
       <c r="A92" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B92" s="27" t="inlineStr">
@@ -6336,27 +6336,27 @@
       </c>
       <c r="C92" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E92" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>list_applications: page/per_page 경계값</t>
+          <t>signup: 허용되지 않는 user_type</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
         <is>
-          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H92" s="28" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
@@ -6383,27 +6383,27 @@
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D93" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 신청이 없으면 빈 목록</t>
+          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>items=[], total=0</t>
+          <t>예외 후 users 0건</t>
         </is>
       </c>
       <c r="H93" s="28" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="94">
       <c r="A94" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>get_application: 본인 / 타인 / 없는 id</t>
+          <t>login: 올바른 자격 증명</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>해당 User 반환</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
@@ -6477,27 +6477,27 @@
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D95" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>get_application: institution 은 모든 신청 조회 가능</t>
+          <t>login: 비밀번호 불일치</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>타인 신청도 반환</t>
+          <t>AuthenticationError</t>
         </is>
       </c>
       <c r="H95" s="28" t="inlineStr">
@@ -6514,7 +6514,7 @@
     <row r="96">
       <c r="A96" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
@@ -6524,32 +6524,32 @@
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: SHA-256 hex</t>
+          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
         </is>
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
+          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I96" s="30" t="n"/>
@@ -6561,7 +6561,7 @@
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
@@ -6571,32 +6571,32 @@
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D97" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E97" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
+          <t>login: 빈 입력/인젝션 문자열</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
+          <t>AuthenticationError (예외 유형 일관)</t>
         </is>
       </c>
       <c r="H97" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I97" s="30" t="n"/>
@@ -6608,7 +6608,7 @@
     <row r="98">
       <c r="A98" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C98" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E98" s="27" t="inlineStr">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 동일 해시</t>
+          <t>get_user: 존재하는 id / 없는 id</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
         <is>
-          <t>'normal'</t>
+          <t>존재하면 User, 없으면 NotFoundError</t>
         </is>
       </c>
       <c r="H98" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I98" s="30" t="n"/>
@@ -6655,7 +6655,7 @@
     <row r="99">
       <c r="A99" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
@@ -6665,32 +6665,32 @@
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D99" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E99" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 상이한 해시</t>
+          <t>create_application: 유효한 알고리즘</t>
         </is>
       </c>
       <c r="G99" s="29" t="inlineStr">
         <is>
-          <t>'suspected'</t>
+          <t>status='submitted', submitted_at 설정, 본인 소유</t>
         </is>
       </c>
       <c r="H99" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I99" s="30" t="n"/>
@@ -6702,7 +6702,7 @@
     <row r="100">
       <c r="A100" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
@@ -6712,32 +6712,32 @@
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E100" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 대소문자만 다른 hex</t>
+          <t>create_application: 허용 알고리즘 전체</t>
         </is>
       </c>
       <c r="G100" s="29" t="inlineStr">
         <is>
-          <t>동일 값으로 보고 'normal'</t>
+          <t>ALGORITHMS 의 모든 값 신청 가능</t>
         </is>
       </c>
       <c r="H100" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I100" s="30" t="n"/>
@@ -6749,7 +6749,7 @@
     <row r="101">
       <c r="A101" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
@@ -6759,32 +6759,32 @@
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D101" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E101" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F101" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인된 신청에 발급</t>
+          <t>create_application: 빈 값/미허용 알고리즘</t>
         </is>
       </c>
       <c r="G101" s="29" t="inlineStr">
         <is>
-          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
+          <t>ValidationError, 레코드 미생성</t>
         </is>
       </c>
       <c r="H101" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I101" s="30" t="n"/>
@@ -6796,7 +6796,7 @@
     <row r="102">
       <c r="A102" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E102" s="27" t="inlineStr">
@@ -6821,17 +6821,17 @@
       </c>
       <c r="F102" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인 이전/반려 상태</t>
+          <t>create_application: 없는 사용자</t>
         </is>
       </c>
       <c r="G102" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 검증서 미생성</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I102" s="30" t="n"/>
@@ -6843,7 +6843,7 @@
     <row r="103">
       <c r="A103" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D103" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E103" s="27" t="inlineStr">
@@ -6868,17 +6868,17 @@
       </c>
       <c r="F103" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 신청당 1건(중복 발급)</t>
+          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
         </is>
       </c>
       <c r="G103" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError</t>
+          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
         </is>
       </c>
       <c r="H103" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I103" s="30" t="n"/>
@@ -6890,7 +6890,7 @@
     <row r="104">
       <c r="A104" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
@@ -6900,32 +6900,32 @@
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E104" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F104" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: institution 이 아니면 발급 불가</t>
+          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
         </is>
       </c>
       <c r="G104" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError</t>
+          <t>허용</t>
         </is>
       </c>
       <c r="H104" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I104" s="30" t="n"/>
@@ -6937,7 +6937,7 @@
     <row r="105">
       <c r="A105" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B105" s="27" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D105" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E105" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
+          <t>update_status: 허용 전이 3종</t>
         </is>
       </c>
       <c r="G105" s="29" t="inlineStr">
         <is>
-          <t>ValidationError / ValidationError / NotFoundError</t>
+          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
         </is>
       </c>
       <c r="H105" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I105" s="30" t="n"/>
@@ -6984,7 +6984,7 @@
     <row r="106">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
@@ -6994,32 +6994,32 @@
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E106" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F106" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: KCMVP 유형도 발급</t>
+          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
         </is>
       </c>
       <c r="G106" s="29" t="inlineStr">
         <is>
-          <t>cert_type='KCMVP'</t>
+          <t>InvalidTransitionError, 상태 불변</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I106" s="30" t="n"/>
@@ -7031,7 +7031,7 @@
     <row r="107">
       <c r="A107" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D107" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E107" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
+          <t>update_status: 존재하지 않는 상태값</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>타인 검증서 제외, issued_at 내림차순</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H107" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I107" s="30" t="n"/>
@@ -7078,7 +7078,7 @@
     <row r="108">
       <c r="A108" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B108" s="27" t="inlineStr">
@@ -7088,12 +7088,12 @@
       </c>
       <c r="C108" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E108" s="27" t="inlineStr">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="F108" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
+          <t>update_status: 전이 시 updated_at 갱신</t>
         </is>
       </c>
       <c r="G108" s="29" t="inlineStr">
         <is>
-          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
+          <t>updated_at 이 이전보다 이후</t>
         </is>
       </c>
       <c r="H108" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I108" s="30" t="n"/>
@@ -7125,7 +7125,7 @@
     <row r="109">
       <c r="A109" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B109" s="27" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D109" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>get_certificate: 본인 / 타인 / 없는 id</t>
+          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>PermissionDeniedError, 상태 불변</t>
         </is>
       </c>
       <c r="H109" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I109" s="30" t="n"/>
@@ -7172,7 +7172,7 @@
     <row r="110">
       <c r="A110" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B110" s="27" t="inlineStr">
@@ -7182,32 +7182,32 @@
       </c>
       <c r="C110" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E110" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 무결 → normal</t>
+          <t>update_status: 없는 신청/없는 사용자</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>tamper_status='normal'</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I110" s="30" t="n"/>
@@ -7219,7 +7219,7 @@
     <row r="111">
       <c r="A111" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B111" s="27" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D111" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E111" s="27" t="inlineStr">
@@ -7244,17 +7244,17 @@
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
+          <t>list_applications: 본인 신청만, 최신순</t>
         </is>
       </c>
       <c r="G111" s="29" t="inlineStr">
         <is>
-          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
+          <t>타인 신청 제외, submitted_at 내림차순</t>
         </is>
       </c>
       <c r="H111" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I111" s="30" t="n"/>
@@ -7266,7 +7266,7 @@
     <row r="112">
       <c r="A112" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B112" s="27" t="inlineStr">
@@ -7276,32 +7276,32 @@
       </c>
       <c r="C112" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
+          <t>list_applications: 상태 필터</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>'suspected' (예외 아님)</t>
+          <t>해당 상태만 반환, total 도 필터 기준</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I112" s="30" t="n"/>
@@ -7313,7 +7313,7 @@
     <row r="113">
       <c r="A113" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B113" s="27" t="inlineStr">
@@ -7323,32 +7323,32 @@
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D113" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 원복 후 재검증 시 normal</t>
+          <t>list_applications: 잘못된 상태 필터</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>변조 → suspected, 원복 → normal</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H113" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I113" s="30" t="n"/>
@@ -7360,7 +7360,7 @@
     <row r="114">
       <c r="A114" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B114" s="27" t="inlineStr">
@@ -7370,32 +7370,32 @@
       </c>
       <c r="C114" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F114" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 존재하지 않는 cert_id</t>
+          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
         </is>
       </c>
       <c r="G114" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I114" s="30" t="n"/>
@@ -7407,7 +7407,7 @@
     <row r="115">
       <c r="A115" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B115" s="27" t="inlineStr">
@@ -7417,32 +7417,32 @@
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D115" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
+          <t>list_applications: page/per_page 경계값</t>
         </is>
       </c>
       <c r="G115" s="29" t="inlineStr">
         <is>
-          <t>검증 후에도 integrity_hash 불변</t>
+          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
         </is>
       </c>
       <c r="H115" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I115" s="30" t="n"/>
@@ -7454,7 +7454,7 @@
     <row r="116">
       <c r="A116" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B116" s="27" t="inlineStr">
@@ -7464,32 +7464,32 @@
       </c>
       <c r="C116" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D116" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F116" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
+          <t>list_applications: 신청이 없으면 빈 목록</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
-          <t>파일이 없으면 suspected 유지</t>
+          <t>items=[], total=0</t>
         </is>
       </c>
       <c r="H116" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I116" s="30" t="n"/>
@@ -7501,7 +7501,7 @@
     <row r="117">
       <c r="A117" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-01</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B117" s="27" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D117" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E117" s="27" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="F117" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 본인 신청만 집계</t>
+          <t>get_application: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H117" s="28" t="inlineStr">
@@ -7548,7 +7548,7 @@
     <row r="118">
       <c r="A118" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-02</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B118" s="27" t="inlineStr">
@@ -7563,22 +7563,22 @@
       </c>
       <c r="D118" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E118" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F118" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
+          <t>get_application: institution 은 모든 신청 조회 가능</t>
         </is>
       </c>
       <c r="G118" s="29" t="inlineStr">
         <is>
-          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
+          <t>타인 신청도 반환</t>
         </is>
       </c>
       <c r="H118" s="28" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="119">
       <c r="A119" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-03</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B119" s="27" t="inlineStr">
@@ -7605,32 +7605,32 @@
       </c>
       <c r="C119" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D119" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E119" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F119" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
+          <t>compute_hash: SHA-256 hex</t>
         </is>
       </c>
       <c r="G119" s="29" t="inlineStr">
         <is>
-          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
+          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
         </is>
       </c>
       <c r="H119" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I119" s="30" t="n"/>
@@ -7642,7 +7642,7 @@
     <row r="120">
       <c r="A120" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-04</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B120" s="27" t="inlineStr">
@@ -7652,32 +7652,32 @@
       </c>
       <c r="C120" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D120" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E120" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F120" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
+          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
         </is>
       </c>
       <c r="G120" s="29" t="inlineStr">
         <is>
-          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
+          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
         </is>
       </c>
       <c r="H120" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I120" s="30" t="n"/>
@@ -7689,7 +7689,7 @@
     <row r="121">
       <c r="A121" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-05</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B121" s="27" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="C121" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D121" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E121" s="27" t="inlineStr">
@@ -7714,17 +7714,17 @@
       </c>
       <c r="F121" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 상태 라벨 매핑</t>
+          <t>compare_hash: 동일 해시</t>
         </is>
       </c>
       <c r="G121" s="29" t="inlineStr">
         <is>
-          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
+          <t>'normal'</t>
         </is>
       </c>
       <c r="H121" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I121" s="30" t="n"/>
@@ -7736,7 +7736,7 @@
     <row r="122">
       <c r="A122" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-06</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B122" s="27" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="C122" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D122" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E122" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F122" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 최근 7일 신규 신청 경계</t>
+          <t>compare_hash: 상이한 해시</t>
         </is>
       </c>
       <c r="G122" s="29" t="inlineStr">
         <is>
-          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
+          <t>'suspected'</t>
         </is>
       </c>
       <c r="H122" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I122" s="30" t="n"/>
@@ -7783,7 +7783,7 @@
     <row r="123">
       <c r="A123" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-07</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B123" s="27" t="inlineStr">
@@ -7793,27 +7793,27 @@
       </c>
       <c r="C123" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D123" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E123" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F123" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
+          <t>compare_hash: 대소문자만 다른 hex</t>
         </is>
       </c>
       <c r="G123" s="29" t="inlineStr">
         <is>
-          <t>total·suspected 가 본인 건만 반영</t>
+          <t>동일 값으로 보고 'normal'</t>
         </is>
       </c>
       <c r="H123" s="28" t="inlineStr">
@@ -7830,7 +7830,7 @@
     <row r="124">
       <c r="A124" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-08</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B124" s="27" t="inlineStr">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="C124" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D124" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E124" s="27" t="inlineStr">
@@ -7855,17 +7855,17 @@
       </c>
       <c r="F124" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 가명·익명 처리 상태</t>
+          <t>issue_certificate: 승인된 신청에 발급</t>
         </is>
       </c>
       <c r="G124" s="29" t="inlineStr">
         <is>
-          <t>처리 전 processed=False, 처리 후 level 반영</t>
+          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
         </is>
       </c>
       <c r="H124" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I124" s="30" t="n"/>
@@ -7877,7 +7877,7 @@
     <row r="125">
       <c r="A125" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-09</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B125" s="27" t="inlineStr">
@@ -7887,27 +7887,27 @@
       </c>
       <c r="C125" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D125" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E125" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F125" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 위변조 의심 알림이 최우선</t>
+          <t>issue_certificate: 승인 이전/반려 상태</t>
         </is>
       </c>
       <c r="G125" s="29" t="inlineStr">
         <is>
-          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
+          <t>InvalidTransitionError, 검증서 미생성</t>
         </is>
       </c>
       <c r="H125" s="28" t="inlineStr">
@@ -7924,7 +7924,7 @@
     <row r="126">
       <c r="A126" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-10</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B126" s="27" t="inlineStr">
@@ -7934,32 +7934,32 @@
       </c>
       <c r="C126" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D126" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E126" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F126" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 신청 진행/결과 알림 문구</t>
+          <t>issue_certificate: 신청당 1건(중복 발급)</t>
         </is>
       </c>
       <c r="G126" s="29" t="inlineStr">
         <is>
-          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
+          <t>DuplicateApplicationError</t>
         </is>
       </c>
       <c r="H126" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I126" s="30" t="n"/>
@@ -7971,7 +7971,7 @@
     <row r="127">
       <c r="A127" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-11</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B127" s="27" t="inlineStr">
@@ -7981,32 +7981,32 @@
       </c>
       <c r="C127" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D127" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E127" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F127" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 알림은 최대 5건</t>
+          <t>issue_certificate: institution 이 아니면 발급 불가</t>
         </is>
       </c>
       <c r="G127" s="29" t="inlineStr">
         <is>
-          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
+          <t>PermissionDeniedError</t>
         </is>
       </c>
       <c r="H127" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I127" s="30" t="n"/>
@@ -8018,7 +8018,7 @@
     <row r="128">
       <c r="A128" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-12</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B128" s="27" t="inlineStr">
@@ -8033,22 +8033,22 @@
       </c>
       <c r="D128" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E128" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F128" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
+          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
         </is>
       </c>
       <c r="G128" s="29" t="inlineStr">
         <is>
-          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
+          <t>ValidationError / ValidationError / NotFoundError</t>
         </is>
       </c>
       <c r="H128" s="28" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="129">
       <c r="A129" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-13</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B129" s="27" t="inlineStr">
@@ -8075,32 +8075,32 @@
       </c>
       <c r="C129" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D129" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E129" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F129" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
+          <t>issue_certificate: KCMVP 유형도 발급</t>
         </is>
       </c>
       <c r="G129" s="29" t="inlineStr">
         <is>
-          <t>scope='own'</t>
+          <t>cert_type='KCMVP'</t>
         </is>
       </c>
       <c r="H129" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I129" s="30" t="n"/>
@@ -8112,7 +8112,7 @@
     <row r="130">
       <c r="A130" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-14</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B130" s="27" t="inlineStr">
@@ -8122,32 +8122,32 @@
       </c>
       <c r="C130" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D130" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E130" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F130" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 없는 사용자</t>
+          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
         </is>
       </c>
       <c r="G130" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>타인 검증서 제외, issued_at 내림차순</t>
         </is>
       </c>
       <c r="H130" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I130" s="30" t="n"/>
@@ -8159,7 +8159,7 @@
     <row r="131">
       <c r="A131" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-15</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B131" s="27" t="inlineStr">
@@ -8169,32 +8169,32 @@
       </c>
       <c r="C131" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D131" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E131" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F131" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
+          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
         </is>
       </c>
       <c r="G131" s="29" t="inlineStr">
         <is>
-          <t>결과 전체에 password/hash 키 없음</t>
+          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
         </is>
       </c>
       <c r="H131" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I131" s="30" t="n"/>
@@ -8206,7 +8206,7 @@
     <row r="132">
       <c r="A132" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-16</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B132" s="27" t="inlineStr">
@@ -8216,32 +8216,32 @@
       </c>
       <c r="C132" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D132" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E132" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F132" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
+          <t>get_certificate: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
         <is>
-          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H132" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I132" s="30" t="n"/>
@@ -8253,7 +8253,7 @@
     <row r="133">
       <c r="A133" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B133" s="27" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="C133" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D133" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E133" s="27" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="F133" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
+          <t>verify_integrity: 파일 무결 → normal</t>
         </is>
       </c>
       <c r="G133" s="29" t="inlineStr">
         <is>
-          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
+          <t>tamper_status='normal'</t>
         </is>
       </c>
       <c r="H133" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I133" s="30" t="n"/>
@@ -8300,7 +8300,7 @@
     <row r="134">
       <c r="A134" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B134" s="27" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="C134" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D134" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E134" s="27" t="inlineStr">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="F134" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 호출마다 다른 값</t>
+          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
         </is>
       </c>
       <c r="G134" s="29" t="inlineStr">
         <is>
-          <t>1000회 호출 모두 유일</t>
+          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
         </is>
       </c>
       <c r="H134" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I134" s="30" t="n"/>
@@ -8347,7 +8347,7 @@
     <row r="135">
       <c r="A135" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B135" s="27" t="inlineStr">
@@ -8357,32 +8357,32 @@
       </c>
       <c r="C135" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D135" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E135" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F135" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 길이별 마스킹 규칙</t>
+          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
         </is>
       </c>
       <c r="G135" s="29" t="inlineStr">
         <is>
-          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
+          <t>'suspected' (예외 아님)</t>
         </is>
       </c>
       <c r="H135" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I135" s="30" t="n"/>
@@ -8394,7 +8394,7 @@
     <row r="136">
       <c r="A136" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B136" s="27" t="inlineStr">
@@ -8404,32 +8404,32 @@
       </c>
       <c r="C136" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D136" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E136" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F136" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 빈 값/공백만</t>
+          <t>verify_integrity: 원복 후 재검증 시 normal</t>
         </is>
       </c>
       <c r="G136" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>변조 → suspected, 원복 → normal</t>
         </is>
       </c>
       <c r="H136" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I136" s="30" t="n"/>
@@ -8441,7 +8441,7 @@
     <row r="137">
       <c r="A137" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B137" s="27" t="inlineStr">
@@ -8451,32 +8451,32 @@
       </c>
       <c r="C137" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D137" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E137" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F137" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
+          <t>verify_integrity: 존재하지 않는 cert_id</t>
         </is>
       </c>
       <c r="G137" s="29" t="inlineStr">
         <is>
-          <t>' 홍길동 ' → '홍*동'</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H137" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I137" s="30" t="n"/>
@@ -8488,7 +8488,7 @@
     <row r="138">
       <c r="A138" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B138" s="27" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="C138" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D138" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E138" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F138" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 하이픈 유/무 입력</t>
+          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
         </is>
       </c>
       <c r="G138" s="29" t="inlineStr">
         <is>
-          <t>모두 '010-****-5678'</t>
+          <t>검증 후에도 integrity_hash 불변</t>
         </is>
       </c>
       <c r="H138" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I138" s="30" t="n"/>
@@ -8535,7 +8535,7 @@
     <row r="139">
       <c r="A139" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B139" s="27" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="C139" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D139" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E139" s="27" t="inlineStr">
@@ -8560,17 +8560,17 @@
       </c>
       <c r="F139" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
+          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
         </is>
       </c>
       <c r="G139" s="29" t="inlineStr">
         <is>
-          <t>'010-***-4567'</t>
+          <t>파일이 없으면 suspected 유지</t>
         </is>
       </c>
       <c r="H139" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I139" s="30" t="n"/>
@@ -8582,7 +8582,7 @@
     <row r="140">
       <c r="A140" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B140" s="27" t="inlineStr">
@@ -8592,27 +8592,27 @@
       </c>
       <c r="C140" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D140" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E140" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F140" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 형식 오류</t>
+          <t>get_summary: 본인 신청만 집계</t>
         </is>
       </c>
       <c r="G140" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
         </is>
       </c>
       <c r="H140" s="28" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="141">
       <c r="A141" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B141" s="27" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="C141" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D141" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E141" s="27" t="inlineStr">
@@ -8654,12 +8654,12 @@
       </c>
       <c r="F141" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 대표 연령대</t>
+          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
         </is>
       </c>
       <c r="G141" s="29" t="inlineStr">
         <is>
-          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
+          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
         </is>
       </c>
       <c r="H141" s="28" t="inlineStr">
@@ -8676,7 +8676,7 @@
     <row r="142">
       <c r="A142" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B142" s="27" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="C142" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D142" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E142" s="27" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="F142" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
+          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
         </is>
       </c>
       <c r="G142" s="29" t="inlineStr">
         <is>
-          <t>생일 당일부터 다음 연령대</t>
+          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
         </is>
       </c>
       <c r="H142" s="28" t="inlineStr">
@@ -8723,7 +8723,7 @@
     <row r="143">
       <c r="A143" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B143" s="27" t="inlineStr">
@@ -8733,27 +8733,27 @@
       </c>
       <c r="C143" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D143" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E143" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F143" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
+          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
         </is>
       </c>
       <c r="G143" s="29" t="inlineStr">
         <is>
-          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
+          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="H143" s="28" t="inlineStr">
@@ -8770,7 +8770,7 @@
     <row r="144">
       <c r="A144" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B144" s="27" t="inlineStr">
@@ -8780,27 +8780,27 @@
       </c>
       <c r="C144" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D144" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E144" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F144" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 미래 날짜</t>
+          <t>get_summary: 상태 라벨 매핑</t>
         </is>
       </c>
       <c r="G144" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
         </is>
       </c>
       <c r="H144" s="28" t="inlineStr">
@@ -8817,7 +8817,7 @@
     <row r="145">
       <c r="A145" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B145" s="27" t="inlineStr">
@@ -8827,27 +8827,27 @@
       </c>
       <c r="C145" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D145" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E145" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F145" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
+          <t>get_summary: 최근 7일 신규 신청 경계</t>
         </is>
       </c>
       <c r="G145" s="29" t="inlineStr">
         <is>
-          <t>연·월·일 숫자열이 결과에 없음</t>
+          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
         </is>
       </c>
       <c r="H145" s="28" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="146">
       <c r="A146" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B146" s="27" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="C146" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D146" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E146" s="27" t="inlineStr">
@@ -8889,17 +8889,17 @@
       </c>
       <c r="F146" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 결과 객체</t>
+          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
         </is>
       </c>
       <c r="G146" s="29" t="inlineStr">
         <is>
-          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
+          <t>total·suspected 가 본인 건만 반영</t>
         </is>
       </c>
       <c r="H146" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I146" s="30" t="n"/>
@@ -8911,7 +8911,7 @@
     <row r="147">
       <c r="A147" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B147" s="27" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D147" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E147" s="27" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="F147" s="29" t="inlineStr">
         <is>
-          <t>process(anonymous): 식별자 없음</t>
+          <t>get_summary: 가명·익명 처리 상태</t>
         </is>
       </c>
       <c r="G147" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
+          <t>처리 전 processed=False, 처리 후 level 반영</t>
         </is>
       </c>
       <c r="H147" s="28" t="inlineStr">
@@ -8958,7 +8958,7 @@
     <row r="148">
       <c r="A148" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B148" s="27" t="inlineStr">
@@ -8968,32 +8968,32 @@
       </c>
       <c r="C148" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D148" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E148" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F148" s="29" t="inlineStr">
         <is>
-          <t>process: 허용되지 않는 mode</t>
+          <t>get_summary: 위변조 의심 알림이 최우선</t>
         </is>
       </c>
       <c r="G148" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
         </is>
       </c>
       <c r="H148" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I148" s="30" t="n"/>
@@ -9005,7 +9005,7 @@
     <row r="149">
       <c r="A149" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B149" s="27" t="inlineStr">
@@ -9015,27 +9015,27 @@
       </c>
       <c r="C149" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D149" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E149" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F149" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
+          <t>get_summary: 신청 진행/결과 알림 문구</t>
         </is>
       </c>
       <c r="G149" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
         </is>
       </c>
       <c r="H149" s="28" t="inlineStr">
@@ -9052,7 +9052,7 @@
     <row r="150">
       <c r="A150" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B150" s="27" t="inlineStr">
@@ -9062,27 +9062,27 @@
       </c>
       <c r="C150" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D150" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E150" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F150" s="29" t="inlineStr">
         <is>
-          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
+          <t>get_summary: 알림은 최대 5건</t>
         </is>
       </c>
       <c r="G150" s="29" t="inlineStr">
         <is>
-          <t>표시값/식별자에 '홍길동' 미포함</t>
+          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
         </is>
       </c>
       <c r="H150" s="28" t="inlineStr">
@@ -9099,7 +9099,7 @@
     <row r="151">
       <c r="A151" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B151" s="27" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="C151" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D151" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E151" s="27" t="inlineStr">
@@ -9124,17 +9124,17 @@
       </c>
       <c r="F151" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: personal_info 저장</t>
+          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
         </is>
       </c>
       <c r="G151" s="29" t="inlineStr">
         <is>
-          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
+          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
         </is>
       </c>
       <c r="H151" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I151" s="30" t="n"/>
@@ -9146,7 +9146,7 @@
     <row r="152">
       <c r="A152" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B152" s="27" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="C152" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D152" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E152" s="27" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="F152" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
+          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
         </is>
       </c>
       <c r="G152" s="29" t="inlineStr">
         <is>
-          <t>행 1건, pseudonym_id 동일</t>
+          <t>scope='own'</t>
         </is>
       </c>
       <c r="H152" s="28" t="inlineStr">
@@ -9193,7 +9193,7 @@
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B153" s="27" t="inlineStr">
@@ -9203,27 +9203,27 @@
       </c>
       <c r="C153" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E153" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F153" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
+          <t>get_summary: 없는 사용자</t>
         </is>
       </c>
       <c r="G153" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H153" s="28" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="154">
       <c r="A154" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B154" s="27" t="inlineStr">
@@ -9250,27 +9250,27 @@
       </c>
       <c r="C154" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D154" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E154" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F154" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 없는 사용자</t>
+          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
         </is>
       </c>
       <c r="G154" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError, 행 미생성</t>
+          <t>결과 전체에 password/hash 키 없음</t>
         </is>
       </c>
       <c r="H154" s="28" t="inlineStr">
@@ -9287,7 +9287,7 @@
     <row r="155">
       <c r="A155" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B155" s="27" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="C155" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D155" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E155" s="27" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="F155" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
         </is>
       </c>
       <c r="G155" s="29" t="inlineStr">
         <is>
-          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
         </is>
       </c>
       <c r="H155" s="28" t="inlineStr">
@@ -9334,7 +9334,7 @@
     <row r="156">
       <c r="A156" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B156" s="27" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="F156" s="29" t="inlineStr">
         <is>
-          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
         </is>
       </c>
       <c r="G156" s="29" t="inlineStr">
         <is>
-          <t>저장된 행 반환, 없으면 NotFoundError</t>
+          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
         </is>
       </c>
       <c r="H156" s="28" t="inlineStr">
@@ -9381,7 +9381,7 @@
     <row r="157">
       <c r="A157" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B157" s="27" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="C157" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D157" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E157" s="27" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="F157" s="29" t="inlineStr">
         <is>
-          <t>seed: 사용자 3종 생성</t>
+          <t>issue_pseudonym_id: 호출마다 다른 값</t>
         </is>
       </c>
       <c r="G157" s="29" t="inlineStr">
         <is>
-          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+          <t>1000회 호출 모두 유일</t>
         </is>
       </c>
       <c r="H157" s="28" t="inlineStr">
@@ -9428,7 +9428,7 @@
     <row r="158">
       <c r="A158" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-PRIV-03</t>
         </is>
       </c>
       <c r="B158" s="27" t="inlineStr">
@@ -9438,27 +9438,27 @@
       </c>
       <c r="C158" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D158" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E158" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F158" s="29" t="inlineStr">
         <is>
-          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+          <t>mask_name: 길이별 마스킹 규칙</t>
         </is>
       </c>
       <c r="G158" s="29" t="inlineStr">
         <is>
-          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
         </is>
       </c>
       <c r="H158" s="28" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="159">
       <c r="A159" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-PRIV-04</t>
         </is>
       </c>
       <c r="B159" s="27" t="inlineStr">
@@ -9485,27 +9485,27 @@
       </c>
       <c r="C159" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D159" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E159" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F159" s="29" t="inlineStr">
         <is>
-          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+          <t>mask_name: 빈 값/공백만</t>
         </is>
       </c>
       <c r="G159" s="29" t="inlineStr">
         <is>
-          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H159" s="28" t="inlineStr">
@@ -9522,7 +9522,7 @@
     <row r="160">
       <c r="A160" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-PRIV-05</t>
         </is>
       </c>
       <c r="B160" s="27" t="inlineStr">
@@ -9532,32 +9532,32 @@
       </c>
       <c r="C160" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D160" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E160" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F160" s="29" t="inlineStr">
         <is>
-          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
         </is>
       </c>
       <c r="G160" s="29" t="inlineStr">
         <is>
-          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+          <t>' 홍길동 ' → '홍*동'</t>
         </is>
       </c>
       <c r="H160" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I160" s="30" t="n"/>
@@ -9569,7 +9569,7 @@
     <row r="161">
       <c r="A161" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-06</t>
         </is>
       </c>
       <c r="B161" s="27" t="inlineStr">
@@ -9584,22 +9584,22 @@
       </c>
       <c r="D161" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E161" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F161" s="29" t="inlineStr">
         <is>
-          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+          <t>mask_phone: 하이픈 유/무 입력</t>
         </is>
       </c>
       <c r="G161" s="29" t="inlineStr">
         <is>
-          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+          <t>모두 '010-****-5678'</t>
         </is>
       </c>
       <c r="H161" s="28" t="inlineStr">
@@ -9616,7 +9616,7 @@
     <row r="162">
       <c r="A162" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-PRIV-07</t>
         </is>
       </c>
       <c r="B162" s="27" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="C162" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D162" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E162" s="27" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="F162" s="29" t="inlineStr">
         <is>
-          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
         </is>
       </c>
       <c r="G162" s="29" t="inlineStr">
         <is>
-          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+          <t>'010-***-4567'</t>
         </is>
       </c>
       <c r="H162" s="28" t="inlineStr">
@@ -9660,9 +9660,1090 @@
         <v/>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-08</t>
+        </is>
+      </c>
+      <c r="B163" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C163" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D163" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E163" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F163" s="29" t="inlineStr">
+        <is>
+          <t>mask_phone: 형식 오류</t>
+        </is>
+      </c>
+      <c r="G163" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H163" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I163" s="30" t="n"/>
+      <c r="J163" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A163,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-09</t>
+        </is>
+      </c>
+      <c r="B164" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C164" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D164" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E164" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F164" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 대표 연령대</t>
+        </is>
+      </c>
+      <c r="G164" s="29" t="inlineStr">
+        <is>
+          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="H164" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I164" s="30" t="n"/>
+      <c r="J164" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A164,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-10</t>
+        </is>
+      </c>
+      <c r="B165" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C165" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D165" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E165" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F165" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
+        </is>
+      </c>
+      <c r="G165" s="29" t="inlineStr">
+        <is>
+          <t>생일 당일부터 다음 연령대</t>
+        </is>
+      </c>
+      <c r="H165" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I165" s="30" t="n"/>
+      <c r="J165" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A165,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-11</t>
+        </is>
+      </c>
+      <c r="B166" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C166" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D166" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E166" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F166" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
+        </is>
+      </c>
+      <c r="G166" s="29" t="inlineStr">
+        <is>
+          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
+        </is>
+      </c>
+      <c r="H166" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I166" s="30" t="n"/>
+      <c r="J166" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A166,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-12</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C167" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D167" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E167" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F167" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 미래 날짜</t>
+        </is>
+      </c>
+      <c r="G167" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H167" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I167" s="30" t="n"/>
+      <c r="J167" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A167,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-13</t>
+        </is>
+      </c>
+      <c r="B168" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C168" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D168" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E168" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F168" s="29" t="inlineStr">
+        <is>
+          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
+        </is>
+      </c>
+      <c r="G168" s="29" t="inlineStr">
+        <is>
+          <t>연·월·일 숫자열이 결과에 없음</t>
+        </is>
+      </c>
+      <c r="H168" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I168" s="30" t="n"/>
+      <c r="J168" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A168,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-14</t>
+        </is>
+      </c>
+      <c r="B169" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C169" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D169" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E169" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F169" s="29" t="inlineStr">
+        <is>
+          <t>process(pseudonym): 결과 객체</t>
+        </is>
+      </c>
+      <c r="G169" s="29" t="inlineStr">
+        <is>
+          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
+        </is>
+      </c>
+      <c r="H169" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I169" s="30" t="n"/>
+      <c r="J169" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A169,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-15</t>
+        </is>
+      </c>
+      <c r="B170" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C170" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D170" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E170" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F170" s="29" t="inlineStr">
+        <is>
+          <t>process(anonymous): 식별자 없음</t>
+        </is>
+      </c>
+      <c r="G170" s="29" t="inlineStr">
+        <is>
+          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
+        </is>
+      </c>
+      <c r="H170" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I170" s="30" t="n"/>
+      <c r="J170" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A170,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-16</t>
+        </is>
+      </c>
+      <c r="B171" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C171" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D171" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E171" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F171" s="29" t="inlineStr">
+        <is>
+          <t>process: 허용되지 않는 mode</t>
+        </is>
+      </c>
+      <c r="G171" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H171" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I171" s="30" t="n"/>
+      <c r="J171" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A171,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-17</t>
+        </is>
+      </c>
+      <c r="B172" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C172" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D172" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E172" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F172" s="29" t="inlineStr">
+        <is>
+          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
+        </is>
+      </c>
+      <c r="G172" s="29" t="inlineStr">
+        <is>
+          <t>ValidationError</t>
+        </is>
+      </c>
+      <c r="H172" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I172" s="30" t="n"/>
+      <c r="J172" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A172,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-18</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C173" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D173" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E173" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F173" s="29" t="inlineStr">
+        <is>
+          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
+        </is>
+      </c>
+      <c r="G173" s="29" t="inlineStr">
+        <is>
+          <t>표시값/식별자에 '홍길동' 미포함</t>
+        </is>
+      </c>
+      <c r="H173" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I173" s="30" t="n"/>
+      <c r="J173" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A173,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-19</t>
+        </is>
+      </c>
+      <c r="B174" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C174" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D174" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E174" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F174" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: personal_info 저장</t>
+        </is>
+      </c>
+      <c r="G174" s="29" t="inlineStr">
+        <is>
+          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
+        </is>
+      </c>
+      <c r="H174" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I174" s="30" t="n"/>
+      <c r="J174" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A174,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-20</t>
+        </is>
+      </c>
+      <c r="B175" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C175" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D175" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E175" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F175" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
+        </is>
+      </c>
+      <c r="G175" s="29" t="inlineStr">
+        <is>
+          <t>행 1건, pseudonym_id 동일</t>
+        </is>
+      </c>
+      <c r="H175" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I175" s="30" t="n"/>
+      <c r="J175" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A175,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-21</t>
+        </is>
+      </c>
+      <c r="B176" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C176" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D176" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E176" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F176" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
+        </is>
+      </c>
+      <c r="G176" s="29" t="inlineStr">
+        <is>
+          <t>level='anonymous', pseudonym_id=None</t>
+        </is>
+      </c>
+      <c r="H176" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I176" s="30" t="n"/>
+      <c r="J176" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A176,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-22</t>
+        </is>
+      </c>
+      <c r="B177" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C177" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D177" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E177" s="27" t="inlineStr">
+        <is>
+          <t>비정상</t>
+        </is>
+      </c>
+      <c r="F177" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 없는 사용자</t>
+        </is>
+      </c>
+      <c r="G177" s="29" t="inlineStr">
+        <is>
+          <t>NotFoundError, 행 미생성</t>
+        </is>
+      </c>
+      <c r="H177" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I177" s="30" t="n"/>
+      <c r="J177" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A177,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-23</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C178" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D178" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E178" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F178" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+        </is>
+      </c>
+      <c r="G178" s="29" t="inlineStr">
+        <is>
+          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+        </is>
+      </c>
+      <c r="H178" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I178" s="30" t="n"/>
+      <c r="J178" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A178,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-24</t>
+        </is>
+      </c>
+      <c r="B179" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C179" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D179" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E179" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F179" s="29" t="inlineStr">
+        <is>
+          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+        </is>
+      </c>
+      <c r="G179" s="29" t="inlineStr">
+        <is>
+          <t>저장된 행 반환, 없으면 NotFoundError</t>
+        </is>
+      </c>
+      <c r="H179" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I179" s="30" t="n"/>
+      <c r="J179" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A179,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-01</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C180" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D180" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E180" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F180" s="29" t="inlineStr">
+        <is>
+          <t>seed: 사용자 3종 생성</t>
+        </is>
+      </c>
+      <c r="G180" s="29" t="inlineStr">
+        <is>
+          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+        </is>
+      </c>
+      <c r="H180" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I180" s="30" t="n"/>
+      <c r="J180" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A180,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B181" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C181" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D181" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E181" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F181" s="29" t="inlineStr">
+        <is>
+          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+        </is>
+      </c>
+      <c r="G181" s="29" t="inlineStr">
+        <is>
+          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+        </is>
+      </c>
+      <c r="H181" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I181" s="30" t="n"/>
+      <c r="J181" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A181,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B182" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C182" s="27" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="D182" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E182" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F182" s="29" t="inlineStr">
+        <is>
+          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+        </is>
+      </c>
+      <c r="G182" s="29" t="inlineStr">
+        <is>
+          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+        </is>
+      </c>
+      <c r="H182" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I182" s="30" t="n"/>
+      <c r="J182" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A182,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C183" s="27" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="D183" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E183" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F183" s="29" t="inlineStr">
+        <is>
+          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+        </is>
+      </c>
+      <c r="G183" s="29" t="inlineStr">
+        <is>
+          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+        </is>
+      </c>
+      <c r="H183" s="28" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="I183" s="30" t="n"/>
+      <c r="J183" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A183,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B184" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C184" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D184" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E184" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F184" s="29" t="inlineStr">
+        <is>
+          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+        </is>
+      </c>
+      <c r="G184" s="29" t="inlineStr">
+        <is>
+          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+        </is>
+      </c>
+      <c r="H184" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I184" s="30" t="n"/>
+      <c r="J184" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A184,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B185" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C185" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D185" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E185" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F185" s="29" t="inlineStr">
+        <is>
+          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+        </is>
+      </c>
+      <c r="G185" s="29" t="inlineStr">
+        <is>
+          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+        </is>
+      </c>
+      <c r="H185" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I185" s="30" t="n"/>
+      <c r="J185" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A185,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J162"/>
-  <conditionalFormatting sqref="J5:J162">
+  <autoFilter ref="A4:J185"/>
+  <conditionalFormatting sqref="J5:J185">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -9698,7 +10779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11086,7 +12167,7 @@
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-ATK-01</t>
         </is>
       </c>
       <c r="B51" s="32">
@@ -11114,7 +12195,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>IT-ATK-02</t>
         </is>
       </c>
       <c r="B52" s="32">
@@ -11142,7 +12223,7 @@
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>IT-ATK-03</t>
         </is>
       </c>
       <c r="B53" s="32">
@@ -11170,7 +12251,7 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>IT-ATK-04</t>
         </is>
       </c>
       <c r="B54" s="32">
@@ -11198,7 +12279,7 @@
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>IT-ATK-05</t>
         </is>
       </c>
       <c r="B55" s="32">
@@ -11210,7 +12291,7 @@
         <v/>
       </c>
       <c r="D55" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E55" s="23" t="n">
         <v>0</v>
@@ -11226,7 +12307,7 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>IT-ATK-06</t>
         </is>
       </c>
       <c r="B56" s="32">
@@ -11238,7 +12319,7 @@
         <v/>
       </c>
       <c r="D56" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" s="23" t="n">
         <v>0</v>
@@ -11254,7 +12335,7 @@
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>IT-ATK-07</t>
         </is>
       </c>
       <c r="B57" s="32">
@@ -11282,7 +12363,7 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>IT-ATK-08</t>
         </is>
       </c>
       <c r="B58" s="32">
@@ -11294,7 +12375,7 @@
         <v/>
       </c>
       <c r="D58" s="23" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E58" s="23" t="n">
         <v>0</v>
@@ -11310,7 +12391,7 @@
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>IT-ATK-09</t>
         </is>
       </c>
       <c r="B59" s="32">
@@ -11322,7 +12403,7 @@
         <v/>
       </c>
       <c r="D59" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="23" t="n">
         <v>0</v>
@@ -11338,7 +12419,7 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>IT-ATK-10</t>
         </is>
       </c>
       <c r="B60" s="32">
@@ -11350,7 +12431,7 @@
         <v/>
       </c>
       <c r="D60" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E60" s="23" t="n">
         <v>0</v>
@@ -11366,7 +12447,7 @@
     <row r="61">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>IT-ATK-11</t>
         </is>
       </c>
       <c r="B61" s="32">
@@ -11394,7 +12475,7 @@
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>IT-ATK-12</t>
         </is>
       </c>
       <c r="B62" s="32">
@@ -11422,7 +12503,7 @@
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>IT-ATK-13</t>
         </is>
       </c>
       <c r="B63" s="32">
@@ -11450,7 +12531,7 @@
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>IT-ATK-14</t>
         </is>
       </c>
       <c r="B64" s="32">
@@ -11462,7 +12543,7 @@
         <v/>
       </c>
       <c r="D64" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" s="23" t="n">
         <v>0</v>
@@ -11478,7 +12559,7 @@
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>IT-ATK-15</t>
         </is>
       </c>
       <c r="B65" s="32">
@@ -11490,7 +12571,7 @@
         <v/>
       </c>
       <c r="D65" s="23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E65" s="23" t="n">
         <v>0</v>
@@ -11506,7 +12587,7 @@
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>IT-ATK-16</t>
         </is>
       </c>
       <c r="B66" s="32">
@@ -11518,7 +12599,7 @@
         <v/>
       </c>
       <c r="D66" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" s="23" t="n">
         <v>0</v>
@@ -11534,7 +12615,7 @@
     <row r="67">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>IT-ATK-17</t>
         </is>
       </c>
       <c r="B67" s="32">
@@ -11546,7 +12627,7 @@
         <v/>
       </c>
       <c r="D67" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" s="23" t="n">
         <v>0</v>
@@ -11562,7 +12643,7 @@
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>IT-ATK-18</t>
         </is>
       </c>
       <c r="B68" s="32">
@@ -11574,7 +12655,7 @@
         <v/>
       </c>
       <c r="D68" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="23" t="n">
         <v>0</v>
@@ -11590,7 +12671,7 @@
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>IT-ATK-19</t>
         </is>
       </c>
       <c r="B69" s="32">
@@ -11618,7 +12699,7 @@
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>IT-ATK-20</t>
         </is>
       </c>
       <c r="B70" s="32">
@@ -11646,7 +12727,7 @@
     <row r="71">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-ATK-01</t>
         </is>
       </c>
       <c r="B71" s="32">
@@ -11674,7 +12755,7 @@
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-ATK-02</t>
         </is>
       </c>
       <c r="B72" s="32">
@@ -11702,7 +12783,7 @@
     <row r="73">
       <c r="A73" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-ATK-03</t>
         </is>
       </c>
       <c r="B73" s="32">
@@ -11714,7 +12795,7 @@
         <v/>
       </c>
       <c r="D73" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E73" s="23" t="n">
         <v>0</v>
@@ -11730,7 +12811,7 @@
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B74" s="32">
@@ -11758,7 +12839,7 @@
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B75" s="32">
@@ -11770,13 +12851,13 @@
         <v/>
       </c>
       <c r="D75" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="23" t="n">
         <v>0</v>
@@ -11786,7 +12867,7 @@
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B76" s="32">
@@ -11798,13 +12879,13 @@
         <v/>
       </c>
       <c r="D76" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>0</v>
@@ -11814,7 +12895,7 @@
     <row r="77">
       <c r="A77" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B77" s="32">
@@ -11826,13 +12907,13 @@
         <v/>
       </c>
       <c r="D77" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>0</v>
@@ -11842,7 +12923,7 @@
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B78" s="32">
@@ -11854,13 +12935,13 @@
         <v/>
       </c>
       <c r="D78" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>0</v>
@@ -11870,7 +12951,7 @@
     <row r="79">
       <c r="A79" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B79" s="32">
@@ -11882,13 +12963,13 @@
         <v/>
       </c>
       <c r="D79" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E79" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G79" s="23" t="n">
         <v>0</v>
@@ -11898,7 +12979,7 @@
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B80" s="32">
@@ -11910,13 +12991,13 @@
         <v/>
       </c>
       <c r="D80" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="23" t="n">
         <v>0</v>
@@ -11926,7 +13007,7 @@
     <row r="81">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B81" s="32">
@@ -11938,13 +13019,13 @@
         <v/>
       </c>
       <c r="D81" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G81" s="23" t="n">
         <v>0</v>
@@ -11954,7 +13035,7 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B82" s="32">
@@ -11966,23 +13047,23 @@
         <v/>
       </c>
       <c r="D82" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G82" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H82" s="22" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B83" s="32">
@@ -11994,13 +13075,13 @@
         <v/>
       </c>
       <c r="D83" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E83" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G83" s="23" t="n">
         <v>0</v>
@@ -12010,7 +13091,7 @@
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B84" s="32">
@@ -12022,13 +13103,13 @@
         <v/>
       </c>
       <c r="D84" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="23" t="n">
         <v>0</v>
@@ -12038,7 +13119,7 @@
     <row r="85">
       <c r="A85" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B85" s="32">
@@ -12050,13 +13131,13 @@
         <v/>
       </c>
       <c r="D85" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="23" t="n">
         <v>0</v>
@@ -12066,7 +13147,7 @@
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B86" s="32">
@@ -12078,13 +13159,13 @@
         <v/>
       </c>
       <c r="D86" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="23" t="n">
         <v>0</v>
@@ -12094,7 +13175,7 @@
     <row r="87">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B87" s="32">
@@ -12106,13 +13187,13 @@
         <v/>
       </c>
       <c r="D87" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E87" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="23" t="n">
         <v>0</v>
@@ -12122,7 +13203,7 @@
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B88" s="32">
@@ -12134,13 +13215,13 @@
         <v/>
       </c>
       <c r="D88" s="23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E88" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="23" t="n">
         <v>0</v>
@@ -12150,7 +13231,7 @@
     <row r="89">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B89" s="32">
@@ -12162,13 +13243,13 @@
         <v/>
       </c>
       <c r="D89" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="23" t="n">
         <v>0</v>
@@ -12178,7 +13259,7 @@
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B90" s="32">
@@ -12190,13 +13271,13 @@
         <v/>
       </c>
       <c r="D90" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E90" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="23" t="n">
         <v>0</v>
@@ -12206,7 +13287,7 @@
     <row r="91">
       <c r="A91" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B91" s="32">
@@ -12218,13 +13299,13 @@
         <v/>
       </c>
       <c r="D91" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E91" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G91" s="23" t="n">
         <v>0</v>
@@ -12234,7 +13315,7 @@
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B92" s="32">
@@ -12246,13 +13327,13 @@
         <v/>
       </c>
       <c r="D92" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="23" t="n">
         <v>0</v>
@@ -12262,7 +13343,7 @@
     <row r="93">
       <c r="A93" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B93" s="32">
@@ -12274,13 +13355,13 @@
         <v/>
       </c>
       <c r="D93" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="23" t="n">
         <v>0</v>
@@ -12290,7 +13371,7 @@
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B94" s="32">
@@ -12302,13 +13383,13 @@
         <v/>
       </c>
       <c r="D94" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="23" t="n">
         <v>0</v>
@@ -12318,7 +13399,7 @@
     <row r="95">
       <c r="A95" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B95" s="32">
@@ -12330,13 +13411,13 @@
         <v/>
       </c>
       <c r="D95" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="23" t="n">
         <v>0</v>
@@ -12346,7 +13427,7 @@
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B96" s="32">
@@ -12358,13 +13439,13 @@
         <v/>
       </c>
       <c r="D96" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E96" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="23" t="n">
         <v>0</v>
@@ -12374,7 +13455,7 @@
     <row r="97">
       <c r="A97" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B97" s="32">
@@ -12386,13 +13467,13 @@
         <v/>
       </c>
       <c r="D97" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="23" t="n">
         <v>0</v>
@@ -12402,7 +13483,7 @@
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B98" s="32">
@@ -12430,7 +13511,7 @@
     <row r="99">
       <c r="A99" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B99" s="32">
@@ -12448,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G99" s="23" t="n">
         <v>0</v>
@@ -12458,7 +13539,7 @@
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B100" s="32">
@@ -12476,7 +13557,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G100" s="23" t="n">
         <v>0</v>
@@ -12486,7 +13567,7 @@
     <row r="101">
       <c r="A101" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B101" s="32">
@@ -12504,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G101" s="23" t="n">
         <v>0</v>
@@ -12514,7 +13595,7 @@
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B102" s="32">
@@ -12532,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G102" s="23" t="n">
         <v>0</v>
@@ -12542,7 +13623,7 @@
     <row r="103">
       <c r="A103" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B103" s="32">
@@ -12570,7 +13651,7 @@
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B104" s="32">
@@ -12588,7 +13669,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G104" s="23" t="n">
         <v>0</v>
@@ -12598,7 +13679,7 @@
     <row r="105">
       <c r="A105" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B105" s="32">
@@ -12616,17 +13697,17 @@
         <v>0</v>
       </c>
       <c r="F105" s="23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G105" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H105" s="22" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B106" s="32">
@@ -12644,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G106" s="23" t="n">
         <v>0</v>
@@ -12654,7 +13735,7 @@
     <row r="107">
       <c r="A107" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B107" s="32">
@@ -12682,7 +13763,7 @@
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B108" s="32">
@@ -12700,7 +13781,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" s="23" t="n">
         <v>0</v>
@@ -12710,7 +13791,7 @@
     <row r="109">
       <c r="A109" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B109" s="32">
@@ -12738,7 +13819,7 @@
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B110" s="32">
@@ -12766,7 +13847,7 @@
     <row r="111">
       <c r="A111" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B111" s="32">
@@ -12794,7 +13875,7 @@
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B112" s="32">
@@ -12822,7 +13903,7 @@
     <row r="113">
       <c r="A113" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B113" s="32">
@@ -12850,7 +13931,7 @@
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B114" s="32">
@@ -12868,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G114" s="23" t="n">
         <v>0</v>
@@ -12878,7 +13959,7 @@
     <row r="115">
       <c r="A115" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B115" s="32">
@@ -12906,7 +13987,7 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-01</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B116" s="32">
@@ -12918,13 +13999,13 @@
         <v/>
       </c>
       <c r="D116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E116" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G116" s="23" t="n">
         <v>0</v>
@@ -12934,7 +14015,7 @@
     <row r="117">
       <c r="A117" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-02</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B117" s="32">
@@ -12946,13 +14027,13 @@
         <v/>
       </c>
       <c r="D117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E117" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G117" s="23" t="n">
         <v>0</v>
@@ -12962,7 +14043,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-03</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B118" s="32">
@@ -12974,13 +14055,13 @@
         <v/>
       </c>
       <c r="D118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E118" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G118" s="23" t="n">
         <v>0</v>
@@ -12990,7 +14071,7 @@
     <row r="119">
       <c r="A119" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-04</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B119" s="32">
@@ -13002,13 +14083,13 @@
         <v/>
       </c>
       <c r="D119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E119" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G119" s="23" t="n">
         <v>0</v>
@@ -13018,7 +14099,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-05</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B120" s="32">
@@ -13030,13 +14111,13 @@
         <v/>
       </c>
       <c r="D120" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E120" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" s="23" t="n">
         <v>0</v>
@@ -13046,7 +14127,7 @@
     <row r="121">
       <c r="A121" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-06</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B121" s="32">
@@ -13058,13 +14139,13 @@
         <v/>
       </c>
       <c r="D121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G121" s="23" t="n">
         <v>0</v>
@@ -13074,7 +14155,7 @@
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-07</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B122" s="32">
@@ -13086,13 +14167,13 @@
         <v/>
       </c>
       <c r="D122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G122" s="23" t="n">
         <v>0</v>
@@ -13102,7 +14183,7 @@
     <row r="123">
       <c r="A123" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-08</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B123" s="32">
@@ -13114,13 +14195,13 @@
         <v/>
       </c>
       <c r="D123" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E123" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" s="23" t="n">
         <v>0</v>
@@ -13130,7 +14211,7 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-09</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B124" s="32">
@@ -13142,13 +14223,13 @@
         <v/>
       </c>
       <c r="D124" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G124" s="23" t="n">
         <v>0</v>
@@ -13158,7 +14239,7 @@
     <row r="125">
       <c r="A125" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-10</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B125" s="32">
@@ -13170,13 +14251,13 @@
         <v/>
       </c>
       <c r="D125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G125" s="23" t="n">
         <v>0</v>
@@ -13186,7 +14267,7 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-11</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B126" s="32">
@@ -13198,13 +14279,13 @@
         <v/>
       </c>
       <c r="D126" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" s="23" t="n">
         <v>0</v>
@@ -13214,7 +14295,7 @@
     <row r="127">
       <c r="A127" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-12</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B127" s="32">
@@ -13226,13 +14307,13 @@
         <v/>
       </c>
       <c r="D127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E127" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G127" s="23" t="n">
         <v>0</v>
@@ -13242,7 +14323,7 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-13</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B128" s="32">
@@ -13254,13 +14335,13 @@
         <v/>
       </c>
       <c r="D128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G128" s="23" t="n">
         <v>0</v>
@@ -13270,7 +14351,7 @@
     <row r="129">
       <c r="A129" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-14</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B129" s="32">
@@ -13282,13 +14363,13 @@
         <v/>
       </c>
       <c r="D129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G129" s="23" t="n">
         <v>0</v>
@@ -13298,7 +14379,7 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-15</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B130" s="32">
@@ -13310,13 +14391,13 @@
         <v/>
       </c>
       <c r="D130" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G130" s="23" t="n">
         <v>0</v>
@@ -13326,7 +14407,7 @@
     <row r="131">
       <c r="A131" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-16</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B131" s="32">
@@ -13338,13 +14419,13 @@
         <v/>
       </c>
       <c r="D131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G131" s="23" t="n">
         <v>0</v>
@@ -13354,7 +14435,7 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B132" s="32">
@@ -13382,7 +14463,7 @@
     <row r="133">
       <c r="A133" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B133" s="32">
@@ -13410,7 +14491,7 @@
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B134" s="32">
@@ -13428,7 +14509,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G134" s="23" t="n">
         <v>0</v>
@@ -13438,7 +14519,7 @@
     <row r="135">
       <c r="A135" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B135" s="32">
@@ -13456,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G135" s="23" t="n">
         <v>0</v>
@@ -13466,7 +14547,7 @@
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B136" s="32">
@@ -13494,7 +14575,7 @@
     <row r="137">
       <c r="A137" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B137" s="32">
@@ -13512,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G137" s="23" t="n">
         <v>0</v>
@@ -13522,7 +14603,7 @@
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B138" s="32">
@@ -13550,7 +14631,7 @@
     <row r="139">
       <c r="A139" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B139" s="32">
@@ -13562,13 +14643,13 @@
         <v/>
       </c>
       <c r="D139" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G139" s="23" t="n">
         <v>0</v>
@@ -13578,7 +14659,7 @@
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B140" s="32">
@@ -13590,13 +14671,13 @@
         <v/>
       </c>
       <c r="D140" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F140" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="23" t="n">
         <v>0</v>
@@ -13606,7 +14687,7 @@
     <row r="141">
       <c r="A141" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B141" s="32">
@@ -13618,13 +14699,13 @@
         <v/>
       </c>
       <c r="D141" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G141" s="23" t="n">
         <v>0</v>
@@ -13634,7 +14715,7 @@
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B142" s="32">
@@ -13646,13 +14727,13 @@
         <v/>
       </c>
       <c r="D142" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" s="23" t="n">
         <v>0</v>
@@ -13662,7 +14743,7 @@
     <row r="143">
       <c r="A143" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B143" s="32">
@@ -13674,13 +14755,13 @@
         <v/>
       </c>
       <c r="D143" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E143" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" s="23" t="n">
         <v>0</v>
@@ -13690,7 +14771,7 @@
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B144" s="32">
@@ -13702,13 +14783,13 @@
         <v/>
       </c>
       <c r="D144" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" s="23" t="n">
         <v>0</v>
@@ -13718,7 +14799,7 @@
     <row r="145">
       <c r="A145" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B145" s="32">
@@ -13730,13 +14811,13 @@
         <v/>
       </c>
       <c r="D145" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="23" t="n">
         <v>0</v>
@@ -13746,7 +14827,7 @@
     <row r="146">
       <c r="A146" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B146" s="32">
@@ -13758,13 +14839,13 @@
         <v/>
       </c>
       <c r="D146" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E146" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" s="23" t="n">
         <v>0</v>
@@ -13774,7 +14855,7 @@
     <row r="147">
       <c r="A147" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B147" s="32">
@@ -13786,13 +14867,13 @@
         <v/>
       </c>
       <c r="D147" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F147" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G147" s="23" t="n">
         <v>0</v>
@@ -13802,7 +14883,7 @@
     <row r="148">
       <c r="A148" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B148" s="32">
@@ -13814,13 +14895,13 @@
         <v/>
       </c>
       <c r="D148" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F148" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" s="23" t="n">
         <v>0</v>
@@ -13830,7 +14911,7 @@
     <row r="149">
       <c r="A149" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B149" s="32">
@@ -13842,13 +14923,13 @@
         <v/>
       </c>
       <c r="D149" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G149" s="23" t="n">
         <v>0</v>
@@ -13858,7 +14939,7 @@
     <row r="150">
       <c r="A150" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B150" s="32">
@@ -13870,13 +14951,13 @@
         <v/>
       </c>
       <c r="D150" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" s="23" t="n">
         <v>0</v>
@@ -13886,7 +14967,7 @@
     <row r="151">
       <c r="A151" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B151" s="32">
@@ -13898,13 +14979,13 @@
         <v/>
       </c>
       <c r="D151" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F151" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" s="23" t="n">
         <v>0</v>
@@ -13914,7 +14995,7 @@
     <row r="152">
       <c r="A152" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B152" s="32">
@@ -13926,13 +15007,13 @@
         <v/>
       </c>
       <c r="D152" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F152" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" s="23" t="n">
         <v>0</v>
@@ -13942,7 +15023,7 @@
     <row r="153">
       <c r="A153" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B153" s="32">
@@ -13954,13 +15035,13 @@
         <v/>
       </c>
       <c r="D153" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F153" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" s="23" t="n">
         <v>0</v>
@@ -13970,7 +15051,7 @@
     <row r="154">
       <c r="A154" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B154" s="32">
@@ -13982,13 +15063,13 @@
         <v/>
       </c>
       <c r="D154" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F154" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="23" t="n">
         <v>0</v>
@@ -13998,7 +15079,7 @@
     <row r="155">
       <c r="A155" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B155" s="32">
@@ -14026,7 +15107,7 @@
     <row r="156">
       <c r="A156" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B156" s="32">
@@ -14054,7 +15135,7 @@
     <row r="157">
       <c r="A157" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-PRIV-03</t>
         </is>
       </c>
       <c r="B157" s="32">
@@ -14072,7 +15153,7 @@
         <v>0</v>
       </c>
       <c r="F157" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G157" s="23" t="n">
         <v>0</v>
@@ -14082,7 +15163,7 @@
     <row r="158">
       <c r="A158" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-PRIV-04</t>
         </is>
       </c>
       <c r="B158" s="32">
@@ -14100,7 +15181,7 @@
         <v>0</v>
       </c>
       <c r="F158" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G158" s="23" t="n">
         <v>0</v>
@@ -14110,7 +15191,7 @@
     <row r="159">
       <c r="A159" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-PRIV-05</t>
         </is>
       </c>
       <c r="B159" s="32">
@@ -14138,7 +15219,7 @@
     <row r="160">
       <c r="A160" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-06</t>
         </is>
       </c>
       <c r="B160" s="32">
@@ -14156,7 +15237,7 @@
         <v>0</v>
       </c>
       <c r="F160" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G160" s="23" t="n">
         <v>0</v>
@@ -14166,7 +15247,7 @@
     <row r="161">
       <c r="A161" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-PRIV-07</t>
         </is>
       </c>
       <c r="B161" s="32">
@@ -14190,6 +15271,650 @@
         <v>0</v>
       </c>
       <c r="H161" s="22" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-08</t>
+        </is>
+      </c>
+      <c r="B162" s="32">
+        <f>IF(E162&gt;0,"FAIL",IF(F162&gt;0,"RED",IF(D162&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C162" s="23">
+        <f>SUM(D162:G162)</f>
+        <v/>
+      </c>
+      <c r="D162" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G162" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="22" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-09</t>
+        </is>
+      </c>
+      <c r="B163" s="32">
+        <f>IF(E163&gt;0,"FAIL",IF(F163&gt;0,"RED",IF(D163&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C163" s="23">
+        <f>SUM(D163:G163)</f>
+        <v/>
+      </c>
+      <c r="D163" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="22" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-10</t>
+        </is>
+      </c>
+      <c r="B164" s="32">
+        <f>IF(E164&gt;0,"FAIL",IF(F164&gt;0,"RED",IF(D164&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C164" s="23">
+        <f>SUM(D164:G164)</f>
+        <v/>
+      </c>
+      <c r="D164" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="22" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-11</t>
+        </is>
+      </c>
+      <c r="B165" s="32">
+        <f>IF(E165&gt;0,"FAIL",IF(F165&gt;0,"RED",IF(D165&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C165" s="23">
+        <f>SUM(D165:G165)</f>
+        <v/>
+      </c>
+      <c r="D165" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="22" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-12</t>
+        </is>
+      </c>
+      <c r="B166" s="32">
+        <f>IF(E166&gt;0,"FAIL",IF(F166&gt;0,"RED",IF(D166&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C166" s="23">
+        <f>SUM(D166:G166)</f>
+        <v/>
+      </c>
+      <c r="D166" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="22" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-13</t>
+        </is>
+      </c>
+      <c r="B167" s="32">
+        <f>IF(E167&gt;0,"FAIL",IF(F167&gt;0,"RED",IF(D167&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C167" s="23">
+        <f>SUM(D167:G167)</f>
+        <v/>
+      </c>
+      <c r="D167" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="22" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-14</t>
+        </is>
+      </c>
+      <c r="B168" s="32">
+        <f>IF(E168&gt;0,"FAIL",IF(F168&gt;0,"RED",IF(D168&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C168" s="23">
+        <f>SUM(D168:G168)</f>
+        <v/>
+      </c>
+      <c r="D168" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="22" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-15</t>
+        </is>
+      </c>
+      <c r="B169" s="32">
+        <f>IF(E169&gt;0,"FAIL",IF(F169&gt;0,"RED",IF(D169&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C169" s="23">
+        <f>SUM(D169:G169)</f>
+        <v/>
+      </c>
+      <c r="D169" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="22" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-16</t>
+        </is>
+      </c>
+      <c r="B170" s="32">
+        <f>IF(E170&gt;0,"FAIL",IF(F170&gt;0,"RED",IF(D170&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C170" s="23">
+        <f>SUM(D170:G170)</f>
+        <v/>
+      </c>
+      <c r="D170" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G170" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="22" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-17</t>
+        </is>
+      </c>
+      <c r="B171" s="32">
+        <f>IF(E171&gt;0,"FAIL",IF(F171&gt;0,"RED",IF(D171&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C171" s="23">
+        <f>SUM(D171:G171)</f>
+        <v/>
+      </c>
+      <c r="D171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="22" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-18</t>
+        </is>
+      </c>
+      <c r="B172" s="32">
+        <f>IF(E172&gt;0,"FAIL",IF(F172&gt;0,"RED",IF(D172&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C172" s="23">
+        <f>SUM(D172:G172)</f>
+        <v/>
+      </c>
+      <c r="D172" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G172" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="22" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-19</t>
+        </is>
+      </c>
+      <c r="B173" s="32">
+        <f>IF(E173&gt;0,"FAIL",IF(F173&gt;0,"RED",IF(D173&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C173" s="23">
+        <f>SUM(D173:G173)</f>
+        <v/>
+      </c>
+      <c r="D173" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="22" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-20</t>
+        </is>
+      </c>
+      <c r="B174" s="32">
+        <f>IF(E174&gt;0,"FAIL",IF(F174&gt;0,"RED",IF(D174&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C174" s="23">
+        <f>SUM(D174:G174)</f>
+        <v/>
+      </c>
+      <c r="D174" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="22" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-21</t>
+        </is>
+      </c>
+      <c r="B175" s="32">
+        <f>IF(E175&gt;0,"FAIL",IF(F175&gt;0,"RED",IF(D175&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C175" s="23">
+        <f>SUM(D175:G175)</f>
+        <v/>
+      </c>
+      <c r="D175" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="22" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-22</t>
+        </is>
+      </c>
+      <c r="B176" s="32">
+        <f>IF(E176&gt;0,"FAIL",IF(F176&gt;0,"RED",IF(D176&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C176" s="23">
+        <f>SUM(D176:G176)</f>
+        <v/>
+      </c>
+      <c r="D176" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="22" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-23</t>
+        </is>
+      </c>
+      <c r="B177" s="32">
+        <f>IF(E177&gt;0,"FAIL",IF(F177&gt;0,"RED",IF(D177&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C177" s="23">
+        <f>SUM(D177:G177)</f>
+        <v/>
+      </c>
+      <c r="D177" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="22" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-24</t>
+        </is>
+      </c>
+      <c r="B178" s="32">
+        <f>IF(E178&gt;0,"FAIL",IF(F178&gt;0,"RED",IF(D178&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C178" s="23">
+        <f>SUM(D178:G178)</f>
+        <v/>
+      </c>
+      <c r="D178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="22" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-01</t>
+        </is>
+      </c>
+      <c r="B179" s="32">
+        <f>IF(E179&gt;0,"FAIL",IF(F179&gt;0,"RED",IF(D179&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C179" s="23">
+        <f>SUM(D179:G179)</f>
+        <v/>
+      </c>
+      <c r="D179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="22" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B180" s="32">
+        <f>IF(E180&gt;0,"FAIL",IF(F180&gt;0,"RED",IF(D180&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C180" s="23">
+        <f>SUM(D180:G180)</f>
+        <v/>
+      </c>
+      <c r="D180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="22" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B181" s="32">
+        <f>IF(E181&gt;0,"FAIL",IF(F181&gt;0,"RED",IF(D181&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C181" s="23">
+        <f>SUM(D181:G181)</f>
+        <v/>
+      </c>
+      <c r="D181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="22" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B182" s="32">
+        <f>IF(E182&gt;0,"FAIL",IF(F182&gt;0,"RED",IF(D182&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C182" s="23">
+        <f>SUM(D182:G182)</f>
+        <v/>
+      </c>
+      <c r="D182" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="22" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B183" s="32">
+        <f>IF(E183&gt;0,"FAIL",IF(F183&gt;0,"RED",IF(D183&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C183" s="23">
+        <f>SUM(D183:G183)</f>
+        <v/>
+      </c>
+      <c r="D183" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="22" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B184" s="32">
+        <f>IF(E184&gt;0,"FAIL",IF(F184&gt;0,"RED",IF(D184&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C184" s="23">
+        <f>SUM(D184:G184)</f>
+        <v/>
+      </c>
+      <c r="D184" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" s="22" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B600">
@@ -14220,7 +15945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14979,6 +16704,48 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-25 18:17</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>fix/attack-sc01-sc02</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>0ca30b2</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>181</v>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>89</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>357</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K20" s="36">
+        <f>IFERROR(E20/(E20+F20+G20),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="실행이력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$20</f>
+              <f>'실행이력'!$A$4:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$20</f>
+              <f>'실행이력'!$E$4:$E$21</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$20</f>
+              <f>'실행이력'!$A$4:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$20</f>
+              <f>'실행이력'!$F$4:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$20</f>
+              <f>'실행이력'!$A$4:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$20</f>
+              <f>'실행이력'!$G$4:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -2146,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2566,22 +2566,22 @@
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>IT-01</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D12" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 동일 아이디 2회 요청</t>
+          <t>브라우저 E2E: 알고리즘을 골라 신청하면 성공 안내와 함께 내 신청 목록에 나타남</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>1차 201, 2차 409(DUPLICATE_USERNAME), users 1건</t>
+          <t>성공 메시지 표시, 목록에 알고리즘·'접수 대기' 배지 행 1건, 화면 이동 없음</t>
         </is>
       </c>
       <c r="H12" s="28" t="inlineStr">
@@ -2613,37 +2613,37 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>IT-02</t>
+          <t>ST-04-N1</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 정상 가입 응답</t>
+          <t>브라우저 E2E: 같은 알고리즘을 진행 중에 다시 신청</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>201, 응답에 id/username/user_type, 비밀번호·해시 미포함, DB 에는 bcrypt 해시</t>
+          <t>오류 안내 표시, 목록은 1건 그대로</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
@@ -2660,22 +2660,22 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>IT-03</t>
+          <t>ST-04-N2</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 잘못된 입력</t>
+          <t>브라우저 E2E: 알고리즘을 고르지 않고 신청</t>
         </is>
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR, users 0건</t>
+          <t>서버에 요청하지 않고 선택 안내 표시, 목록 변화 없음</t>
         </is>
       </c>
       <c r="H14" s="28" t="inlineStr">
@@ -2707,37 +2707,37 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>IT-04</t>
+          <t>ST-04-N3</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/signup: 본문 없음/JSON 아님</t>
+          <t>브라우저 E2E: 대시보드 → 신청 화면 → 신청 → 대시보드 최근 신청 반영</t>
         </is>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>400 (500 이 아님)</t>
+          <t>'+ CAVP 시험 신청' 클릭으로 이동, 신청 후 대시보드 최근 신청·진행중 KPI 에 반영</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
@@ -2754,37 +2754,37 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>IT-05</t>
+          <t>ST-04-N4</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D16" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F16" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: 로그인 후 세션 유지</t>
+          <t>브라우저 E2E: 로그인하지 않고 신청 화면에 접근</t>
         </is>
       </c>
       <c r="G16" s="29" t="inlineStr">
         <is>
-          <t>200 → GET /api/auth/me 가 본인 정보 반환</t>
+          <t>로그인 화면으로 이동</t>
         </is>
       </c>
       <c r="H16" s="28" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>IT-06</t>
+          <t>IT-01</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: 세션 쿠키 보안 속성</t>
+          <t>POST /api/auth/signup: 동일 아이디 2회 요청</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>Set-Cookie 에 HttpOnly 와 SameSite 포함</t>
+          <t>1차 201, 2차 409(DUPLICATE_USERNAME), users 1건</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>IT-07</t>
+          <t>IT-02</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: 실패 시 401, 계정 존재 여부 비노출</t>
+          <t>POST /api/auth/signup: 정상 가입 응답</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>없는 아이디/틀린 비밀번호의 응답 본문 동일, 이후에도 /me 는 401</t>
+          <t>201, 응답에 id/username/user_type, 비밀번호·해시 미포함, DB 에는 bcrypt 해시</t>
         </is>
       </c>
       <c r="H18" s="28" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>IT-08</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -2915,17 +2915,17 @@
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/login: SQL 인젝션/빈 값</t>
+          <t>POST /api/auth/signup: 잘못된 입력</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>401 또는 400, 500 없음</t>
+          <t>400 VALIDATION_ERROR, users 0건</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>IT-09</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>POST /api/auth/logout: 세션 종료</t>
+          <t>POST /api/auth/signup: 본문 없음/JSON 아님</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>204 이후 /me 401, 재로그아웃도 오류 없음</t>
+          <t>400 (500 이 아님)</t>
         </is>
       </c>
       <c r="H20" s="28" t="inlineStr">
@@ -2989,7 +2989,7 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>IT-10</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>세션: 서로 다른 클라이언트 격리 / 위조 쿠키</t>
+          <t>POST /api/auth/login: 로그인 후 세션 유지</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>A 로그인이 B 에 영향 없음, 임의 쿠키는 401</t>
+          <t>200 → GET /api/auth/me 가 본인 정보 반환</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>IT-11</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D22" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>보호 API: 미로그인 호출</t>
+          <t>POST /api/auth/login: 세션 쿠키 보안 속성</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>401 반환, 어떤 레코드도 생성되지 않음</t>
+          <t>Set-Cookie 에 HttpOnly 와 SameSite 포함</t>
         </is>
       </c>
       <c r="H22" s="28" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>IT-12</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
@@ -3098,22 +3098,22 @@
       </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>오류 응답 형식 일관성</t>
+          <t>POST /api/auth/login: 실패 시 401, 계정 존재 여부 비노출</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>존재하지 않는 /api 경로 404, 잘못된 메서드 405 모두 JSON {error:{code,message}}</t>
+          <t>없는 아이디/틀린 비밀번호의 응답 본문 동일, 이후에도 /me 는 401</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>IT-13</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
@@ -3140,27 +3140,27 @@
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>POST /api/privacy/process: 가명/익명 각 1회</t>
+          <t>POST /api/auth/login: SQL 인젝션/빈 값</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>level별 personal_info 가 올바른 값으로 저장 (가명=PSN-…, 익명=None/'익명')</t>
+          <t>401 또는 400, 500 없음</t>
         </is>
       </c>
       <c r="H24" s="28" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>IT-14</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
@@ -3187,27 +3187,27 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
-          <t>가명·익명 처리: 원본 개인정보 비저장·비노출</t>
+          <t>POST /api/auth/logout: 세션 종료</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
         <is>
-          <t>응답과 DB 전 테이블 어디에도 '홍길동' / '1990-04-12' 없음</t>
+          <t>204 이후 /me 401, 재로그아웃도 오류 없음</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
@@ -3224,7 +3224,7 @@
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>IT-15</t>
+          <t>IT-10</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
@@ -3234,27 +3234,27 @@
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>POST /api/privacy/process: 잘못된 입력</t>
+          <t>세션: 서로 다른 클라이언트 격리 / 위조 쿠키</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR, personal_info 0건</t>
+          <t>A 로그인이 B 에 영향 없음, 임의 쿠키는 401</t>
         </is>
       </c>
       <c r="H26" s="28" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>IT-16</t>
+          <t>IT-11</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
@@ -3281,27 +3281,27 @@
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>GET /api/privacy/me: 처리 전 404, 처리 후 200</t>
+          <t>보호 API: 미로그인 호출</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>404 NOT_FOUND → 200 {level, display, pseudonym_id}</t>
+          <t>401 반환, 어떤 레코드도 생성되지 않음</t>
         </is>
       </c>
       <c r="H27" s="28" t="inlineStr">
@@ -3318,7 +3318,7 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>IT-17</t>
+          <t>IT-12</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
@@ -3328,27 +3328,27 @@
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>개인정보 처리 결과는 본인 것만 조회</t>
+          <t>오류 응답 형식 일관성</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>A 의 처리 결과가 B 의 /privacy/me 에 노출되지 않음</t>
+          <t>존재하지 않는 /api 경로 404, 잘못된 메서드 405 모두 JSON {error:{code,message}}</t>
         </is>
       </c>
       <c r="H28" s="28" t="inlineStr">
@@ -3365,7 +3365,7 @@
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>IT-18</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>POST /api/cavp/applications → GET 목록</t>
+          <t>POST /api/privacy/process: 가명/익명 각 1회</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>201 status=submitted, 목록 응답에 방금 신청 포함</t>
+          <t>level별 personal_info 가 올바른 값으로 저장 (가명=PSN-…, 익명=None/'익명')</t>
         </is>
       </c>
       <c r="H29" s="28" t="inlineStr">
@@ -3412,7 +3412,7 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>IT-19</t>
+          <t>IT-14</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
-          <t>신청 입력 오류/중복</t>
+          <t>가명·익명 처리: 원본 개인정보 비저장·비노출</t>
         </is>
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>미허용 알고리즘 400, 진행 중 중복 409(DUPLICATE_APPLICATION), 레코드 증가 없음</t>
+          <t>응답과 DB 전 테이블 어디에도 '홍길동' / '1990-04-12' 없음</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>IT-20</t>
+          <t>IT-15</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
@@ -3469,27 +3469,27 @@
       </c>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>신청 목록: 상태 필터·페이지네이션 쿼리</t>
+          <t>POST /api/privacy/process: 잘못된 입력</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>status/page/per_page 가 반영되고 total 이 필터 기준</t>
+          <t>400 VALIDATION_ERROR, personal_info 0건</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>IT-21</t>
+          <t>IT-16</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
@@ -3516,27 +3516,27 @@
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>신청 목록: 잘못된 쿼리 파라미터</t>
+          <t>GET /api/privacy/me: 처리 전 404, 처리 후 200</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>page=0, per_page=51, per_page=abc, status=weird → 400</t>
+          <t>404 NOT_FOUND → 200 {level, display, pseudonym_id}</t>
         </is>
       </c>
       <c r="H32" s="28" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
         <is>
-          <t>IT-22</t>
+          <t>IT-17</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>신청 조회 격리: 타인 신청 목록/상세</t>
+          <t>개인정보 처리 결과는 본인 것만 조회</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>목록에 타인 건 없음, 타인 상세 403 FORBIDDEN, 없는 id 404</t>
+          <t>A 의 처리 결과가 B 의 /privacy/me 에 노출되지 않음</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
@@ -3600,7 +3600,7 @@
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>IT-23</t>
+          <t>IT-18</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>PATCH /api/cavp/applications/{id}/status: 기관 심사 흐름</t>
+          <t>POST /api/cavp/applications → GET 목록</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>submitted→reviewing→approved 200, 잘못된 전이 409 INVALID_TRANSITION, 기관은 타인 신청 상세 조회 가능</t>
+          <t>201 status=submitted, 목록 응답에 방금 신청 포함</t>
         </is>
       </c>
       <c r="H34" s="28" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>IT-24</t>
+          <t>IT-19</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
@@ -3667,17 +3667,17 @@
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>PATCH status: 기관이 아닌 사용자 / 알 수 없는 상태</t>
+          <t>신청 입력 오류/중복</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>403 FORBIDDEN / 400 VALIDATION_ERROR, 상태 불변</t>
+          <t>미허용 알고리즘 400, 진행 중 중복 409(DUPLICATE_APPLICATION), 레코드 증가 없음</t>
         </is>
       </c>
       <c r="H35" s="28" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>IT-25</t>
+          <t>IT-20</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>POST /api/cavp/applications/{id}/certificate: 승인 건 발급</t>
+          <t>신청 목록: 상태 필터·페이지네이션 쿼리</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>201, tamper_status=normal, 소유자의 /api/certificates 목록·상세에 노출</t>
+          <t>status/page/per_page 가 반영되고 total 이 필터 기준</t>
         </is>
       </c>
       <c r="H36" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I36" s="30" t="n"/>
@@ -3741,7 +3741,7 @@
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>IT-26</t>
+          <t>IT-21</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>검증서 발급 오류 경로</t>
+          <t>신청 목록: 잘못된 쿼리 파라미터</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>미승인 신청 409, 중복 발급 409, 비기관 403, 잘못된 cert_type 400, 레코드 증가 없음</t>
+          <t>page=0, per_page=51, per_page=abc, status=weird → 400</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I37" s="30" t="n"/>
@@ -3788,7 +3788,7 @@
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>IT-27</t>
+          <t>IT-22</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
@@ -3798,32 +3798,32 @@
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>GET /api/certificates/{id}/verify: 정상 건 / 위변조 의심 건</t>
+          <t>신청 조회 격리: 타인 신청 목록/상세</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>tamper_status 값에 따라 판정 필드 일치(normal / suspected)</t>
+          <t>목록에 타인 건 없음, 타인 상세 403 FORBIDDEN, 없는 id 404</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I38" s="30" t="n"/>
@@ -3835,7 +3835,7 @@
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
         <is>
-          <t>IT-28</t>
+          <t>IT-23</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
@@ -3845,32 +3845,32 @@
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>검증서 파일 삭제 후 verify</t>
+          <t>PATCH /api/cavp/applications/{id}/status: 기관 심사 흐름</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>200 + suspected (서버 오류 500 아님)</t>
+          <t>submitted→reviewing→approved 200, 잘못된 전이 409 INVALID_TRANSITION, 기관은 타인 신청 상세 조회 가능</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I39" s="30" t="n"/>
@@ -3882,7 +3882,7 @@
     <row r="40">
       <c r="A40" s="27" t="inlineStr">
         <is>
-          <t>IT-29</t>
+          <t>IT-24</t>
         </is>
       </c>
       <c r="B40" s="27" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E40" s="27" t="inlineStr">
@@ -3907,17 +3907,17 @@
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>검증서 조회 격리</t>
+          <t>PATCH status: 기관이 아닌 사용자 / 알 수 없는 상태</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>타인의 검증서 상세·verify 403, 목록에 타인 건 없음, 없는 id 404</t>
+          <t>403 FORBIDDEN / 400 VALIDATION_ERROR, 상태 불변</t>
         </is>
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I40" s="30" t="n"/>
@@ -3929,7 +3929,7 @@
     <row r="41">
       <c r="A41" s="27" t="inlineStr">
         <is>
-          <t>IT-30</t>
+          <t>IT-25</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
@@ -3939,27 +3939,27 @@
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>검증서 응답 보안: 서버 파일 경로·해시 원문 비노출</t>
+          <t>POST /api/cavp/applications/{id}/certificate: 승인 건 발급</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>응답 본문에 저장 디렉터리 경로 없음</t>
+          <t>201, tamper_status=normal, 소유자의 /api/certificates 목록·상세에 노출</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="42">
       <c r="A42" s="27" t="inlineStr">
         <is>
-          <t>IT-31</t>
+          <t>IT-26</t>
         </is>
       </c>
       <c r="B42" s="27" t="inlineStr">
@@ -3986,27 +3986,27 @@
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>FR-14</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>E2E: 가입→로그인→가명처리→신청→심사→발급→조회→변조탐지</t>
+          <t>검증서 발급 오류 경로</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>전 단계 성공, 변조 후 suspected</t>
+          <t>미승인 신청 409, 중복 발급 409, 비기관 403, 잘못된 cert_type 400, 레코드 증가 없음</t>
         </is>
       </c>
       <c r="H42" s="28" t="inlineStr">
@@ -4023,7 +4023,7 @@
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>IT-32</t>
+          <t>IT-27</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D43" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>초기데이터(seed) 적재 후 데모 계정으로 화면 데이터 조회</t>
+          <t>GET /api/certificates/{id}/verify: 정상 건 / 위변조 의심 건</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>demo_individual 로그인 → 신청/검증서 목록 존재, 위변조 의심 건 1건 확인(기관 계정)</t>
+          <t>tamper_status 값에 따라 판정 필드 일치(normal / suspected)</t>
         </is>
       </c>
       <c r="H43" s="28" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="44">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>IT-33</t>
+          <t>IT-28</t>
         </is>
       </c>
       <c r="B44" s="27" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>GET /api/dashboard: 로그인 사용자의 요약 구조</t>
+          <t>검증서 파일 삭제 후 verify</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>200, scope/user/applications/certificates/privacy/recent_applications/notifications 키 포함</t>
+          <t>200 + suspected (서버 오류 500 아님)</t>
         </is>
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I44" s="30" t="n"/>
@@ -4117,7 +4117,7 @@
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>IT-34</t>
+          <t>IT-29</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D45" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
@@ -4142,17 +4142,17 @@
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>GET /api/dashboard: 비로그인 접근</t>
+          <t>검증서 조회 격리</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>401 AUTHENTICATION_FAILED</t>
+          <t>타인의 검증서 상세·verify 403, 목록에 타인 건 없음, 없는 id 404</t>
         </is>
       </c>
       <c r="H45" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I45" s="30" t="n"/>
@@ -4164,7 +4164,7 @@
     <row r="46">
       <c r="A46" s="27" t="inlineStr">
         <is>
-          <t>IT-35</t>
+          <t>IT-30</t>
         </is>
       </c>
       <c r="B46" s="27" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E46" s="27" t="inlineStr">
@@ -4189,17 +4189,17 @@
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>GET /api/dashboard: 사용자 간 데이터 격리</t>
+          <t>검증서 응답 보안: 서버 파일 경로·해시 원문 비노출</t>
         </is>
       </c>
       <c r="G46" s="29" t="inlineStr">
         <is>
-          <t>A 의 신청/검증서 건수가 B 의 응답에 포함되지 않음</t>
+          <t>응답 본문에 저장 디렉터리 경로 없음</t>
         </is>
       </c>
       <c r="H46" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I46" s="30" t="n"/>
@@ -4211,7 +4211,7 @@
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>IT-36</t>
+          <t>IT-31</t>
         </is>
       </c>
       <c r="B47" s="27" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-14</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E47" s="27" t="inlineStr">
@@ -4236,17 +4236,17 @@
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>GET /api/dashboard: 기관 사용자는 전체 범위</t>
+          <t>E2E: 가입→로그인→가명처리→신청→심사→발급→조회→변조탐지</t>
         </is>
       </c>
       <c r="G47" s="29" t="inlineStr">
         <is>
-          <t>scope=all, 타 사용자 신청도 집계에 포함</t>
+          <t>전 단계 성공, 변조 후 suspected</t>
         </is>
       </c>
       <c r="H47" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I47" s="30" t="n"/>
@@ -4258,7 +4258,7 @@
     <row r="48">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>IT-37</t>
+          <t>IT-32</t>
         </is>
       </c>
       <c r="B48" s="27" t="inlineStr">
@@ -4268,32 +4268,32 @@
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>GET /api/dashboard: 비밀번호/해시 비노출</t>
+          <t>초기데이터(seed) 적재 후 데모 계정으로 화면 데이터 조회</t>
         </is>
       </c>
       <c r="G48" s="29" t="inlineStr">
         <is>
-          <t>응답 본문에 password / hash 문자열 없음</t>
+          <t>demo_individual 로그인 → 신청/검증서 목록 존재, 위변조 의심 건 1건 확인(기관 계정)</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I48" s="30" t="n"/>
@@ -4305,7 +4305,7 @@
     <row r="49">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>IT-38</t>
+          <t>IT-33</t>
         </is>
       </c>
       <c r="B49" s="27" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>GET /api/dashboard: 데이터 변경 즉시 반영</t>
+          <t>GET /api/dashboard: 로그인 사용자의 요약 구조</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>신청·위변조 의심 검증서 추가 후 재호출 시 건수·알림 증가</t>
+          <t>200, scope/user/applications/certificates/privacy/recent_applications/notifications 키 포함</t>
         </is>
       </c>
       <c r="H49" s="28" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>IT-39</t>
+          <t>IT-34</t>
         </is>
       </c>
       <c r="B50" s="27" t="inlineStr">
@@ -4372,17 +4372,17 @@
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>GET /dashboard 페이지: 접근 제어와 화면 요소</t>
+          <t>GET /api/dashboard: 비로그인 접근</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>비로그인 302 → /, 로그인 시 #welcome/#kpi-in-progress/#recent-body/#notifications/#logout 포함</t>
+          <t>401 AUTHENTICATION_FAILED</t>
         </is>
       </c>
       <c r="H50" s="28" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="51">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>IT-40</t>
+          <t>IT-35</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
@@ -4419,17 +4419,17 @@
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>POST /api/dashboard: 허용되지 않은 메서드</t>
+          <t>GET /api/dashboard: 사용자 간 데이터 격리</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>405 METHOD_NOT_ALLOWED JSON</t>
+          <t>A 의 신청/검증서 건수가 B 의 응답에 포함되지 않음</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-01</t>
+          <t>IT-36</t>
         </is>
       </c>
       <c r="B52" s="27" t="inlineStr">
@@ -4456,27 +4456,27 @@
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t>최대 길이(64자) 비밀번호에서 마지막 글자만 다른 비밀번호로 로그인</t>
+          <t>GET /api/dashboard: 기관 사용자는 전체 범위</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
-          <t>다른 비밀번호는 로그인 실패(401), 원래 비밀번호는 성공</t>
+          <t>scope=all, 타 사용자 신청도 집계에 포함</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-02</t>
+          <t>IT-37</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D53" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E53" s="27" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>한글 비밀번호의 바이트 한도(글자 수는 64자 이내지만 바이트는 72 초과)</t>
+          <t>GET /api/dashboard: 비밀번호/해시 비노출</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
         <is>
-          <t>잘려서 같은 비밀번호로 취급되지 않는다(가입 거부 또는 로그인 401)</t>
+          <t>응답 본문에 password / hash 문자열 없음</t>
         </is>
       </c>
       <c r="H53" s="28" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="54">
       <c r="A54" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-03</t>
+          <t>IT-38</t>
         </is>
       </c>
       <c r="B54" s="27" t="inlineStr">
@@ -4550,27 +4550,27 @@
       </c>
       <c r="C54" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>NUL 문자(\x00)가 든 비밀번호로 가입/로그인</t>
+          <t>GET /api/dashboard: 데이터 변경 즉시 반영</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>서버 오류(500) 없이 가입 400, 로그인 401</t>
+          <t>신청·위변조 의심 검증서 추가 후 재호출 시 건수·알림 증가</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-04</t>
+          <t>IT-39</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
@@ -4597,27 +4597,27 @@
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>유니코드 숫자(아라비아-인도 숫자 등)만으로 '숫자 1자 이상' 규칙 통과 시도</t>
+          <t>GET /dashboard 페이지: 접근 제어와 화면 요소</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>ASCII 숫자가 없으면 400</t>
+          <t>비로그인 302 → /, 로그인 시 #welcome/#kpi-in-progress/#recent-body/#notifications/#logout 포함</t>
         </is>
       </c>
       <c r="H55" s="28" t="inlineStr">
@@ -4634,7 +4634,7 @@
     <row r="56">
       <c r="A56" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-05</t>
+          <t>IT-40</t>
         </is>
       </c>
       <c r="B56" s="27" t="inlineStr">
@@ -4644,27 +4644,27 @@
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>아이디 변형 입력: 줄바꿈·공백·전각 문자·제로폭 문자·길이 초과/미달</t>
+          <t>POST /api/dashboard: 허용되지 않은 메서드</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>모두 400, 사용자 생성 없음</t>
+          <t>405 METHOD_NOT_ALLOWED JSON</t>
         </is>
       </c>
       <c r="H56" s="28" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="57">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-06</t>
+          <t>IT-41</t>
         </is>
       </c>
       <c r="B57" s="27" t="inlineStr">
@@ -4691,27 +4691,27 @@
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D57" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E57" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>기관 코드에 비정상적으로 긴 문자열(1만 자)과 제어 문자</t>
+          <t>GET /cavp/apply 페이지: 접근 제어와 화면 요소</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>설계서 VARCHAR(50) 한도를 넘으면 400, 사용자 생성 없음</t>
+          <t>비로그인 302 → /, 로그인 시 #algorithm/#submit-app/#apply-msg/#my-apps-body/#logout 포함</t>
         </is>
       </c>
       <c r="H57" s="28" t="inlineStr">
@@ -4728,7 +4728,7 @@
     <row r="58">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-07</t>
+          <t>IT-42</t>
         </is>
       </c>
       <c r="B58" s="27" t="inlineStr">
@@ -4738,27 +4738,27 @@
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>SQL 인젝션 문자열을 아이디/비밀번호에 입력</t>
+          <t>대시보드의 신청 버튼/메뉴가 신청 화면으로 연결</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>가입 400, 로그인 401, users 테이블 변화 없음</t>
+          <t>#new-app 이 /cavp/apply 로 이동, 사이드 메뉴에 /cavp/apply 링크</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="59">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-08</t>
+          <t>IT-43</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
@@ -4785,27 +4785,27 @@
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D59" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>필드 타입 혼동(문자열 자리에 배열·객체·숫자·null)</t>
+          <t>GET /api/cavp/algorithms: 로그인 필요 + 허용 알고리즘 목록</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>서버 오류 없이 가입 400 / 로그인 401</t>
+          <t>비로그인 401, 로그인 시 서비스의 ALGORITHMS 와 동일</t>
         </is>
       </c>
       <c r="H59" s="28" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="60">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-09</t>
+          <t>IT-ATK-01</t>
         </is>
       </c>
       <c r="B60" s="27" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>깊게 중첩된 JSON 본문(3만 단계, 크기 제한 이내)</t>
+          <t>최대 길이(64자) 비밀번호에서 마지막 글자만 다른 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>서버 오류(500) 없이 400</t>
+          <t>다른 비밀번호는 로그인 실패(401), 원래 비밀번호는 성공</t>
         </is>
       </c>
       <c r="H60" s="28" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="61">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-10</t>
+          <t>IT-ATK-02</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="E61" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F61" s="29" t="inlineStr">
         <is>
-          <t>JSON이 아닌 요청(form, 빈 본문, 배열, 문자열)</t>
+          <t>한글 비밀번호의 바이트 한도(글자 수는 64자 이내지만 바이트는 72 초과)</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>모두 400 JSON 오류 형식</t>
+          <t>잘려서 같은 비밀번호로 취급되지 않는다(가입 거부 또는 로그인 401)</t>
         </is>
       </c>
       <c r="H61" s="28" t="inlineStr">
@@ -4916,7 +4916,7 @@
     <row r="62">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-11</t>
+          <t>IT-ATK-03</t>
         </is>
       </c>
       <c r="B62" s="27" t="inlineStr">
@@ -4936,17 +4936,17 @@
       </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>2MB 크기의 요청 본문</t>
+          <t>NUL 문자(\x00)가 든 비밀번호로 가입/로그인</t>
         </is>
       </c>
       <c r="G62" s="29" t="inlineStr">
         <is>
-          <t>본문 크기 제한으로 413 거부</t>
+          <t>서버 오류(500) 없이 가입 400, 로그인 401</t>
         </is>
       </c>
       <c r="H62" s="28" t="inlineStr">
@@ -4963,7 +4963,7 @@
     <row r="63">
       <c r="A63" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-12</t>
+          <t>IT-ATK-04</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
@@ -4983,17 +4983,17 @@
       </c>
       <c r="E63" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>같은 계정에 비밀번호를 연속으로 틀려 입력(무차별 대입)</t>
+          <t>유니코드 숫자(아라비아-인도 숫자 등)만으로 '숫자 1자 이상' 규칙 통과 시도</t>
         </is>
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>일정 횟수 뒤 429 등으로 제한되고, 제한 중에는 올바른 비밀번호도 거부</t>
+          <t>ASCII 숫자가 없으면 400</t>
         </is>
       </c>
       <c r="H63" s="28" t="inlineStr">
@@ -5010,7 +5010,7 @@
     <row r="64">
       <c r="A64" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-13</t>
+          <t>IT-ATK-05</t>
         </is>
       </c>
       <c r="B64" s="27" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>로그아웃 전에 훔친 세션 쿠키를 로그아웃 후 재사용</t>
+          <t>아이디 변형 입력: 줄바꿈·공백·전각 문자·제로폭 문자·길이 초과/미달</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>로그아웃한 세션은 서버에서 무효 → 401</t>
+          <t>모두 400, 사용자 생성 없음</t>
         </is>
       </c>
       <c r="H64" s="28" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="65">
       <c r="A65" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-14</t>
+          <t>IT-ATK-06</t>
         </is>
       </c>
       <c r="B65" s="27" t="inlineStr">
@@ -5077,17 +5077,17 @@
       </c>
       <c r="E65" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>기본 비밀키(dev-secret-change-me)로 세션 쿠키 위조</t>
+          <t>기관 코드에 비정상적으로 긴 문자열(1만 자)과 제어 문자</t>
         </is>
       </c>
       <c r="G65" s="29" t="inlineStr">
         <is>
-          <t>운영 구성에서 기본 키로는 서버가 뜨지 않거나, 위조 쿠키는 거부(401)</t>
+          <t>설계서 VARCHAR(50) 한도를 넘으면 400, 사용자 생성 없음</t>
         </is>
       </c>
       <c r="H65" s="28" t="inlineStr">
@@ -5104,7 +5104,7 @@
     <row r="66">
       <c r="A66" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-15</t>
+          <t>IT-ATK-07</t>
         </is>
       </c>
       <c r="B66" s="27" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="F66" s="29" t="inlineStr">
         <is>
-          <t>응답 보안 헤더(nosniff, 프레임 삽입 차단)</t>
+          <t>SQL 인젝션 문자열을 아이디/비밀번호에 입력</t>
         </is>
       </c>
       <c r="G66" s="29" t="inlineStr">
         <is>
-          <t>X-Content-Type-Options: nosniff, X-Frame-Options 또는 CSP frame-ancestors</t>
+          <t>가입 400, 로그인 401, users 테이블 변화 없음</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="67">
       <c r="A67" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-16</t>
+          <t>IT-ATK-08</t>
         </is>
       </c>
       <c r="B67" s="27" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="E67" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>세션 쿠키 속성: HttpOnly·SameSite·Secure</t>
+          <t>필드 타입 혼동(문자열 자리에 배열·객체·숫자·null)</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>운영 설정에서 세 속성이 모두 켜짐</t>
+          <t>서버 오류 없이 가입 400 / 로그인 401</t>
         </is>
       </c>
       <c r="H67" s="28" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="68">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-17</t>
+          <t>IT-ATK-09</t>
         </is>
       </c>
       <c r="B68" s="27" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="E68" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
-          <t>로그인 실패 응답의 계정 존재 여부 은닉</t>
+          <t>깊게 중첩된 JSON 본문(3만 단계, 크기 제한 이내)</t>
         </is>
       </c>
       <c r="G68" s="29" t="inlineStr">
         <is>
-          <t>없는 아이디와 틀린 비밀번호의 응답(상태·본문)이 동일</t>
+          <t>서버 오류(500) 없이 400</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="69">
       <c r="A69" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-18</t>
+          <t>IT-ATK-10</t>
         </is>
       </c>
       <c r="B69" s="27" t="inlineStr">
@@ -5255,27 +5255,27 @@
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E69" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>대시보드 요청에 user_id/scope 쿼리를 붙여 타인·전체 범위 요청</t>
+          <t>JSON이 아닌 요청(form, 빈 본문, 배열, 문자열)</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>쿼리는 무시되고 로그인 사용자 본인 범위만 반환</t>
+          <t>모두 400 JSON 오류 형식</t>
         </is>
       </c>
       <c r="H69" s="28" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="70">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-19</t>
+          <t>IT-ATK-11</t>
         </is>
       </c>
       <c r="B70" s="27" t="inlineStr">
@@ -5302,27 +5302,27 @@
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E70" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>대시보드 접근에 변조된 세션(존재하지 않는 user_id)</t>
+          <t>2MB 크기의 요청 본문</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>401 이고 세션이 정리됨</t>
+          <t>본문 크기 제한으로 413 거부</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="71">
       <c r="A71" s="27" t="inlineStr">
         <is>
-          <t>IT-ATK-20</t>
+          <t>IT-ATK-12</t>
         </is>
       </c>
       <c r="B71" s="27" t="inlineStr">
@@ -5359,17 +5359,17 @@
       </c>
       <c r="E71" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F71" s="29" t="inlineStr">
         <is>
-          <t>같은 아이디로 12개 요청을 동시에 가입</t>
+          <t>같은 계정에 비밀번호를 연속으로 틀려 입력(무차별 대입)</t>
         </is>
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>정확히 1건 201, 나머지 409, 서버 오류(500) 없음, users 1건</t>
+          <t>일정 횟수 뒤 429 등으로 제한되고, 제한 중에는 올바른 비밀번호도 거부</t>
         </is>
       </c>
       <c r="H71" s="28" t="inlineStr">
@@ -5386,12 +5386,12 @@
     <row r="72">
       <c r="A72" s="27" t="inlineStr">
         <is>
-          <t>UT-ATK-01</t>
+          <t>IT-ATK-13</t>
         </is>
       </c>
       <c r="B72" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
@@ -5406,17 +5406,17 @@
       </c>
       <c r="E72" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>LoginThrottle: 5회 실패 전까지는 막지 않고 5회째부터 차단</t>
+          <t>로그아웃 전에 훔친 세션 쿠키를 로그아웃 후 재사용</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>4회 실패 후 차단 아님, 5회 후 차단</t>
+          <t>로그아웃한 세션은 서버에서 무효 → 401</t>
         </is>
       </c>
       <c r="H72" s="28" t="inlineStr">
@@ -5433,12 +5433,12 @@
     <row r="73">
       <c r="A73" s="27" t="inlineStr">
         <is>
-          <t>UT-ATK-02</t>
+          <t>IT-ATK-14</t>
         </is>
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="E73" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>LoginThrottle: 시간이 지나면 풀리고, 성공하면 초기화되며, 아이디는 대소문자 무관/서로 독립</t>
+          <t>기본 비밀키(dev-secret-change-me)로 세션 쿠키 위조</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>15분 경과 후 해제, reset 후 해제, ALICE01 도 같은 계정으로 계산, 다른 아이디는 영향 없음</t>
+          <t>운영 구성에서 기본 키로는 서버가 뜨지 않거나, 위조 쿠키는 거부(401)</t>
         </is>
       </c>
       <c r="H73" s="28" t="inlineStr">
@@ -5480,12 +5480,12 @@
     <row r="74">
       <c r="A74" s="27" t="inlineStr">
         <is>
-          <t>UT-ATK-03</t>
+          <t>IT-ATK-15</t>
         </is>
       </c>
       <c r="B74" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
@@ -5500,17 +5500,17 @@
       </c>
       <c r="E74" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>LoginThrottle: 서로 다른 아이디를 대량으로 시도해도 기억하는 개수가 상한을 넘지 않음</t>
+          <t>응답 보안 헤더(nosniff, 프레임 삽입 차단)</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>max_keys 이하로 유지</t>
+          <t>X-Content-Type-Options: nosniff, X-Frame-Options 또는 CSP frame-ancestors</t>
         </is>
       </c>
       <c r="H74" s="28" t="inlineStr">
@@ -5527,12 +5527,12 @@
     <row r="75">
       <c r="A75" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-ATK-16</t>
         </is>
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
@@ -5547,17 +5547,17 @@
       </c>
       <c r="E75" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 원문과 다른 bcrypt 해시</t>
+          <t>세션 쿠키 속성: HttpOnly·SameSite·Secure</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
+          <t>운영 설정에서 세 속성이 모두 켜짐</t>
         </is>
       </c>
       <c r="H75" s="28" t="inlineStr">
@@ -5574,12 +5574,12 @@
     <row r="76">
       <c r="A76" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>IT-ATK-17</t>
         </is>
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
@@ -5594,17 +5594,17 @@
       </c>
       <c r="E76" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
+          <t>로그인 실패 응답의 계정 존재 여부 은닉</t>
         </is>
       </c>
       <c r="G76" s="29" t="inlineStr">
         <is>
-          <t>두 번 호출한 해시가 서로 다름</t>
+          <t>없는 아이디와 틀린 비밀번호의 응답(상태·본문)이 동일</t>
         </is>
       </c>
       <c r="H76" s="28" t="inlineStr">
@@ -5621,37 +5621,37 @@
     <row r="77">
       <c r="A77" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>IT-ATK-18</t>
         </is>
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D77" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E77" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F77" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 올바른 평문</t>
+          <t>대시보드 요청에 user_id/scope 쿼리를 붙여 타인·전체 범위 요청</t>
         </is>
       </c>
       <c r="G77" s="29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>쿼리는 무시되고 로그인 사용자 본인 범위만 반환</t>
         </is>
       </c>
       <c r="H77" s="28" t="inlineStr">
@@ -5668,37 +5668,37 @@
     <row r="78">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>IT-ATK-19</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E78" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 잘못된 평문</t>
+          <t>대시보드 접근에 변조된 세션(존재하지 않는 user_id)</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>401 이고 세션이 정리됨</t>
         </is>
       </c>
       <c r="H78" s="28" t="inlineStr">
@@ -5715,12 +5715,12 @@
     <row r="79">
       <c r="A79" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>IT-ATK-20</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="F79" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 대소문자 구분</t>
+          <t>같은 아이디로 12개 요청을 동시에 가입</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
         <is>
-          <t>대소문자만 다른 평문은 False</t>
+          <t>정확히 1건 201, 나머지 409, 서버 오류(500) 없음, users 1건</t>
         </is>
       </c>
       <c r="H79" s="28" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="80">
       <c r="A80" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>UT-ATK-01</t>
         </is>
       </c>
       <c r="B80" s="27" t="inlineStr">
@@ -5782,17 +5782,17 @@
       </c>
       <c r="E80" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F80" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
+          <t>LoginThrottle: 5회 실패 전까지는 막지 않고 5회째부터 차단</t>
         </is>
       </c>
       <c r="G80" s="29" t="inlineStr">
         <is>
-          <t>예외 없이 False</t>
+          <t>4회 실패 후 차단 아님, 5회 후 차단</t>
         </is>
       </c>
       <c r="H80" s="28" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="81">
       <c r="A81" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>UT-ATK-02</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="F81" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
+          <t>LoginThrottle: 시간이 지나면 풀리고, 성공하면 초기화되며, 아이디는 대소문자 무관/서로 독립</t>
         </is>
       </c>
       <c r="G81" s="29" t="inlineStr">
         <is>
-          <t>해시 생성 후 verify 가 True</t>
+          <t>15분 경과 후 해제, reset 후 해제, ALICE01 도 같은 계정으로 계산, 다른 아이디는 영향 없음</t>
         </is>
       </c>
       <c r="H81" s="28" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="82">
       <c r="A82" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>UT-ATK-03</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="E82" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자 가입</t>
+          <t>LoginThrottle: 서로 다른 아이디를 대량으로 시도해도 기억하는 개수가 상한을 넘지 않음</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
+          <t>max_keys 이하로 유지</t>
         </is>
       </c>
       <c r="H82" s="28" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="83">
       <c r="A83" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
+          <t>hash_password: 원문과 다른 bcrypt 해시</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>user_type·org_code 가 그대로 저장</t>
+          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
         </is>
       </c>
       <c r="H83" s="28" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="84">
       <c r="A84" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
@@ -5970,17 +5970,17 @@
       </c>
       <c r="E84" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관인데 org_code 누락</t>
+          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 사용자 미생성</t>
+          <t>두 번 호출한 해시가 서로 다름</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
@@ -5997,7 +5997,7 @@
     <row r="85">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="E85" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F85" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
+          <t>verify_password: 올바른 평문</t>
         </is>
       </c>
       <c r="G85" s="29" t="inlineStr">
         <is>
-          <t>org_code 는 None</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H85" s="28" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="86">
       <c r="A86" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>signup: 중복 username</t>
+          <t>verify_password: 잘못된 평문</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H86" s="28" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="87">
       <c r="A87" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
-          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
+          <t>verify_password: 대소문자 구분</t>
         </is>
       </c>
       <c r="G87" s="29" t="inlineStr">
         <is>
-          <t>두 계정 모두 생성</t>
+          <t>대소문자만 다른 평문은 False</t>
         </is>
       </c>
       <c r="H87" s="28" t="inlineStr">
@@ -6138,7 +6138,7 @@
     <row r="88">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="E88" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
-          <t>signup: username 길이 경계 3/4/20/21자</t>
+          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
         </is>
       </c>
       <c r="G88" s="29" t="inlineStr">
         <is>
-          <t>4~20자만 허용, 나머지 ValidationError</t>
+          <t>예외 없이 False</t>
         </is>
       </c>
       <c r="H88" s="28" t="inlineStr">
@@ -6185,7 +6185,7 @@
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="E89" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
+          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>해시 생성 후 verify 가 True</t>
         </is>
       </c>
       <c r="H89" s="28" t="inlineStr">
@@ -6232,7 +6232,7 @@
     <row r="90">
       <c r="A90" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
@@ -6252,17 +6252,17 @@
       </c>
       <c r="E90" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F90" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
+          <t>signup: 개인 사용자 가입</t>
         </is>
       </c>
       <c r="G90" s="29" t="inlineStr">
         <is>
-          <t>8~64자만 허용</t>
+          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
@@ -6279,7 +6279,7 @@
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F91" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
+          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
         <is>
-          <t>숫자만/영문만/공백만 → ValidationError</t>
+          <t>user_type·org_code 가 그대로 저장</t>
         </is>
       </c>
       <c r="H91" s="28" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="92">
       <c r="A92" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B92" s="27" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>signup: 허용되지 않는 user_type</t>
+          <t>signup: 기업/기관인데 org_code 누락</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>ValidationError, 사용자 미생성</t>
         </is>
       </c>
       <c r="H92" s="28" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
@@ -6393,17 +6393,17 @@
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
+          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>예외 후 users 0건</t>
+          <t>org_code 는 None</t>
         </is>
       </c>
       <c r="H93" s="28" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="94">
       <c r="A94" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
@@ -6440,17 +6440,17 @@
       </c>
       <c r="E94" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>login: 올바른 자격 증명</t>
+          <t>signup: 중복 username</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>해당 User 반환</t>
+          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
@@ -6487,17 +6487,17 @@
       </c>
       <c r="E95" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>login: 비밀번호 불일치</t>
+          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError</t>
+          <t>두 계정 모두 생성</t>
         </is>
       </c>
       <c r="H95" s="28" t="inlineStr">
@@ -6514,7 +6514,7 @@
     <row r="96">
       <c r="A96" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
@@ -6534,17 +6534,17 @@
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
+          <t>signup: username 길이 경계 3/4/20/21자</t>
         </is>
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
+          <t>4~20자만 허용, 나머지 ValidationError</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="E97" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>login: 빈 입력/인젝션 문자열</t>
+          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError (예외 유형 일관)</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H97" s="28" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="98">
       <c r="A98" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
@@ -6628,17 +6628,17 @@
       </c>
       <c r="E98" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>get_user: 존재하는 id / 없는 id</t>
+          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
         <is>
-          <t>존재하면 User, 없으면 NotFoundError</t>
+          <t>8~64자만 허용</t>
         </is>
       </c>
       <c r="H98" s="28" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="99">
       <c r="A99" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
@@ -6665,27 +6665,27 @@
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D99" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E99" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>create_application: 유효한 알고리즘</t>
+          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
         </is>
       </c>
       <c r="G99" s="29" t="inlineStr">
         <is>
-          <t>status='submitted', submitted_at 설정, 본인 소유</t>
+          <t>숫자만/영문만/공백만 → ValidationError</t>
         </is>
       </c>
       <c r="H99" s="28" t="inlineStr">
@@ -6702,7 +6702,7 @@
     <row r="100">
       <c r="A100" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
@@ -6712,27 +6712,27 @@
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E100" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
-          <t>create_application: 허용 알고리즘 전체</t>
+          <t>signup: 허용되지 않는 user_type</t>
         </is>
       </c>
       <c r="G100" s="29" t="inlineStr">
         <is>
-          <t>ALGORITHMS 의 모든 값 신청 가능</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H100" s="28" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="101">
       <c r="A101" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D101" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E101" s="27" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="F101" s="29" t="inlineStr">
         <is>
-          <t>create_application: 빈 값/미허용 알고리즘</t>
+          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
         </is>
       </c>
       <c r="G101" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 레코드 미생성</t>
+          <t>예외 후 users 0건</t>
         </is>
       </c>
       <c r="H101" s="28" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="102">
       <c r="A102" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
@@ -6806,27 +6806,27 @@
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E102" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F102" s="29" t="inlineStr">
         <is>
-          <t>create_application: 없는 사용자</t>
+          <t>login: 올바른 자격 증명</t>
         </is>
       </c>
       <c r="G102" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>해당 User 반환</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
@@ -6843,7 +6843,7 @@
     <row r="103">
       <c r="A103" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D103" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E103" s="27" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="F103" s="29" t="inlineStr">
         <is>
-          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
+          <t>login: 비밀번호 불일치</t>
         </is>
       </c>
       <c r="G103" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
+          <t>AuthenticationError</t>
         </is>
       </c>
       <c r="H103" s="28" t="inlineStr">
@@ -6890,7 +6890,7 @@
     <row r="104">
       <c r="A104" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
@@ -6900,27 +6900,27 @@
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E104" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F104" s="29" t="inlineStr">
         <is>
-          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
+          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
         </is>
       </c>
       <c r="G104" s="29" t="inlineStr">
         <is>
-          <t>허용</t>
+          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
         </is>
       </c>
       <c r="H104" s="28" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="105">
       <c r="A105" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B105" s="27" t="inlineStr">
@@ -6947,27 +6947,27 @@
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D105" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E105" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용 전이 3종</t>
+          <t>login: 빈 입력/인젝션 문자열</t>
         </is>
       </c>
       <c r="G105" s="29" t="inlineStr">
         <is>
-          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
+          <t>AuthenticationError (예외 유형 일관)</t>
         </is>
       </c>
       <c r="H105" s="28" t="inlineStr">
@@ -6984,7 +6984,7 @@
     <row r="106">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
@@ -6994,27 +6994,27 @@
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E106" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F106" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
+          <t>get_user: 존재하는 id / 없는 id</t>
         </is>
       </c>
       <c r="G106" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 상태 불변</t>
+          <t>존재하면 User, 없으면 NotFoundError</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="107">
       <c r="A107" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="E107" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>update_status: 존재하지 않는 상태값</t>
+          <t>create_application: 유효한 알고리즘</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>status='submitted', submitted_at 설정, 본인 소유</t>
         </is>
       </c>
       <c r="H107" s="28" t="inlineStr">
@@ -7078,7 +7078,7 @@
     <row r="108">
       <c r="A108" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B108" s="27" t="inlineStr">
@@ -7098,17 +7098,17 @@
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F108" s="29" t="inlineStr">
         <is>
-          <t>update_status: 전이 시 updated_at 갱신</t>
+          <t>create_application: 허용 알고리즘 전체</t>
         </is>
       </c>
       <c r="G108" s="29" t="inlineStr">
         <is>
-          <t>updated_at 이 이전보다 이후</t>
+          <t>ALGORITHMS 의 모든 값 신청 가능</t>
         </is>
       </c>
       <c r="H108" s="28" t="inlineStr">
@@ -7125,7 +7125,7 @@
     <row r="109">
       <c r="A109" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B109" s="27" t="inlineStr">
@@ -7145,17 +7145,17 @@
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
+          <t>create_application: 빈 값/미허용 알고리즘</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError, 상태 불변</t>
+          <t>ValidationError, 레코드 미생성</t>
         </is>
       </c>
       <c r="H109" s="28" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="110">
       <c r="A110" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B110" s="27" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>update_status: 없는 신청/없는 사용자</t>
+          <t>create_application: 없는 사용자</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
@@ -7219,7 +7219,7 @@
     <row r="111">
       <c r="A111" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B111" s="27" t="inlineStr">
@@ -7239,17 +7239,17 @@
       </c>
       <c r="E111" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 본인 신청만, 최신순</t>
+          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
         </is>
       </c>
       <c r="G111" s="29" t="inlineStr">
         <is>
-          <t>타인 신청 제외, submitted_at 내림차순</t>
+          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
         </is>
       </c>
       <c r="H111" s="28" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="112">
       <c r="A112" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B112" s="27" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 상태 필터</t>
+          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>해당 상태만 반환, total 도 필터 기준</t>
+          <t>허용</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
@@ -7313,7 +7313,7 @@
     <row r="113">
       <c r="A113" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B113" s="27" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 잘못된 상태 필터</t>
+          <t>update_status: 허용 전이 3종</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
         </is>
       </c>
       <c r="H113" s="28" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="114">
       <c r="A114" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B114" s="27" t="inlineStr">
@@ -7380,17 +7380,17 @@
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F114" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
+          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
         </is>
       </c>
       <c r="G114" s="29" t="inlineStr">
         <is>
-          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
+          <t>InvalidTransitionError, 상태 불변</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
@@ -7407,7 +7407,7 @@
     <row r="115">
       <c r="A115" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B115" s="27" t="inlineStr">
@@ -7427,17 +7427,17 @@
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>list_applications: page/per_page 경계값</t>
+          <t>update_status: 존재하지 않는 상태값</t>
         </is>
       </c>
       <c r="G115" s="29" t="inlineStr">
         <is>
-          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H115" s="28" t="inlineStr">
@@ -7454,7 +7454,7 @@
     <row r="116">
       <c r="A116" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B116" s="27" t="inlineStr">
@@ -7474,17 +7474,17 @@
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F116" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 신청이 없으면 빈 목록</t>
+          <t>update_status: 전이 시 updated_at 갱신</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
-          <t>items=[], total=0</t>
+          <t>updated_at 이 이전보다 이후</t>
         </is>
       </c>
       <c r="H116" s="28" t="inlineStr">
@@ -7501,7 +7501,7 @@
     <row r="117">
       <c r="A117" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B117" s="27" t="inlineStr">
@@ -7521,17 +7521,17 @@
       </c>
       <c r="E117" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F117" s="29" t="inlineStr">
         <is>
-          <t>get_application: 본인 / 타인 / 없는 id</t>
+          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
         </is>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>PermissionDeniedError, 상태 불변</t>
         </is>
       </c>
       <c r="H117" s="28" t="inlineStr">
@@ -7548,7 +7548,7 @@
     <row r="118">
       <c r="A118" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B118" s="27" t="inlineStr">
@@ -7568,17 +7568,17 @@
       </c>
       <c r="E118" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F118" s="29" t="inlineStr">
         <is>
-          <t>get_application: institution 은 모든 신청 조회 가능</t>
+          <t>update_status: 없는 신청/없는 사용자</t>
         </is>
       </c>
       <c r="G118" s="29" t="inlineStr">
         <is>
-          <t>타인 신청도 반환</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H118" s="28" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="119">
       <c r="A119" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B119" s="27" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="C119" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D119" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E119" s="27" t="inlineStr">
@@ -7620,17 +7620,17 @@
       </c>
       <c r="F119" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: SHA-256 hex</t>
+          <t>list_applications: 본인 신청만, 최신순</t>
         </is>
       </c>
       <c r="G119" s="29" t="inlineStr">
         <is>
-          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
+          <t>타인 신청 제외, submitted_at 내림차순</t>
         </is>
       </c>
       <c r="H119" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I119" s="30" t="n"/>
@@ -7642,7 +7642,7 @@
     <row r="120">
       <c r="A120" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B120" s="27" t="inlineStr">
@@ -7652,32 +7652,32 @@
       </c>
       <c r="C120" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D120" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E120" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F120" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
+          <t>list_applications: 상태 필터</t>
         </is>
       </c>
       <c r="G120" s="29" t="inlineStr">
         <is>
-          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
+          <t>해당 상태만 반환, total 도 필터 기준</t>
         </is>
       </c>
       <c r="H120" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I120" s="30" t="n"/>
@@ -7689,7 +7689,7 @@
     <row r="121">
       <c r="A121" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B121" s="27" t="inlineStr">
@@ -7699,32 +7699,32 @@
       </c>
       <c r="C121" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D121" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E121" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F121" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 동일 해시</t>
+          <t>list_applications: 잘못된 상태 필터</t>
         </is>
       </c>
       <c r="G121" s="29" t="inlineStr">
         <is>
-          <t>'normal'</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H121" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I121" s="30" t="n"/>
@@ -7736,7 +7736,7 @@
     <row r="122">
       <c r="A122" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B122" s="27" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="C122" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D122" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E122" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F122" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 상이한 해시</t>
+          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
         </is>
       </c>
       <c r="G122" s="29" t="inlineStr">
         <is>
-          <t>'suspected'</t>
+          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
         </is>
       </c>
       <c r="H122" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I122" s="30" t="n"/>
@@ -7783,7 +7783,7 @@
     <row r="123">
       <c r="A123" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B123" s="27" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="C123" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D123" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E123" s="27" t="inlineStr">
@@ -7808,17 +7808,17 @@
       </c>
       <c r="F123" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 대소문자만 다른 hex</t>
+          <t>list_applications: page/per_page 경계값</t>
         </is>
       </c>
       <c r="G123" s="29" t="inlineStr">
         <is>
-          <t>동일 값으로 보고 'normal'</t>
+          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
         </is>
       </c>
       <c r="H123" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I123" s="30" t="n"/>
@@ -7830,7 +7830,7 @@
     <row r="124">
       <c r="A124" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B124" s="27" t="inlineStr">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="C124" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D124" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E124" s="27" t="inlineStr">
@@ -7855,17 +7855,17 @@
       </c>
       <c r="F124" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인된 신청에 발급</t>
+          <t>list_applications: 신청이 없으면 빈 목록</t>
         </is>
       </c>
       <c r="G124" s="29" t="inlineStr">
         <is>
-          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
+          <t>items=[], total=0</t>
         </is>
       </c>
       <c r="H124" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I124" s="30" t="n"/>
@@ -7877,7 +7877,7 @@
     <row r="125">
       <c r="A125" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B125" s="27" t="inlineStr">
@@ -7887,32 +7887,32 @@
       </c>
       <c r="C125" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D125" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E125" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F125" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인 이전/반려 상태</t>
+          <t>get_application: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G125" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 검증서 미생성</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H125" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I125" s="30" t="n"/>
@@ -7924,7 +7924,7 @@
     <row r="126">
       <c r="A126" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B126" s="27" t="inlineStr">
@@ -7934,32 +7934,32 @@
       </c>
       <c r="C126" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D126" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E126" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F126" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 신청당 1건(중복 발급)</t>
+          <t>get_application: institution 은 모든 신청 조회 가능</t>
         </is>
       </c>
       <c r="G126" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError</t>
+          <t>타인 신청도 반환</t>
         </is>
       </c>
       <c r="H126" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I126" s="30" t="n"/>
@@ -7971,7 +7971,7 @@
     <row r="127">
       <c r="A127" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B127" s="27" t="inlineStr">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="C127" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D127" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E127" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F127" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: institution 이 아니면 발급 불가</t>
+          <t>compute_hash: SHA-256 hex</t>
         </is>
       </c>
       <c r="G127" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError</t>
+          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
         </is>
       </c>
       <c r="H127" s="28" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="128">
       <c r="A128" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B128" s="27" t="inlineStr">
@@ -8028,27 +8028,27 @@
       </c>
       <c r="C128" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D128" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E128" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F128" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
+          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
         </is>
       </c>
       <c r="G128" s="29" t="inlineStr">
         <is>
-          <t>ValidationError / ValidationError / NotFoundError</t>
+          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
         </is>
       </c>
       <c r="H128" s="28" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="129">
       <c r="A129" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B129" s="27" t="inlineStr">
@@ -8075,27 +8075,27 @@
       </c>
       <c r="C129" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D129" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E129" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F129" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: KCMVP 유형도 발급</t>
+          <t>compare_hash: 동일 해시</t>
         </is>
       </c>
       <c r="G129" s="29" t="inlineStr">
         <is>
-          <t>cert_type='KCMVP'</t>
+          <t>'normal'</t>
         </is>
       </c>
       <c r="H129" s="28" t="inlineStr">
@@ -8112,7 +8112,7 @@
     <row r="130">
       <c r="A130" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B130" s="27" t="inlineStr">
@@ -8122,27 +8122,27 @@
       </c>
       <c r="C130" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D130" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E130" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F130" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
+          <t>compare_hash: 상이한 해시</t>
         </is>
       </c>
       <c r="G130" s="29" t="inlineStr">
         <is>
-          <t>타인 검증서 제외, issued_at 내림차순</t>
+          <t>'suspected'</t>
         </is>
       </c>
       <c r="H130" s="28" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="131">
       <c r="A131" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B131" s="27" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C131" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D131" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E131" s="27" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="F131" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
+          <t>compare_hash: 대소문자만 다른 hex</t>
         </is>
       </c>
       <c r="G131" s="29" t="inlineStr">
         <is>
-          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
+          <t>동일 값으로 보고 'normal'</t>
         </is>
       </c>
       <c r="H131" s="28" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="132">
       <c r="A132" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B132" s="27" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="F132" s="29" t="inlineStr">
         <is>
-          <t>get_certificate: 본인 / 타인 / 없는 id</t>
+          <t>issue_certificate: 승인된 신청에 발급</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
         </is>
       </c>
       <c r="H132" s="28" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="133">
       <c r="A133" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B133" s="27" t="inlineStr">
@@ -8263,27 +8263,27 @@
       </c>
       <c r="C133" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D133" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E133" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F133" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 무결 → normal</t>
+          <t>issue_certificate: 승인 이전/반려 상태</t>
         </is>
       </c>
       <c r="G133" s="29" t="inlineStr">
         <is>
-          <t>tamper_status='normal'</t>
+          <t>InvalidTransitionError, 검증서 미생성</t>
         </is>
       </c>
       <c r="H133" s="28" t="inlineStr">
@@ -8300,7 +8300,7 @@
     <row r="134">
       <c r="A134" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B134" s="27" t="inlineStr">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="C134" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D134" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E134" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F134" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
+          <t>issue_certificate: 신청당 1건(중복 발급)</t>
         </is>
       </c>
       <c r="G134" s="29" t="inlineStr">
         <is>
-          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
+          <t>DuplicateApplicationError</t>
         </is>
       </c>
       <c r="H134" s="28" t="inlineStr">
@@ -8347,7 +8347,7 @@
     <row r="135">
       <c r="A135" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B135" s="27" t="inlineStr">
@@ -8357,27 +8357,27 @@
       </c>
       <c r="C135" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D135" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E135" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F135" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
+          <t>issue_certificate: institution 이 아니면 발급 불가</t>
         </is>
       </c>
       <c r="G135" s="29" t="inlineStr">
         <is>
-          <t>'suspected' (예외 아님)</t>
+          <t>PermissionDeniedError</t>
         </is>
       </c>
       <c r="H135" s="28" t="inlineStr">
@@ -8394,7 +8394,7 @@
     <row r="136">
       <c r="A136" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B136" s="27" t="inlineStr">
@@ -8404,27 +8404,27 @@
       </c>
       <c r="C136" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D136" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E136" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F136" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 원복 후 재검증 시 normal</t>
+          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
         </is>
       </c>
       <c r="G136" s="29" t="inlineStr">
         <is>
-          <t>변조 → suspected, 원복 → normal</t>
+          <t>ValidationError / ValidationError / NotFoundError</t>
         </is>
       </c>
       <c r="H136" s="28" t="inlineStr">
@@ -8441,7 +8441,7 @@
     <row r="137">
       <c r="A137" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B137" s="27" t="inlineStr">
@@ -8451,27 +8451,27 @@
       </c>
       <c r="C137" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D137" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E137" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F137" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 존재하지 않는 cert_id</t>
+          <t>issue_certificate: KCMVP 유형도 발급</t>
         </is>
       </c>
       <c r="G137" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>cert_type='KCMVP'</t>
         </is>
       </c>
       <c r="H137" s="28" t="inlineStr">
@@ -8488,7 +8488,7 @@
     <row r="138">
       <c r="A138" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B138" s="27" t="inlineStr">
@@ -8498,27 +8498,27 @@
       </c>
       <c r="C138" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D138" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E138" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F138" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
+          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
         </is>
       </c>
       <c r="G138" s="29" t="inlineStr">
         <is>
-          <t>검증 후에도 integrity_hash 불변</t>
+          <t>타인 검증서 제외, issued_at 내림차순</t>
         </is>
       </c>
       <c r="H138" s="28" t="inlineStr">
@@ -8535,7 +8535,7 @@
     <row r="139">
       <c r="A139" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B139" s="27" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="C139" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D139" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E139" s="27" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="F139" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
+          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
         </is>
       </c>
       <c r="G139" s="29" t="inlineStr">
         <is>
-          <t>파일이 없으면 suspected 유지</t>
+          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
         </is>
       </c>
       <c r="H139" s="28" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="140">
       <c r="A140" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-01</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B140" s="27" t="inlineStr">
@@ -8592,12 +8592,12 @@
       </c>
       <c r="C140" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D140" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E140" s="27" t="inlineStr">
@@ -8607,17 +8607,17 @@
       </c>
       <c r="F140" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 본인 신청만 집계</t>
+          <t>get_certificate: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G140" s="29" t="inlineStr">
         <is>
-          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H140" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I140" s="30" t="n"/>
@@ -8629,7 +8629,7 @@
     <row r="141">
       <c r="A141" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-02</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B141" s="27" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="C141" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D141" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E141" s="27" t="inlineStr">
@@ -8654,17 +8654,17 @@
       </c>
       <c r="F141" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
+          <t>verify_integrity: 파일 무결 → normal</t>
         </is>
       </c>
       <c r="G141" s="29" t="inlineStr">
         <is>
-          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
+          <t>tamper_status='normal'</t>
         </is>
       </c>
       <c r="H141" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I141" s="30" t="n"/>
@@ -8676,7 +8676,7 @@
     <row r="142">
       <c r="A142" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-03</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B142" s="27" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="C142" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D142" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E142" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F142" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
+          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
         </is>
       </c>
       <c r="G142" s="29" t="inlineStr">
         <is>
-          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
+          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
         </is>
       </c>
       <c r="H142" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I142" s="30" t="n"/>
@@ -8723,7 +8723,7 @@
     <row r="143">
       <c r="A143" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-04</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B143" s="27" t="inlineStr">
@@ -8733,32 +8733,32 @@
       </c>
       <c r="C143" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D143" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E143" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F143" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
+          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
         </is>
       </c>
       <c r="G143" s="29" t="inlineStr">
         <is>
-          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
+          <t>'suspected' (예외 아님)</t>
         </is>
       </c>
       <c r="H143" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I143" s="30" t="n"/>
@@ -8770,7 +8770,7 @@
     <row r="144">
       <c r="A144" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-05</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B144" s="27" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="C144" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D144" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E144" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F144" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 상태 라벨 매핑</t>
+          <t>verify_integrity: 원복 후 재검증 시 normal</t>
         </is>
       </c>
       <c r="G144" s="29" t="inlineStr">
         <is>
-          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
+          <t>변조 → suspected, 원복 → normal</t>
         </is>
       </c>
       <c r="H144" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I144" s="30" t="n"/>
@@ -8817,7 +8817,7 @@
     <row r="145">
       <c r="A145" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-06</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B145" s="27" t="inlineStr">
@@ -8827,32 +8827,32 @@
       </c>
       <c r="C145" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D145" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E145" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F145" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 최근 7일 신규 신청 경계</t>
+          <t>verify_integrity: 존재하지 않는 cert_id</t>
         </is>
       </c>
       <c r="G145" s="29" t="inlineStr">
         <is>
-          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H145" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I145" s="30" t="n"/>
@@ -8864,7 +8864,7 @@
     <row r="146">
       <c r="A146" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-07</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B146" s="27" t="inlineStr">
@@ -8874,27 +8874,27 @@
       </c>
       <c r="C146" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D146" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E146" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F146" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
+          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
         </is>
       </c>
       <c r="G146" s="29" t="inlineStr">
         <is>
-          <t>total·suspected 가 본인 건만 반영</t>
+          <t>검증 후에도 integrity_hash 불변</t>
         </is>
       </c>
       <c r="H146" s="28" t="inlineStr">
@@ -8911,7 +8911,7 @@
     <row r="147">
       <c r="A147" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-08</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B147" s="27" t="inlineStr">
@@ -8921,32 +8921,32 @@
       </c>
       <c r="C147" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D147" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E147" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F147" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 가명·익명 처리 상태</t>
+          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
         </is>
       </c>
       <c r="G147" s="29" t="inlineStr">
         <is>
-          <t>처리 전 processed=False, 처리 후 level 반영</t>
+          <t>파일이 없으면 suspected 유지</t>
         </is>
       </c>
       <c r="H147" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I147" s="30" t="n"/>
@@ -8958,7 +8958,7 @@
     <row r="148">
       <c r="A148" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-09</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B148" s="27" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C148" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D148" s="28" t="inlineStr">
@@ -8983,17 +8983,17 @@
       </c>
       <c r="F148" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 위변조 의심 알림이 최우선</t>
+          <t>get_summary: 본인 신청만 집계</t>
         </is>
       </c>
       <c r="G148" s="29" t="inlineStr">
         <is>
-          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
+          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
         </is>
       </c>
       <c r="H148" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I148" s="30" t="n"/>
@@ -9005,7 +9005,7 @@
     <row r="149">
       <c r="A149" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-10</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B149" s="27" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="F149" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 신청 진행/결과 알림 문구</t>
+          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
         </is>
       </c>
       <c r="G149" s="29" t="inlineStr">
         <is>
-          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
+          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
         </is>
       </c>
       <c r="H149" s="28" t="inlineStr">
@@ -9052,7 +9052,7 @@
     <row r="150">
       <c r="A150" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-11</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B150" s="27" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="F150" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 알림은 최대 5건</t>
+          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
         </is>
       </c>
       <c r="G150" s="29" t="inlineStr">
         <is>
-          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
+          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
         </is>
       </c>
       <c r="H150" s="28" t="inlineStr">
@@ -9099,7 +9099,7 @@
     <row r="151">
       <c r="A151" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-12</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B151" s="27" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="C151" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D151" s="28" t="inlineStr">
@@ -9124,17 +9124,17 @@
       </c>
       <c r="F151" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
+          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
         </is>
       </c>
       <c r="G151" s="29" t="inlineStr">
         <is>
-          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
+          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="H151" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I151" s="30" t="n"/>
@@ -9146,7 +9146,7 @@
     <row r="152">
       <c r="A152" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-13</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B152" s="27" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C152" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D152" s="28" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="F152" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
+          <t>get_summary: 상태 라벨 매핑</t>
         </is>
       </c>
       <c r="G152" s="29" t="inlineStr">
         <is>
-          <t>scope='own'</t>
+          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
         </is>
       </c>
       <c r="H152" s="28" t="inlineStr">
@@ -9193,7 +9193,7 @@
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-14</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B153" s="27" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="C153" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
@@ -9213,17 +9213,17 @@
       </c>
       <c r="E153" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F153" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 없는 사용자</t>
+          <t>get_summary: 최근 7일 신규 신청 경계</t>
         </is>
       </c>
       <c r="G153" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
         </is>
       </c>
       <c r="H153" s="28" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="154">
       <c r="A154" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-15</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B154" s="27" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="C154" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D154" s="28" t="inlineStr">
@@ -9260,22 +9260,22 @@
       </c>
       <c r="E154" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F154" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
+          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
         </is>
       </c>
       <c r="G154" s="29" t="inlineStr">
         <is>
-          <t>결과 전체에 password/hash 키 없음</t>
+          <t>total·suspected 가 본인 건만 반영</t>
         </is>
       </c>
       <c r="H154" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I154" s="30" t="n"/>
@@ -9287,7 +9287,7 @@
     <row r="155">
       <c r="A155" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-16</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B155" s="27" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="C155" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D155" s="28" t="inlineStr">
@@ -9307,17 +9307,17 @@
       </c>
       <c r="E155" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F155" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
+          <t>get_summary: 가명·익명 처리 상태</t>
         </is>
       </c>
       <c r="G155" s="29" t="inlineStr">
         <is>
-          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
+          <t>처리 전 processed=False, 처리 후 level 반영</t>
         </is>
       </c>
       <c r="H155" s="28" t="inlineStr">
@@ -9334,7 +9334,7 @@
     <row r="156">
       <c r="A156" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B156" s="27" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="C156" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D156" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E156" s="27" t="inlineStr">
@@ -9359,17 +9359,17 @@
       </c>
       <c r="F156" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
+          <t>get_summary: 위변조 의심 알림이 최우선</t>
         </is>
       </c>
       <c r="G156" s="29" t="inlineStr">
         <is>
-          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
+          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
         </is>
       </c>
       <c r="H156" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I156" s="30" t="n"/>
@@ -9381,7 +9381,7 @@
     <row r="157">
       <c r="A157" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B157" s="27" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="C157" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D157" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E157" s="27" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="F157" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 호출마다 다른 값</t>
+          <t>get_summary: 신청 진행/결과 알림 문구</t>
         </is>
       </c>
       <c r="G157" s="29" t="inlineStr">
         <is>
-          <t>1000회 호출 모두 유일</t>
+          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
         </is>
       </c>
       <c r="H157" s="28" t="inlineStr">
@@ -9428,7 +9428,7 @@
     <row r="158">
       <c r="A158" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B158" s="27" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="C158" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D158" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E158" s="27" t="inlineStr">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="F158" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 길이별 마스킹 규칙</t>
+          <t>get_summary: 알림은 최대 5건</t>
         </is>
       </c>
       <c r="G158" s="29" t="inlineStr">
         <is>
-          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
+          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
         </is>
       </c>
       <c r="H158" s="28" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="159">
       <c r="A159" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B159" s="27" t="inlineStr">
@@ -9485,32 +9485,32 @@
       </c>
       <c r="C159" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D159" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E159" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F159" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 빈 값/공백만</t>
+          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
         </is>
       </c>
       <c r="G159" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
         </is>
       </c>
       <c r="H159" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I159" s="30" t="n"/>
@@ -9522,7 +9522,7 @@
     <row r="160">
       <c r="A160" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B160" s="27" t="inlineStr">
@@ -9532,27 +9532,27 @@
       </c>
       <c r="C160" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D160" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E160" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F160" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
+          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
         </is>
       </c>
       <c r="G160" s="29" t="inlineStr">
         <is>
-          <t>' 홍길동 ' → '홍*동'</t>
+          <t>scope='own'</t>
         </is>
       </c>
       <c r="H160" s="28" t="inlineStr">
@@ -9569,7 +9569,7 @@
     <row r="161">
       <c r="A161" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B161" s="27" t="inlineStr">
@@ -9579,27 +9579,27 @@
       </c>
       <c r="C161" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D161" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E161" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F161" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 하이픈 유/무 입력</t>
+          <t>get_summary: 없는 사용자</t>
         </is>
       </c>
       <c r="G161" s="29" t="inlineStr">
         <is>
-          <t>모두 '010-****-5678'</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H161" s="28" t="inlineStr">
@@ -9616,7 +9616,7 @@
     <row r="162">
       <c r="A162" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B162" s="27" t="inlineStr">
@@ -9626,27 +9626,27 @@
       </c>
       <c r="C162" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D162" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E162" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F162" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
+          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
         </is>
       </c>
       <c r="G162" s="29" t="inlineStr">
         <is>
-          <t>'010-***-4567'</t>
+          <t>결과 전체에 password/hash 키 없음</t>
         </is>
       </c>
       <c r="H162" s="28" t="inlineStr">
@@ -9663,7 +9663,7 @@
     <row r="163">
       <c r="A163" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B163" s="27" t="inlineStr">
@@ -9673,27 +9673,27 @@
       </c>
       <c r="C163" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D163" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E163" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F163" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 형식 오류</t>
+          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
         </is>
       </c>
       <c r="G163" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
         </is>
       </c>
       <c r="H163" s="28" t="inlineStr">
@@ -9710,7 +9710,7 @@
     <row r="164">
       <c r="A164" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B164" s="27" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="F164" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 대표 연령대</t>
+          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
         </is>
       </c>
       <c r="G164" s="29" t="inlineStr">
         <is>
-          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
+          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
         </is>
       </c>
       <c r="H164" s="28" t="inlineStr">
@@ -9757,7 +9757,7 @@
     <row r="165">
       <c r="A165" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B165" s="27" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="E165" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F165" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
+          <t>issue_pseudonym_id: 호출마다 다른 값</t>
         </is>
       </c>
       <c r="G165" s="29" t="inlineStr">
         <is>
-          <t>생일 당일부터 다음 연령대</t>
+          <t>1000회 호출 모두 유일</t>
         </is>
       </c>
       <c r="H165" s="28" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="166">
       <c r="A166" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-PRIV-03</t>
         </is>
       </c>
       <c r="B166" s="27" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="F166" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
+          <t>mask_name: 길이별 마스킹 규칙</t>
         </is>
       </c>
       <c r="G166" s="29" t="inlineStr">
         <is>
-          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
+          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
         </is>
       </c>
       <c r="H166" s="28" t="inlineStr">
@@ -9851,7 +9851,7 @@
     <row r="167">
       <c r="A167" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-PRIV-04</t>
         </is>
       </c>
       <c r="B167" s="27" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="F167" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 미래 날짜</t>
+          <t>mask_name: 빈 값/공백만</t>
         </is>
       </c>
       <c r="G167" s="29" t="inlineStr">
@@ -9898,7 +9898,7 @@
     <row r="168">
       <c r="A168" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-PRIV-05</t>
         </is>
       </c>
       <c r="B168" s="27" t="inlineStr">
@@ -9918,17 +9918,17 @@
       </c>
       <c r="E168" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F168" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
+          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
         </is>
       </c>
       <c r="G168" s="29" t="inlineStr">
         <is>
-          <t>연·월·일 숫자열이 결과에 없음</t>
+          <t>' 홍길동 ' → '홍*동'</t>
         </is>
       </c>
       <c r="H168" s="28" t="inlineStr">
@@ -9945,7 +9945,7 @@
     <row r="169">
       <c r="A169" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-PRIV-06</t>
         </is>
       </c>
       <c r="B169" s="27" t="inlineStr">
@@ -9970,12 +9970,12 @@
       </c>
       <c r="F169" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 결과 객체</t>
+          <t>mask_phone: 하이픈 유/무 입력</t>
         </is>
       </c>
       <c r="G169" s="29" t="inlineStr">
         <is>
-          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
+          <t>모두 '010-****-5678'</t>
         </is>
       </c>
       <c r="H169" s="28" t="inlineStr">
@@ -9992,7 +9992,7 @@
     <row r="170">
       <c r="A170" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-PRIV-07</t>
         </is>
       </c>
       <c r="B170" s="27" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="E170" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F170" s="29" t="inlineStr">
         <is>
-          <t>process(anonymous): 식별자 없음</t>
+          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
         </is>
       </c>
       <c r="G170" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
+          <t>'010-***-4567'</t>
         </is>
       </c>
       <c r="H170" s="28" t="inlineStr">
@@ -10039,7 +10039,7 @@
     <row r="171">
       <c r="A171" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-PRIV-08</t>
         </is>
       </c>
       <c r="B171" s="27" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="F171" s="29" t="inlineStr">
         <is>
-          <t>process: 허용되지 않는 mode</t>
+          <t>mask_phone: 형식 오류</t>
         </is>
       </c>
       <c r="G171" s="29" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="172">
       <c r="A172" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-PRIV-09</t>
         </is>
       </c>
       <c r="B172" s="27" t="inlineStr">
@@ -10106,17 +10106,17 @@
       </c>
       <c r="E172" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F172" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
+          <t>anonymize_birthdate: 대표 연령대</t>
         </is>
       </c>
       <c r="G172" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
         </is>
       </c>
       <c r="H172" s="28" t="inlineStr">
@@ -10133,7 +10133,7 @@
     <row r="173">
       <c r="A173" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-PRIV-10</t>
         </is>
       </c>
       <c r="B173" s="27" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="E173" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F173" s="29" t="inlineStr">
         <is>
-          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
+          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
         </is>
       </c>
       <c r="G173" s="29" t="inlineStr">
         <is>
-          <t>표시값/식별자에 '홍길동' 미포함</t>
+          <t>생일 당일부터 다음 연령대</t>
         </is>
       </c>
       <c r="H173" s="28" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="174">
       <c r="A174" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-PRIV-11</t>
         </is>
       </c>
       <c r="B174" s="27" t="inlineStr">
@@ -10200,17 +10200,17 @@
       </c>
       <c r="E174" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F174" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: personal_info 저장</t>
+          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
         </is>
       </c>
       <c r="G174" s="29" t="inlineStr">
         <is>
-          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
+          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
         </is>
       </c>
       <c r="H174" s="28" t="inlineStr">
@@ -10227,7 +10227,7 @@
     <row r="175">
       <c r="A175" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-PRIV-12</t>
         </is>
       </c>
       <c r="B175" s="27" t="inlineStr">
@@ -10247,17 +10247,17 @@
       </c>
       <c r="E175" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F175" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
+          <t>anonymize_birthdate: 미래 날짜</t>
         </is>
       </c>
       <c r="G175" s="29" t="inlineStr">
         <is>
-          <t>행 1건, pseudonym_id 동일</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H175" s="28" t="inlineStr">
@@ -10274,7 +10274,7 @@
     <row r="176">
       <c r="A176" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-PRIV-13</t>
         </is>
       </c>
       <c r="B176" s="27" t="inlineStr">
@@ -10294,17 +10294,17 @@
       </c>
       <c r="E176" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F176" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
+          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
         </is>
       </c>
       <c r="G176" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None</t>
+          <t>연·월·일 숫자열이 결과에 없음</t>
         </is>
       </c>
       <c r="H176" s="28" t="inlineStr">
@@ -10321,7 +10321,7 @@
     <row r="177">
       <c r="A177" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-PRIV-14</t>
         </is>
       </c>
       <c r="B177" s="27" t="inlineStr">
@@ -10341,17 +10341,17 @@
       </c>
       <c r="E177" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F177" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 없는 사용자</t>
+          <t>process(pseudonym): 결과 객체</t>
         </is>
       </c>
       <c r="G177" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError, 행 미생성</t>
+          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
         </is>
       </c>
       <c r="H177" s="28" t="inlineStr">
@@ -10368,7 +10368,7 @@
     <row r="178">
       <c r="A178" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-PRIV-15</t>
         </is>
       </c>
       <c r="B178" s="27" t="inlineStr">
@@ -10388,17 +10388,17 @@
       </c>
       <c r="E178" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F178" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+          <t>process(anonymous): 식별자 없음</t>
         </is>
       </c>
       <c r="G178" s="29" t="inlineStr">
         <is>
-          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
         </is>
       </c>
       <c r="H178" s="28" t="inlineStr">
@@ -10415,7 +10415,7 @@
     <row r="179">
       <c r="A179" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-PRIV-16</t>
         </is>
       </c>
       <c r="B179" s="27" t="inlineStr">
@@ -10435,17 +10435,17 @@
       </c>
       <c r="E179" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F179" s="29" t="inlineStr">
         <is>
-          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+          <t>process: 허용되지 않는 mode</t>
         </is>
       </c>
       <c r="G179" s="29" t="inlineStr">
         <is>
-          <t>저장된 행 반환, 없으면 NotFoundError</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H179" s="28" t="inlineStr">
@@ -10462,7 +10462,7 @@
     <row r="180">
       <c r="A180" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-PRIV-17</t>
         </is>
       </c>
       <c r="B180" s="27" t="inlineStr">
@@ -10472,27 +10472,27 @@
       </c>
       <c r="C180" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D180" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E180" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F180" s="29" t="inlineStr">
         <is>
-          <t>seed: 사용자 3종 생성</t>
+          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
         </is>
       </c>
       <c r="G180" s="29" t="inlineStr">
         <is>
-          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H180" s="28" t="inlineStr">
@@ -10509,7 +10509,7 @@
     <row r="181">
       <c r="A181" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-PRIV-18</t>
         </is>
       </c>
       <c r="B181" s="27" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="C181" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D181" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E181" s="27" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="F181" s="29" t="inlineStr">
         <is>
-          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
         </is>
       </c>
       <c r="G181" s="29" t="inlineStr">
         <is>
-          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+          <t>표시값/식별자에 '홍길동' 미포함</t>
         </is>
       </c>
       <c r="H181" s="28" t="inlineStr">
@@ -10556,7 +10556,7 @@
     <row r="182">
       <c r="A182" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-PRIV-19</t>
         </is>
       </c>
       <c r="B182" s="27" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="C182" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D182" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E182" s="27" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="F182" s="29" t="inlineStr">
         <is>
-          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+          <t>process_and_store: personal_info 저장</t>
         </is>
       </c>
       <c r="G182" s="29" t="inlineStr">
         <is>
-          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
         </is>
       </c>
       <c r="H182" s="28" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="183">
       <c r="A183" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-PRIV-20</t>
         </is>
       </c>
       <c r="B183" s="27" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="C183" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D183" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E183" s="27" t="inlineStr">
@@ -10628,17 +10628,17 @@
       </c>
       <c r="F183" s="29" t="inlineStr">
         <is>
-          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
         </is>
       </c>
       <c r="G183" s="29" t="inlineStr">
         <is>
-          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+          <t>행 1건, pseudonym_id 동일</t>
         </is>
       </c>
       <c r="H183" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I183" s="30" t="n"/>
@@ -10650,7 +10650,7 @@
     <row r="184">
       <c r="A184" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-21</t>
         </is>
       </c>
       <c r="B184" s="27" t="inlineStr">
@@ -10665,22 +10665,22 @@
       </c>
       <c r="D184" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E184" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F184" s="29" t="inlineStr">
         <is>
-          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
         </is>
       </c>
       <c r="G184" s="29" t="inlineStr">
         <is>
-          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+          <t>level='anonymous', pseudonym_id=None</t>
         </is>
       </c>
       <c r="H184" s="28" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="185">
       <c r="A185" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-PRIV-22</t>
         </is>
       </c>
       <c r="B185" s="27" t="inlineStr">
@@ -10707,27 +10707,27 @@
       </c>
       <c r="C185" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D185" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E185" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F185" s="29" t="inlineStr">
         <is>
-          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+          <t>process_and_store: 없는 사용자</t>
         </is>
       </c>
       <c r="G185" s="29" t="inlineStr">
         <is>
-          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+          <t>NotFoundError, 행 미생성</t>
         </is>
       </c>
       <c r="H185" s="28" t="inlineStr">
@@ -10741,9 +10741,385 @@
         <v/>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-23</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C186" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D186" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E186" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F186" s="29" t="inlineStr">
+        <is>
+          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+        </is>
+      </c>
+      <c r="G186" s="29" t="inlineStr">
+        <is>
+          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+        </is>
+      </c>
+      <c r="H186" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I186" s="30" t="n"/>
+      <c r="J186" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A186,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="27" t="inlineStr">
+        <is>
+          <t>UT-PRIV-24</t>
+        </is>
+      </c>
+      <c r="B187" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C187" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D187" s="28" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="E187" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F187" s="29" t="inlineStr">
+        <is>
+          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+        </is>
+      </c>
+      <c r="G187" s="29" t="inlineStr">
+        <is>
+          <t>저장된 행 반환, 없으면 NotFoundError</t>
+        </is>
+      </c>
+      <c r="H187" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I187" s="30" t="n"/>
+      <c r="J187" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A187,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-01</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C188" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D188" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E188" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F188" s="29" t="inlineStr">
+        <is>
+          <t>seed: 사용자 3종 생성</t>
+        </is>
+      </c>
+      <c r="G188" s="29" t="inlineStr">
+        <is>
+          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+        </is>
+      </c>
+      <c r="H188" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I188" s="30" t="n"/>
+      <c r="J188" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A188,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B189" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C189" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D189" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E189" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F189" s="29" t="inlineStr">
+        <is>
+          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+        </is>
+      </c>
+      <c r="G189" s="29" t="inlineStr">
+        <is>
+          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+        </is>
+      </c>
+      <c r="H189" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I189" s="30" t="n"/>
+      <c r="J189" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A189,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B190" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C190" s="27" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="D190" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E190" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F190" s="29" t="inlineStr">
+        <is>
+          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+        </is>
+      </c>
+      <c r="G190" s="29" t="inlineStr">
+        <is>
+          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+        </is>
+      </c>
+      <c r="H190" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I190" s="30" t="n"/>
+      <c r="J190" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A190,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B191" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C191" s="27" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="D191" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E191" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F191" s="29" t="inlineStr">
+        <is>
+          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+        </is>
+      </c>
+      <c r="G191" s="29" t="inlineStr">
+        <is>
+          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+        </is>
+      </c>
+      <c r="H191" s="28" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="I191" s="30" t="n"/>
+      <c r="J191" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A191,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B192" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C192" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D192" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E192" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F192" s="29" t="inlineStr">
+        <is>
+          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+        </is>
+      </c>
+      <c r="G192" s="29" t="inlineStr">
+        <is>
+          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+        </is>
+      </c>
+      <c r="H192" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I192" s="30" t="n"/>
+      <c r="J192" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A192,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B193" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C193" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D193" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E193" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F193" s="29" t="inlineStr">
+        <is>
+          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+        </is>
+      </c>
+      <c r="G193" s="29" t="inlineStr">
+        <is>
+          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+        </is>
+      </c>
+      <c r="H193" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I193" s="30" t="n"/>
+      <c r="J193" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A193,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J185"/>
-  <conditionalFormatting sqref="J5:J185">
+  <autoFilter ref="A4:J193"/>
+  <conditionalFormatting sqref="J5:J193">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -10779,7 +11155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11047,7 +11423,7 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>IT-01</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="B11" s="32">
@@ -11075,7 +11451,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>IT-02</t>
+          <t>ST-04-N1</t>
         </is>
       </c>
       <c r="B12" s="32">
@@ -11103,7 +11479,7 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>IT-03</t>
+          <t>ST-04-N2</t>
         </is>
       </c>
       <c r="B13" s="32">
@@ -11115,7 +11491,7 @@
         <v/>
       </c>
       <c r="D13" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0</v>
@@ -11131,7 +11507,7 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>IT-04</t>
+          <t>ST-04-N3</t>
         </is>
       </c>
       <c r="B14" s="32">
@@ -11159,7 +11535,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>IT-05</t>
+          <t>ST-04-N4</t>
         </is>
       </c>
       <c r="B15" s="32">
@@ -11187,7 +11563,7 @@
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>IT-06</t>
+          <t>IT-01</t>
         </is>
       </c>
       <c r="B16" s="32">
@@ -11215,7 +11591,7 @@
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>IT-07</t>
+          <t>IT-02</t>
         </is>
       </c>
       <c r="B17" s="32">
@@ -11243,7 +11619,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>IT-08</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="B18" s="32">
@@ -11255,7 +11631,7 @@
         <v/>
       </c>
       <c r="D18" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>0</v>
@@ -11271,7 +11647,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>IT-09</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="B19" s="32">
@@ -11299,7 +11675,7 @@
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>IT-10</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="B20" s="32">
@@ -11327,7 +11703,7 @@
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>IT-11</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="B21" s="32">
@@ -11339,13 +11715,13 @@
         <v/>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>0</v>
@@ -11355,7 +11731,7 @@
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>IT-12</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="B22" s="32">
@@ -11383,7 +11759,7 @@
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>IT-13</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="B23" s="32">
@@ -11395,13 +11771,13 @@
         <v/>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>0</v>
@@ -11411,7 +11787,7 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>IT-14</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="B24" s="32">
@@ -11423,13 +11799,13 @@
         <v/>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>0</v>
@@ -11439,7 +11815,7 @@
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>IT-15</t>
+          <t>IT-10</t>
         </is>
       </c>
       <c r="B25" s="32">
@@ -11451,13 +11827,13 @@
         <v/>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>0</v>
@@ -11467,7 +11843,7 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>IT-16</t>
+          <t>IT-11</t>
         </is>
       </c>
       <c r="B26" s="32">
@@ -11479,13 +11855,13 @@
         <v/>
       </c>
       <c r="D26" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>0</v>
@@ -11495,7 +11871,7 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>IT-17</t>
+          <t>IT-12</t>
         </is>
       </c>
       <c r="B27" s="32">
@@ -11507,13 +11883,13 @@
         <v/>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>0</v>
@@ -11523,7 +11899,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>IT-18</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="B28" s="32">
@@ -11551,7 +11927,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>IT-19</t>
+          <t>IT-14</t>
         </is>
       </c>
       <c r="B29" s="32">
@@ -11579,7 +11955,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>IT-20</t>
+          <t>IT-15</t>
         </is>
       </c>
       <c r="B30" s="32">
@@ -11597,7 +11973,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>0</v>
@@ -11607,7 +11983,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>IT-21</t>
+          <t>IT-16</t>
         </is>
       </c>
       <c r="B31" s="32">
@@ -11625,7 +12001,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>0</v>
@@ -11635,7 +12011,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>IT-22</t>
+          <t>IT-17</t>
         </is>
       </c>
       <c r="B32" s="32">
@@ -11663,7 +12039,7 @@
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>IT-23</t>
+          <t>IT-18</t>
         </is>
       </c>
       <c r="B33" s="32">
@@ -11675,13 +12051,13 @@
         <v/>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>0</v>
@@ -11691,7 +12067,7 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>IT-24</t>
+          <t>IT-19</t>
         </is>
       </c>
       <c r="B34" s="32">
@@ -11703,13 +12079,13 @@
         <v/>
       </c>
       <c r="D34" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>0</v>
@@ -11719,7 +12095,7 @@
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>IT-25</t>
+          <t>IT-20</t>
         </is>
       </c>
       <c r="B35" s="32">
@@ -11731,13 +12107,13 @@
         <v/>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="23" t="n">
         <v>0</v>
@@ -11747,7 +12123,7 @@
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>IT-26</t>
+          <t>IT-21</t>
         </is>
       </c>
       <c r="B36" s="32">
@@ -11759,13 +12135,13 @@
         <v/>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="23" t="n">
         <v>0</v>
@@ -11775,7 +12151,7 @@
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>IT-27</t>
+          <t>IT-22</t>
         </is>
       </c>
       <c r="B37" s="32">
@@ -11803,7 +12179,7 @@
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>IT-28</t>
+          <t>IT-23</t>
         </is>
       </c>
       <c r="B38" s="32">
@@ -11831,7 +12207,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>IT-29</t>
+          <t>IT-24</t>
         </is>
       </c>
       <c r="B39" s="32">
@@ -11859,7 +12235,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>IT-30</t>
+          <t>IT-25</t>
         </is>
       </c>
       <c r="B40" s="32">
@@ -11887,7 +12263,7 @@
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>IT-31</t>
+          <t>IT-26</t>
         </is>
       </c>
       <c r="B41" s="32">
@@ -11915,7 +12291,7 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>IT-32</t>
+          <t>IT-27</t>
         </is>
       </c>
       <c r="B42" s="32">
@@ -11943,7 +12319,7 @@
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>IT-33</t>
+          <t>IT-28</t>
         </is>
       </c>
       <c r="B43" s="32">
@@ -11955,13 +12331,13 @@
         <v/>
       </c>
       <c r="D43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>0</v>
@@ -11971,7 +12347,7 @@
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>IT-34</t>
+          <t>IT-29</t>
         </is>
       </c>
       <c r="B44" s="32">
@@ -11983,13 +12359,13 @@
         <v/>
       </c>
       <c r="D44" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E44" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>0</v>
@@ -11999,7 +12375,7 @@
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>IT-35</t>
+          <t>IT-30</t>
         </is>
       </c>
       <c r="B45" s="32">
@@ -12011,13 +12387,13 @@
         <v/>
       </c>
       <c r="D45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E45" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>0</v>
@@ -12027,7 +12403,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>IT-36</t>
+          <t>IT-31</t>
         </is>
       </c>
       <c r="B46" s="32">
@@ -12039,13 +12415,13 @@
         <v/>
       </c>
       <c r="D46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G46" s="23" t="n">
         <v>0</v>
@@ -12055,7 +12431,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>IT-37</t>
+          <t>IT-32</t>
         </is>
       </c>
       <c r="B47" s="32">
@@ -12067,13 +12443,13 @@
         <v/>
       </c>
       <c r="D47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G47" s="23" t="n">
         <v>0</v>
@@ -12083,7 +12459,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>IT-38</t>
+          <t>IT-33</t>
         </is>
       </c>
       <c r="B48" s="32">
@@ -12111,7 +12487,7 @@
     <row r="49">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>IT-39</t>
+          <t>IT-34</t>
         </is>
       </c>
       <c r="B49" s="32">
@@ -12139,7 +12515,7 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>IT-40</t>
+          <t>IT-35</t>
         </is>
       </c>
       <c r="B50" s="32">
@@ -12167,7 +12543,7 @@
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-01</t>
+          <t>IT-36</t>
         </is>
       </c>
       <c r="B51" s="32">
@@ -12195,7 +12571,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-02</t>
+          <t>IT-37</t>
         </is>
       </c>
       <c r="B52" s="32">
@@ -12223,7 +12599,7 @@
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-03</t>
+          <t>IT-38</t>
         </is>
       </c>
       <c r="B53" s="32">
@@ -12251,7 +12627,7 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-04</t>
+          <t>IT-39</t>
         </is>
       </c>
       <c r="B54" s="32">
@@ -12279,7 +12655,7 @@
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-05</t>
+          <t>IT-40</t>
         </is>
       </c>
       <c r="B55" s="32">
@@ -12291,7 +12667,7 @@
         <v/>
       </c>
       <c r="D55" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E55" s="23" t="n">
         <v>0</v>
@@ -12307,7 +12683,7 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-06</t>
+          <t>IT-41</t>
         </is>
       </c>
       <c r="B56" s="32">
@@ -12335,7 +12711,7 @@
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-07</t>
+          <t>IT-42</t>
         </is>
       </c>
       <c r="B57" s="32">
@@ -12363,7 +12739,7 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-08</t>
+          <t>IT-43</t>
         </is>
       </c>
       <c r="B58" s="32">
@@ -12375,7 +12751,7 @@
         <v/>
       </c>
       <c r="D58" s="23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E58" s="23" t="n">
         <v>0</v>
@@ -12391,7 +12767,7 @@
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-09</t>
+          <t>IT-ATK-01</t>
         </is>
       </c>
       <c r="B59" s="32">
@@ -12419,7 +12795,7 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-10</t>
+          <t>IT-ATK-02</t>
         </is>
       </c>
       <c r="B60" s="32">
@@ -12447,7 +12823,7 @@
     <row r="61">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-11</t>
+          <t>IT-ATK-03</t>
         </is>
       </c>
       <c r="B61" s="32">
@@ -12475,7 +12851,7 @@
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-12</t>
+          <t>IT-ATK-04</t>
         </is>
       </c>
       <c r="B62" s="32">
@@ -12503,7 +12879,7 @@
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-13</t>
+          <t>IT-ATK-05</t>
         </is>
       </c>
       <c r="B63" s="32">
@@ -12515,7 +12891,7 @@
         <v/>
       </c>
       <c r="D63" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E63" s="23" t="n">
         <v>0</v>
@@ -12531,7 +12907,7 @@
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-14</t>
+          <t>IT-ATK-06</t>
         </is>
       </c>
       <c r="B64" s="32">
@@ -12559,7 +12935,7 @@
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-15</t>
+          <t>IT-ATK-07</t>
         </is>
       </c>
       <c r="B65" s="32">
@@ -12587,7 +12963,7 @@
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-16</t>
+          <t>IT-ATK-08</t>
         </is>
       </c>
       <c r="B66" s="32">
@@ -12599,7 +12975,7 @@
         <v/>
       </c>
       <c r="D66" s="23" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E66" s="23" t="n">
         <v>0</v>
@@ -12615,7 +12991,7 @@
     <row r="67">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-17</t>
+          <t>IT-ATK-09</t>
         </is>
       </c>
       <c r="B67" s="32">
@@ -12643,7 +13019,7 @@
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-18</t>
+          <t>IT-ATK-10</t>
         </is>
       </c>
       <c r="B68" s="32">
@@ -12671,7 +13047,7 @@
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-19</t>
+          <t>IT-ATK-11</t>
         </is>
       </c>
       <c r="B69" s="32">
@@ -12699,7 +13075,7 @@
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>IT-ATK-20</t>
+          <t>IT-ATK-12</t>
         </is>
       </c>
       <c r="B70" s="32">
@@ -12727,7 +13103,7 @@
     <row r="71">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>UT-ATK-01</t>
+          <t>IT-ATK-13</t>
         </is>
       </c>
       <c r="B71" s="32">
@@ -12755,7 +13131,7 @@
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>UT-ATK-02</t>
+          <t>IT-ATK-14</t>
         </is>
       </c>
       <c r="B72" s="32">
@@ -12783,7 +13159,7 @@
     <row r="73">
       <c r="A73" s="22" t="inlineStr">
         <is>
-          <t>UT-ATK-03</t>
+          <t>IT-ATK-15</t>
         </is>
       </c>
       <c r="B73" s="32">
@@ -12811,7 +13187,7 @@
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-ATK-16</t>
         </is>
       </c>
       <c r="B74" s="32">
@@ -12839,7 +13215,7 @@
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>IT-ATK-17</t>
         </is>
       </c>
       <c r="B75" s="32">
@@ -12867,7 +13243,7 @@
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>IT-ATK-18</t>
         </is>
       </c>
       <c r="B76" s="32">
@@ -12895,7 +13271,7 @@
     <row r="77">
       <c r="A77" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>IT-ATK-19</t>
         </is>
       </c>
       <c r="B77" s="32">
@@ -12923,7 +13299,7 @@
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>IT-ATK-20</t>
         </is>
       </c>
       <c r="B78" s="32">
@@ -12951,7 +13327,7 @@
     <row r="79">
       <c r="A79" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>UT-ATK-01</t>
         </is>
       </c>
       <c r="B79" s="32">
@@ -12963,7 +13339,7 @@
         <v/>
       </c>
       <c r="D79" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" s="23" t="n">
         <v>0</v>
@@ -12979,7 +13355,7 @@
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>UT-ATK-02</t>
         </is>
       </c>
       <c r="B80" s="32">
@@ -13007,7 +13383,7 @@
     <row r="81">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>UT-ATK-03</t>
         </is>
       </c>
       <c r="B81" s="32">
@@ -13035,7 +13411,7 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B82" s="32">
@@ -13047,7 +13423,7 @@
         <v/>
       </c>
       <c r="D82" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="23" t="n">
         <v>0</v>
@@ -13063,7 +13439,7 @@
     <row r="83">
       <c r="A83" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B83" s="32">
@@ -13075,7 +13451,7 @@
         <v/>
       </c>
       <c r="D83" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E83" s="23" t="n">
         <v>0</v>
@@ -13091,7 +13467,7 @@
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B84" s="32">
@@ -13119,7 +13495,7 @@
     <row r="85">
       <c r="A85" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B85" s="32">
@@ -13147,7 +13523,7 @@
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B86" s="32">
@@ -13175,7 +13551,7 @@
     <row r="87">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B87" s="32">
@@ -13203,7 +13579,7 @@
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B88" s="32">
@@ -13215,7 +13591,7 @@
         <v/>
       </c>
       <c r="D88" s="23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E88" s="23" t="n">
         <v>0</v>
@@ -13231,7 +13607,7 @@
     <row r="89">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B89" s="32">
@@ -13243,7 +13619,7 @@
         <v/>
       </c>
       <c r="D89" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="23" t="n">
         <v>0</v>
@@ -13259,7 +13635,7 @@
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B90" s="32">
@@ -13271,7 +13647,7 @@
         <v/>
       </c>
       <c r="D90" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E90" s="23" t="n">
         <v>0</v>
@@ -13287,7 +13663,7 @@
     <row r="91">
       <c r="A91" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B91" s="32">
@@ -13299,7 +13675,7 @@
         <v/>
       </c>
       <c r="D91" s="23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E91" s="23" t="n">
         <v>0</v>
@@ -13315,7 +13691,7 @@
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B92" s="32">
@@ -13343,7 +13719,7 @@
     <row r="93">
       <c r="A93" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B93" s="32">
@@ -13371,7 +13747,7 @@
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B94" s="32">
@@ -13399,7 +13775,7 @@
     <row r="95">
       <c r="A95" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B95" s="32">
@@ -13411,7 +13787,7 @@
         <v/>
       </c>
       <c r="D95" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E95" s="23" t="n">
         <v>0</v>
@@ -13427,7 +13803,7 @@
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B96" s="32">
@@ -13439,7 +13815,7 @@
         <v/>
       </c>
       <c r="D96" s="23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E96" s="23" t="n">
         <v>0</v>
@@ -13455,7 +13831,7 @@
     <row r="97">
       <c r="A97" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B97" s="32">
@@ -13467,7 +13843,7 @@
         <v/>
       </c>
       <c r="D97" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97" s="23" t="n">
         <v>0</v>
@@ -13483,7 +13859,7 @@
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B98" s="32">
@@ -13495,13 +13871,13 @@
         <v/>
       </c>
       <c r="D98" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E98" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F98" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="23" t="n">
         <v>0</v>
@@ -13511,7 +13887,7 @@
     <row r="99">
       <c r="A99" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B99" s="32">
@@ -13523,13 +13899,13 @@
         <v/>
       </c>
       <c r="D99" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E99" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G99" s="23" t="n">
         <v>0</v>
@@ -13539,7 +13915,7 @@
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B100" s="32">
@@ -13551,13 +13927,13 @@
         <v/>
       </c>
       <c r="D100" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G100" s="23" t="n">
         <v>0</v>
@@ -13567,7 +13943,7 @@
     <row r="101">
       <c r="A101" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B101" s="32">
@@ -13579,13 +13955,13 @@
         <v/>
       </c>
       <c r="D101" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="23" t="n">
         <v>0</v>
@@ -13595,7 +13971,7 @@
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B102" s="32">
@@ -13607,13 +13983,13 @@
         <v/>
       </c>
       <c r="D102" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G102" s="23" t="n">
         <v>0</v>
@@ -13623,7 +13999,7 @@
     <row r="103">
       <c r="A103" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B103" s="32">
@@ -13635,13 +14011,13 @@
         <v/>
       </c>
       <c r="D103" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="23" t="n">
         <v>0</v>
@@ -13651,7 +14027,7 @@
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B104" s="32">
@@ -13663,13 +14039,13 @@
         <v/>
       </c>
       <c r="D104" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E104" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G104" s="23" t="n">
         <v>0</v>
@@ -13679,7 +14055,7 @@
     <row r="105">
       <c r="A105" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B105" s="32">
@@ -13691,23 +14067,23 @@
         <v/>
       </c>
       <c r="D105" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G105" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H105" s="22" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B106" s="32">
@@ -13719,13 +14095,13 @@
         <v/>
       </c>
       <c r="D106" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G106" s="23" t="n">
         <v>0</v>
@@ -13735,7 +14111,7 @@
     <row r="107">
       <c r="A107" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B107" s="32">
@@ -13747,13 +14123,13 @@
         <v/>
       </c>
       <c r="D107" s="23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E107" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" s="23" t="n">
         <v>0</v>
@@ -13763,7 +14139,7 @@
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B108" s="32">
@@ -13775,13 +14151,13 @@
         <v/>
       </c>
       <c r="D108" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E108" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G108" s="23" t="n">
         <v>0</v>
@@ -13791,7 +14167,7 @@
     <row r="109">
       <c r="A109" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B109" s="32">
@@ -13803,13 +14179,13 @@
         <v/>
       </c>
       <c r="D109" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F109" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="23" t="n">
         <v>0</v>
@@ -13819,7 +14195,7 @@
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B110" s="32">
@@ -13831,13 +14207,13 @@
         <v/>
       </c>
       <c r="D110" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="23" t="n">
         <v>0</v>
@@ -13847,7 +14223,7 @@
     <row r="111">
       <c r="A111" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B111" s="32">
@@ -13859,13 +14235,13 @@
         <v/>
       </c>
       <c r="D111" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E111" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="23" t="n">
         <v>0</v>
@@ -13875,7 +14251,7 @@
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B112" s="32">
@@ -13893,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" s="23" t="n">
         <v>0</v>
@@ -13903,7 +14279,7 @@
     <row r="113">
       <c r="A113" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B113" s="32">
@@ -13921,17 +14297,17 @@
         <v>0</v>
       </c>
       <c r="F113" s="23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G113" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H113" s="22" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B114" s="32">
@@ -13949,7 +14325,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G114" s="23" t="n">
         <v>0</v>
@@ -13959,7 +14335,7 @@
     <row r="115">
       <c r="A115" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B115" s="32">
@@ -13987,7 +14363,7 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B116" s="32">
@@ -14005,7 +14381,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" s="23" t="n">
         <v>0</v>
@@ -14015,7 +14391,7 @@
     <row r="117">
       <c r="A117" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B117" s="32">
@@ -14043,7 +14419,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B118" s="32">
@@ -14055,13 +14431,13 @@
         <v/>
       </c>
       <c r="D118" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="23" t="n">
         <v>0</v>
@@ -14071,7 +14447,7 @@
     <row r="119">
       <c r="A119" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B119" s="32">
@@ -14083,13 +14459,13 @@
         <v/>
       </c>
       <c r="D119" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="23" t="n">
         <v>0</v>
@@ -14099,7 +14475,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B120" s="32">
@@ -14111,13 +14487,13 @@
         <v/>
       </c>
       <c r="D120" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="23" t="n">
         <v>0</v>
@@ -14127,7 +14503,7 @@
     <row r="121">
       <c r="A121" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B121" s="32">
@@ -14139,13 +14515,13 @@
         <v/>
       </c>
       <c r="D121" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="23" t="n">
         <v>0</v>
@@ -14155,7 +14531,7 @@
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B122" s="32">
@@ -14167,13 +14543,13 @@
         <v/>
       </c>
       <c r="D122" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E122" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F122" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="23" t="n">
         <v>0</v>
@@ -14183,7 +14559,7 @@
     <row r="123">
       <c r="A123" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B123" s="32">
@@ -14195,13 +14571,13 @@
         <v/>
       </c>
       <c r="D123" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" s="23" t="n">
         <v>0</v>
@@ -14211,7 +14587,7 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B124" s="32">
@@ -14229,7 +14605,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G124" s="23" t="n">
         <v>0</v>
@@ -14239,7 +14615,7 @@
     <row r="125">
       <c r="A125" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B125" s="32">
@@ -14267,7 +14643,7 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B126" s="32">
@@ -14285,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G126" s="23" t="n">
         <v>0</v>
@@ -14295,7 +14671,7 @@
     <row r="127">
       <c r="A127" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B127" s="32">
@@ -14323,7 +14699,7 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B128" s="32">
@@ -14351,7 +14727,7 @@
     <row r="129">
       <c r="A129" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B129" s="32">
@@ -14379,7 +14755,7 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B130" s="32">
@@ -14407,7 +14783,7 @@
     <row r="131">
       <c r="A131" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B131" s="32">
@@ -14435,7 +14811,7 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B132" s="32">
@@ -14453,7 +14829,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G132" s="23" t="n">
         <v>0</v>
@@ -14463,7 +14839,7 @@
     <row r="133">
       <c r="A133" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B133" s="32">
@@ -14491,7 +14867,7 @@
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B134" s="32">
@@ -14509,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" s="23" t="n">
         <v>0</v>
@@ -14519,7 +14895,7 @@
     <row r="135">
       <c r="A135" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B135" s="32">
@@ -14547,7 +14923,7 @@
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B136" s="32">
@@ -14575,7 +14951,7 @@
     <row r="137">
       <c r="A137" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B137" s="32">
@@ -14603,7 +14979,7 @@
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B138" s="32">
@@ -14631,7 +15007,7 @@
     <row r="139">
       <c r="A139" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-01</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B139" s="32">
@@ -14643,13 +15019,13 @@
         <v/>
       </c>
       <c r="D139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G139" s="23" t="n">
         <v>0</v>
@@ -14659,7 +15035,7 @@
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-02</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B140" s="32">
@@ -14671,13 +15047,13 @@
         <v/>
       </c>
       <c r="D140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E140" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G140" s="23" t="n">
         <v>0</v>
@@ -14687,7 +15063,7 @@
     <row r="141">
       <c r="A141" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-03</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B141" s="32">
@@ -14699,13 +15075,13 @@
         <v/>
       </c>
       <c r="D141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E141" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G141" s="23" t="n">
         <v>0</v>
@@ -14715,7 +15091,7 @@
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-04</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B142" s="32">
@@ -14727,13 +15103,13 @@
         <v/>
       </c>
       <c r="D142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E142" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G142" s="23" t="n">
         <v>0</v>
@@ -14743,7 +15119,7 @@
     <row r="143">
       <c r="A143" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-05</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B143" s="32">
@@ -14755,13 +15131,13 @@
         <v/>
       </c>
       <c r="D143" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E143" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="23" t="n">
         <v>0</v>
@@ -14771,7 +15147,7 @@
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-06</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B144" s="32">
@@ -14783,13 +15159,13 @@
         <v/>
       </c>
       <c r="D144" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E144" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G144" s="23" t="n">
         <v>0</v>
@@ -14799,7 +15175,7 @@
     <row r="145">
       <c r="A145" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-07</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B145" s="32">
@@ -14811,13 +15187,13 @@
         <v/>
       </c>
       <c r="D145" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E145" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G145" s="23" t="n">
         <v>0</v>
@@ -14827,7 +15203,7 @@
     <row r="146">
       <c r="A146" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-08</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B146" s="32">
@@ -14839,13 +15215,13 @@
         <v/>
       </c>
       <c r="D146" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E146" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" s="23" t="n">
         <v>0</v>
@@ -14855,7 +15231,7 @@
     <row r="147">
       <c r="A147" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-09</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B147" s="32">
@@ -14883,7 +15259,7 @@
     <row r="148">
       <c r="A148" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-10</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B148" s="32">
@@ -14911,7 +15287,7 @@
     <row r="149">
       <c r="A149" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-11</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B149" s="32">
@@ -14939,7 +15315,7 @@
     <row r="150">
       <c r="A150" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-12</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B150" s="32">
@@ -14967,7 +15343,7 @@
     <row r="151">
       <c r="A151" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-13</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B151" s="32">
@@ -14979,7 +15355,7 @@
         <v/>
       </c>
       <c r="D151" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" s="23" t="n">
         <v>0</v>
@@ -14995,7 +15371,7 @@
     <row r="152">
       <c r="A152" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-14</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B152" s="32">
@@ -15023,7 +15399,7 @@
     <row r="153">
       <c r="A153" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-15</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B153" s="32">
@@ -15051,7 +15427,7 @@
     <row r="154">
       <c r="A154" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-16</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B154" s="32">
@@ -15063,7 +15439,7 @@
         <v/>
       </c>
       <c r="D154" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="23" t="n">
         <v>0</v>
@@ -15079,7 +15455,7 @@
     <row r="155">
       <c r="A155" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B155" s="32">
@@ -15091,13 +15467,13 @@
         <v/>
       </c>
       <c r="D155" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F155" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" s="23" t="n">
         <v>0</v>
@@ -15107,7 +15483,7 @@
     <row r="156">
       <c r="A156" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B156" s="32">
@@ -15119,13 +15495,13 @@
         <v/>
       </c>
       <c r="D156" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" s="23" t="n">
         <v>0</v>
@@ -15135,7 +15511,7 @@
     <row r="157">
       <c r="A157" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B157" s="32">
@@ -15147,13 +15523,13 @@
         <v/>
       </c>
       <c r="D157" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F157" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G157" s="23" t="n">
         <v>0</v>
@@ -15163,7 +15539,7 @@
     <row r="158">
       <c r="A158" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B158" s="32">
@@ -15175,13 +15551,13 @@
         <v/>
       </c>
       <c r="D158" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F158" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G158" s="23" t="n">
         <v>0</v>
@@ -15191,7 +15567,7 @@
     <row r="159">
       <c r="A159" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B159" s="32">
@@ -15203,13 +15579,13 @@
         <v/>
       </c>
       <c r="D159" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" s="23" t="n">
         <v>0</v>
@@ -15219,7 +15595,7 @@
     <row r="160">
       <c r="A160" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B160" s="32">
@@ -15231,13 +15607,13 @@
         <v/>
       </c>
       <c r="D160" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F160" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G160" s="23" t="n">
         <v>0</v>
@@ -15247,7 +15623,7 @@
     <row r="161">
       <c r="A161" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B161" s="32">
@@ -15259,13 +15635,13 @@
         <v/>
       </c>
       <c r="D161" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" s="23" t="n">
         <v>0</v>
@@ -15275,7 +15651,7 @@
     <row r="162">
       <c r="A162" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B162" s="32">
@@ -15287,13 +15663,13 @@
         <v/>
       </c>
       <c r="D162" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F162" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G162" s="23" t="n">
         <v>0</v>
@@ -15303,7 +15679,7 @@
     <row r="163">
       <c r="A163" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B163" s="32">
@@ -15331,7 +15707,7 @@
     <row r="164">
       <c r="A164" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B164" s="32">
@@ -15349,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="F164" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G164" s="23" t="n">
         <v>0</v>
@@ -15359,7 +15735,7 @@
     <row r="165">
       <c r="A165" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-PRIV-03</t>
         </is>
       </c>
       <c r="B165" s="32">
@@ -15377,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="F165" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G165" s="23" t="n">
         <v>0</v>
@@ -15387,7 +15763,7 @@
     <row r="166">
       <c r="A166" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-PRIV-04</t>
         </is>
       </c>
       <c r="B166" s="32">
@@ -15405,7 +15781,7 @@
         <v>0</v>
       </c>
       <c r="F166" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G166" s="23" t="n">
         <v>0</v>
@@ -15415,7 +15791,7 @@
     <row r="167">
       <c r="A167" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-PRIV-05</t>
         </is>
       </c>
       <c r="B167" s="32">
@@ -15443,7 +15819,7 @@
     <row r="168">
       <c r="A168" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-PRIV-06</t>
         </is>
       </c>
       <c r="B168" s="32">
@@ -15461,7 +15837,7 @@
         <v>0</v>
       </c>
       <c r="F168" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G168" s="23" t="n">
         <v>0</v>
@@ -15471,7 +15847,7 @@
     <row r="169">
       <c r="A169" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-PRIV-07</t>
         </is>
       </c>
       <c r="B169" s="32">
@@ -15499,7 +15875,7 @@
     <row r="170">
       <c r="A170" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-PRIV-08</t>
         </is>
       </c>
       <c r="B170" s="32">
@@ -15517,7 +15893,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G170" s="23" t="n">
         <v>0</v>
@@ -15527,7 +15903,7 @@
     <row r="171">
       <c r="A171" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-PRIV-09</t>
         </is>
       </c>
       <c r="B171" s="32">
@@ -15555,7 +15931,7 @@
     <row r="172">
       <c r="A172" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-PRIV-10</t>
         </is>
       </c>
       <c r="B172" s="32">
@@ -15573,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G172" s="23" t="n">
         <v>0</v>
@@ -15583,7 +15959,7 @@
     <row r="173">
       <c r="A173" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-PRIV-11</t>
         </is>
       </c>
       <c r="B173" s="32">
@@ -15611,7 +15987,7 @@
     <row r="174">
       <c r="A174" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-PRIV-12</t>
         </is>
       </c>
       <c r="B174" s="32">
@@ -15639,7 +16015,7 @@
     <row r="175">
       <c r="A175" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-PRIV-13</t>
         </is>
       </c>
       <c r="B175" s="32">
@@ -15667,7 +16043,7 @@
     <row r="176">
       <c r="A176" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-PRIV-14</t>
         </is>
       </c>
       <c r="B176" s="32">
@@ -15695,7 +16071,7 @@
     <row r="177">
       <c r="A177" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-PRIV-15</t>
         </is>
       </c>
       <c r="B177" s="32">
@@ -15723,7 +16099,7 @@
     <row r="178">
       <c r="A178" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-PRIV-16</t>
         </is>
       </c>
       <c r="B178" s="32">
@@ -15741,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="F178" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G178" s="23" t="n">
         <v>0</v>
@@ -15751,7 +16127,7 @@
     <row r="179">
       <c r="A179" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-PRIV-17</t>
         </is>
       </c>
       <c r="B179" s="32">
@@ -15779,7 +16155,7 @@
     <row r="180">
       <c r="A180" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-PRIV-18</t>
         </is>
       </c>
       <c r="B180" s="32">
@@ -15797,7 +16173,7 @@
         <v>0</v>
       </c>
       <c r="F180" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G180" s="23" t="n">
         <v>0</v>
@@ -15807,7 +16183,7 @@
     <row r="181">
       <c r="A181" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-PRIV-19</t>
         </is>
       </c>
       <c r="B181" s="32">
@@ -15835,7 +16211,7 @@
     <row r="182">
       <c r="A182" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-PRIV-20</t>
         </is>
       </c>
       <c r="B182" s="32">
@@ -15863,7 +16239,7 @@
     <row r="183">
       <c r="A183" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-21</t>
         </is>
       </c>
       <c r="B183" s="32">
@@ -15891,7 +16267,7 @@
     <row r="184">
       <c r="A184" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-PRIV-22</t>
         </is>
       </c>
       <c r="B184" s="32">
@@ -15915,6 +16291,230 @@
         <v>0</v>
       </c>
       <c r="H184" s="22" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-23</t>
+        </is>
+      </c>
+      <c r="B185" s="32">
+        <f>IF(E185&gt;0,"FAIL",IF(F185&gt;0,"RED",IF(D185&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C185" s="23">
+        <f>SUM(D185:G185)</f>
+        <v/>
+      </c>
+      <c r="D185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="22" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>UT-PRIV-24</t>
+        </is>
+      </c>
+      <c r="B186" s="32">
+        <f>IF(E186&gt;0,"FAIL",IF(F186&gt;0,"RED",IF(D186&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C186" s="23">
+        <f>SUM(D186:G186)</f>
+        <v/>
+      </c>
+      <c r="D186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="22" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-01</t>
+        </is>
+      </c>
+      <c r="B187" s="32">
+        <f>IF(E187&gt;0,"FAIL",IF(F187&gt;0,"RED",IF(D187&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C187" s="23">
+        <f>SUM(D187:G187)</f>
+        <v/>
+      </c>
+      <c r="D187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" s="22" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B188" s="32">
+        <f>IF(E188&gt;0,"FAIL",IF(F188&gt;0,"RED",IF(D188&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C188" s="23">
+        <f>SUM(D188:G188)</f>
+        <v/>
+      </c>
+      <c r="D188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="22" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B189" s="32">
+        <f>IF(E189&gt;0,"FAIL",IF(F189&gt;0,"RED",IF(D189&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C189" s="23">
+        <f>SUM(D189:G189)</f>
+        <v/>
+      </c>
+      <c r="D189" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" s="22" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B190" s="32">
+        <f>IF(E190&gt;0,"FAIL",IF(F190&gt;0,"RED",IF(D190&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C190" s="23">
+        <f>SUM(D190:G190)</f>
+        <v/>
+      </c>
+      <c r="D190" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" s="22" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B191" s="32">
+        <f>IF(E191&gt;0,"FAIL",IF(F191&gt;0,"RED",IF(D191&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C191" s="23">
+        <f>SUM(D191:G191)</f>
+        <v/>
+      </c>
+      <c r="D191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="22" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B192" s="32">
+        <f>IF(E192&gt;0,"FAIL",IF(F192&gt;0,"RED",IF(D192&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C192" s="23">
+        <f>SUM(D192:G192)</f>
+        <v/>
+      </c>
+      <c r="D192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="22" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B600">
@@ -15945,7 +16545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16746,6 +17346,48 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-25 18:53</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>feature/sc04-cavp-apply</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>3f02fb8</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>189</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>113</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>76</v>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>365</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="K21" s="36">
+        <f>IFERROR(E21/(E21+F21+G21),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$22</f>
+              <f>'실행이력'!$A$4:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$22</f>
+              <f>'실행이력'!$E$4:$E$23</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$22</f>
+              <f>'실행이력'!$A$4:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$22</f>
+              <f>'실행이력'!$F$4:$F$23</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$22</f>
+              <f>'실행이력'!$A$4:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$22</f>
+              <f>'실행이력'!$G$4:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -17145,7 +17145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18030,6 +18030,48 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-26 00:31</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>feature/weekly-report</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>8a83a7e</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>197</v>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>132</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>373</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K23" s="36">
+        <f>IFERROR(E23/(E23+F23+G23),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$23</f>
+              <f>'실행이력'!$A$4:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$23</f>
+              <f>'실행이력'!$E$4:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$23</f>
+              <f>'실행이력'!$A$4:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$23</f>
+              <f>'실행이력'!$F$4:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$23</f>
+              <f>'실행이력'!$A$4:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$23</f>
+              <f>'실행이력'!$G$4:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -17145,7 +17145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18072,6 +18072,48 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:30</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>feature/aws-lowcost</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>b80b869</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>197</v>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>132</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>373</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="K24" s="36">
+        <f>IFERROR(E24/(E24+F24+G24),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="실행이력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'케이스관리'!$A$4:$J$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$24</f>
+              <f>'실행이력'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$24</f>
+              <f>'실행이력'!$E$4:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$24</f>
+              <f>'실행이력'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$24</f>
+              <f>'실행이력'!$F$4:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$24</f>
+              <f>'실행이력'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$24</f>
+              <f>'실행이력'!$G$4:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -2146,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6138,22 +6138,22 @@
     <row r="88">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>UT-ATK-01</t>
+          <t>IT-ATK-21</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E88" s="27" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
-          <t>LoginThrottle: 5회 실패 전까지는 막지 않고 5회째부터 차단</t>
+          <t>같은 사용자가 같은 알고리즘을 16개 요청으로 동시에 신청</t>
         </is>
       </c>
       <c r="G88" s="29" t="inlineStr">
         <is>
-          <t>4회 실패 후 차단 아님, 5회 후 차단</t>
+          <t>201 은 정확히 1건, 나머지 409, 서버 오류 없음, 신청 1건만 저장</t>
         </is>
       </c>
       <c r="H88" s="28" t="inlineStr">
@@ -6185,22 +6185,22 @@
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>UT-ATK-02</t>
+          <t>IT-ATK-22</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>LoginThrottle: 시간이 지나면 풀리고, 성공하면 초기화되며, 아이디는 대소문자 무관/서로 독립</t>
+          <t>기관 사용자 둘이 같은 심사중 신청을 동시에 승인/반려(각 6건씩, 5라운드 반복)</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>15분 경과 후 해제, reset 후 해제, ALICE01 도 같은 계정으로 계산, 다른 아이디는 영향 없음</t>
+          <t>라운드마다 200 은 정확히 1건, 나머지 409(INVALID_TRANSITION), 최종 상태는 이긴 요청의 값, 서버 오류 없음</t>
         </is>
       </c>
       <c r="H89" s="28" t="inlineStr">
@@ -6232,22 +6232,22 @@
     <row r="90">
       <c r="A90" s="27" t="inlineStr">
         <is>
-          <t>UT-ATK-03</t>
+          <t>IT-ATK-23</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E90" s="27" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="F90" s="29" t="inlineStr">
         <is>
-          <t>LoginThrottle: 서로 다른 아이디를 대량으로 시도해도 기억하는 개수가 상한을 넘지 않음</t>
+          <t>한 사용자가 서로 다른 알고리즘 7종을 동시에 신청</t>
         </is>
       </c>
       <c r="G90" s="29" t="inlineStr">
         <is>
-          <t>max_keys 이하로 유지</t>
+          <t>7건 모두 201, 서버 오류(DB 잠김 등) 없음, 7건 저장</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
@@ -6279,12 +6279,12 @@
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-ATK-24</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F91" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 원문과 다른 bcrypt 해시</t>
+          <t>같은 계정에 틀린 비밀번호를 24개 요청으로 동시에 시도</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
         <is>
-          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
+          <t>로그인 시도 제한(5회)이 동시 요청에도 적용되어, 실제로 비밀번호를 검사하는 요청은 5건 이하</t>
         </is>
       </c>
       <c r="H91" s="28" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="92">
       <c r="A92" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>UT-ATK-01</t>
         </is>
       </c>
       <c r="B92" s="27" t="inlineStr">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="E92" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
+          <t>LoginThrottle: 5회 실패 전까지는 막지 않고 5회째부터 차단</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
         <is>
-          <t>두 번 호출한 해시가 서로 다름</t>
+          <t>4회 실패 후 차단 아님, 5회 후 차단</t>
         </is>
       </c>
       <c r="H92" s="28" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>UT-ATK-02</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
@@ -6393,17 +6393,17 @@
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 올바른 평문</t>
+          <t>LoginThrottle: 시간이 지나면 풀리고, 성공하면 초기화되며, 아이디는 대소문자 무관/서로 독립</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>15분 경과 후 해제, reset 후 해제, ALICE01 도 같은 계정으로 계산, 다른 아이디는 영향 없음</t>
         </is>
       </c>
       <c r="H93" s="28" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="94">
       <c r="A94" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>UT-ATK-03</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
@@ -6440,17 +6440,17 @@
       </c>
       <c r="E94" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 잘못된 평문</t>
+          <t>LoginThrottle: 서로 다른 아이디를 대량으로 시도해도 기억하는 개수가 상한을 넘지 않음</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>max_keys 이하로 유지</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>UT-ATK-04</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
@@ -6487,17 +6487,17 @@
       </c>
       <c r="E95" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 대소문자 구분</t>
+          <t>LoginThrottle.try_acquire: 검사와 기록이 한 번에 처리되어 한도(5)를 넘는 시도는 모두 거부</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>대소문자만 다른 평문은 False</t>
+          <t>처음 5번은 True, 이후는 False, 아이디가 달라도 대소문자 무관, reset 후 다시 허용</t>
         </is>
       </c>
       <c r="H95" s="28" t="inlineStr">
@@ -6514,7 +6514,7 @@
     <row r="96">
       <c r="A96" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
@@ -6534,17 +6534,17 @@
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
+          <t>hash_password: 원문과 다른 bcrypt 해시</t>
         </is>
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>예외 없이 False</t>
+          <t>원문과 다르며 '$2' 로 시작하는 bcrypt 해시 문자열</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="E97" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
+          <t>hash_password: 동일 입력도 salt 로 매번 다른 해시</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>해시 생성 후 verify 가 True</t>
+          <t>두 번 호출한 해시가 서로 다름</t>
         </is>
       </c>
       <c r="H97" s="28" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="98">
       <c r="A98" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자 가입</t>
+          <t>verify_password: 올바른 평문</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
         <is>
-          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H98" s="28" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="99">
       <c r="A99" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
@@ -6675,17 +6675,17 @@
       </c>
       <c r="E99" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
+          <t>verify_password: 잘못된 평문</t>
         </is>
       </c>
       <c r="G99" s="29" t="inlineStr">
         <is>
-          <t>user_type·org_code 가 그대로 저장</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H99" s="28" t="inlineStr">
@@ -6702,7 +6702,7 @@
     <row r="100">
       <c r="A100" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
@@ -6722,17 +6722,17 @@
       </c>
       <c r="E100" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
-          <t>signup: 기업/기관인데 org_code 누락</t>
+          <t>verify_password: 대소문자 구분</t>
         </is>
       </c>
       <c r="G100" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 사용자 미생성</t>
+          <t>대소문자만 다른 평문은 False</t>
         </is>
       </c>
       <c r="H100" s="28" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="101">
       <c r="A101" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
@@ -6769,17 +6769,17 @@
       </c>
       <c r="E101" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F101" s="29" t="inlineStr">
         <is>
-          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
+          <t>verify_password: 빈 입력/깨진 해시는 예외 없이 False</t>
         </is>
       </c>
       <c r="G101" s="29" t="inlineStr">
         <is>
-          <t>org_code 는 None</t>
+          <t>예외 없이 False</t>
         </is>
       </c>
       <c r="H101" s="28" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="102">
       <c r="A102" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="E102" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F102" s="29" t="inlineStr">
         <is>
-          <t>signup: 중복 username</t>
+          <t>hash_password: 한글·특수문자 포함 비밀번호</t>
         </is>
       </c>
       <c r="G102" s="29" t="inlineStr">
         <is>
-          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
+          <t>해시 생성 후 verify 가 True</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
@@ -6843,7 +6843,7 @@
     <row r="103">
       <c r="A103" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
@@ -6863,17 +6863,17 @@
       </c>
       <c r="E103" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F103" s="29" t="inlineStr">
         <is>
-          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
+          <t>signup: 개인 사용자 가입</t>
         </is>
       </c>
       <c r="G103" s="29" t="inlineStr">
         <is>
-          <t>두 계정 모두 생성</t>
+          <t>User 생성, password_hash 는 원문과 다른 bcrypt 값, org_code 는 None</t>
         </is>
       </c>
       <c r="H103" s="28" t="inlineStr">
@@ -6890,7 +6890,7 @@
     <row r="104">
       <c r="A104" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
@@ -6910,17 +6910,17 @@
       </c>
       <c r="E104" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F104" s="29" t="inlineStr">
         <is>
-          <t>signup: username 길이 경계 3/4/20/21자</t>
+          <t>signup: 기업/기관 사용자는 org_code 와 함께 가입</t>
         </is>
       </c>
       <c r="G104" s="29" t="inlineStr">
         <is>
-          <t>4~20자만 허용, 나머지 ValidationError</t>
+          <t>user_type·org_code 가 그대로 저장</t>
         </is>
       </c>
       <c r="H104" s="28" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="105">
       <c r="A105" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B105" s="27" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
+          <t>signup: 기업/기관인데 org_code 누락</t>
         </is>
       </c>
       <c r="G105" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>ValidationError, 사용자 미생성</t>
         </is>
       </c>
       <c r="H105" s="28" t="inlineStr">
@@ -6984,7 +6984,7 @@
     <row r="106">
       <c r="A106" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="F106" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
+          <t>signup: 개인 사용자가 org_code 를 보내도 저장하지 않음</t>
         </is>
       </c>
       <c r="G106" s="29" t="inlineStr">
         <is>
-          <t>8~64자만 허용</t>
+          <t>org_code 는 None</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="107">
       <c r="A107" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
+          <t>signup: 중복 username</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>숫자만/영문만/공백만 → ValidationError</t>
+          <t>DuplicateUsernameError, users 레코드 1건 유지</t>
         </is>
       </c>
       <c r="H107" s="28" t="inlineStr">
@@ -7078,7 +7078,7 @@
     <row r="108">
       <c r="A108" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B108" s="27" t="inlineStr">
@@ -7098,17 +7098,17 @@
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F108" s="29" t="inlineStr">
         <is>
-          <t>signup: 허용되지 않는 user_type</t>
+          <t>signup: username 은 대소문자를 구분(Alice01 ≠ alice01)</t>
         </is>
       </c>
       <c r="G108" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>두 계정 모두 생성</t>
         </is>
       </c>
       <c r="H108" s="28" t="inlineStr">
@@ -7125,7 +7125,7 @@
     <row r="109">
       <c r="A109" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B109" s="27" t="inlineStr">
@@ -7145,17 +7145,17 @@
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
+          <t>signup: username 길이 경계 3/4/20/21자</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>예외 후 users 0건</t>
+          <t>4~20자만 허용, 나머지 ValidationError</t>
         </is>
       </c>
       <c r="H109" s="28" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="110">
       <c r="A110" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B110" s="27" t="inlineStr">
@@ -7192,17 +7192,17 @@
       </c>
       <c r="E110" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>login: 올바른 자격 증명</t>
+          <t>signup: username 허용 문자(영문/숫자/_) 외 입력</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>해당 User 반환</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
@@ -7219,7 +7219,7 @@
     <row r="111">
       <c r="A111" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B111" s="27" t="inlineStr">
@@ -7239,17 +7239,17 @@
       </c>
       <c r="E111" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>login: 비밀번호 불일치</t>
+          <t>signup: 비밀번호 길이 경계 7/8/64/65자</t>
         </is>
       </c>
       <c r="G111" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError</t>
+          <t>8~64자만 허용</t>
         </is>
       </c>
       <c r="H111" s="28" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="112">
       <c r="A112" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B112" s="27" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
+          <t>signup: 비밀번호 구성 규칙(영문+숫자 각 1자 이상)</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
+          <t>숫자만/영문만/공백만 → ValidationError</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
@@ -7313,7 +7313,7 @@
     <row r="113">
       <c r="A113" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B113" s="27" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>login: 빈 입력/인젝션 문자열</t>
+          <t>signup: 허용되지 않는 user_type</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>AuthenticationError (예외 유형 일관)</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H113" s="28" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="114">
       <c r="A114" s="27" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B114" s="27" t="inlineStr">
@@ -7380,17 +7380,17 @@
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F114" s="29" t="inlineStr">
         <is>
-          <t>get_user: 존재하는 id / 없는 id</t>
+          <t>signup: 실패한 가입은 레코드를 남기지 않음(원자성)</t>
         </is>
       </c>
       <c r="G114" s="29" t="inlineStr">
         <is>
-          <t>존재하면 User, 없으면 NotFoundError</t>
+          <t>예외 후 users 0건</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
@@ -7407,7 +7407,7 @@
     <row r="115">
       <c r="A115" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B115" s="27" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D115" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E115" s="27" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>create_application: 유효한 알고리즘</t>
+          <t>login: 올바른 자격 증명</t>
         </is>
       </c>
       <c r="G115" s="29" t="inlineStr">
         <is>
-          <t>status='submitted', submitted_at 설정, 본인 소유</t>
+          <t>해당 User 반환</t>
         </is>
       </c>
       <c r="H115" s="28" t="inlineStr">
@@ -7454,7 +7454,7 @@
     <row r="116">
       <c r="A116" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B116" s="27" t="inlineStr">
@@ -7464,27 +7464,27 @@
       </c>
       <c r="C116" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D116" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F116" s="29" t="inlineStr">
         <is>
-          <t>create_application: 허용 알고리즘 전체</t>
+          <t>login: 비밀번호 불일치</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
-          <t>ALGORITHMS 의 모든 값 신청 가능</t>
+          <t>AuthenticationError</t>
         </is>
       </c>
       <c r="H116" s="28" t="inlineStr">
@@ -7501,7 +7501,7 @@
     <row r="117">
       <c r="A117" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B117" s="27" t="inlineStr">
@@ -7511,27 +7511,27 @@
       </c>
       <c r="C117" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D117" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E117" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F117" s="29" t="inlineStr">
         <is>
-          <t>create_application: 빈 값/미허용 알고리즘</t>
+          <t>login: 없는 아이디 — 비밀번호 불일치와 동일한 예외/메시지</t>
         </is>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>ValidationError, 레코드 미생성</t>
+          <t>AuthenticationError, 메시지가 UT-AUTH-21 과 동일(계정 존재 여부 비노출)</t>
         </is>
       </c>
       <c r="H117" s="28" t="inlineStr">
@@ -7548,7 +7548,7 @@
     <row r="118">
       <c r="A118" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B118" s="27" t="inlineStr">
@@ -7558,27 +7558,27 @@
       </c>
       <c r="C118" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D118" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E118" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F118" s="29" t="inlineStr">
         <is>
-          <t>create_application: 없는 사용자</t>
+          <t>login: 빈 입력/인젝션 문자열</t>
         </is>
       </c>
       <c r="G118" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>AuthenticationError (예외 유형 일관)</t>
         </is>
       </c>
       <c r="H118" s="28" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="119">
       <c r="A119" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B119" s="27" t="inlineStr">
@@ -7605,27 +7605,27 @@
       </c>
       <c r="C119" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D119" s="28" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E119" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F119" s="29" t="inlineStr">
         <is>
-          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
+          <t>get_user: 존재하는 id / 없는 id</t>
         </is>
       </c>
       <c r="G119" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
+          <t>존재하면 User, 없으면 NotFoundError</t>
         </is>
       </c>
       <c r="H119" s="28" t="inlineStr">
@@ -7642,7 +7642,7 @@
     <row r="120">
       <c r="A120" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B120" s="27" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="E120" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F120" s="29" t="inlineStr">
         <is>
-          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
+          <t>create_application: 유효한 알고리즘</t>
         </is>
       </c>
       <c r="G120" s="29" t="inlineStr">
         <is>
-          <t>허용</t>
+          <t>status='submitted', submitted_at 설정, 본인 소유</t>
         </is>
       </c>
       <c r="H120" s="28" t="inlineStr">
@@ -7689,7 +7689,7 @@
     <row r="121">
       <c r="A121" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B121" s="27" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="F121" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용 전이 3종</t>
+          <t>create_application: 허용 알고리즘 전체</t>
         </is>
       </c>
       <c r="G121" s="29" t="inlineStr">
         <is>
-          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
+          <t>ALGORITHMS 의 모든 값 신청 가능</t>
         </is>
       </c>
       <c r="H121" s="28" t="inlineStr">
@@ -7736,7 +7736,7 @@
     <row r="122">
       <c r="A122" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B122" s="27" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="F122" s="29" t="inlineStr">
         <is>
-          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
+          <t>create_application: 빈 값/미허용 알고리즘</t>
         </is>
       </c>
       <c r="G122" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 상태 불변</t>
+          <t>ValidationError, 레코드 미생성</t>
         </is>
       </c>
       <c r="H122" s="28" t="inlineStr">
@@ -7783,7 +7783,7 @@
     <row r="123">
       <c r="A123" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B123" s="27" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="F123" s="29" t="inlineStr">
         <is>
-          <t>update_status: 존재하지 않는 상태값</t>
+          <t>create_application: 없는 사용자</t>
         </is>
       </c>
       <c r="G123" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H123" s="28" t="inlineStr">
@@ -7830,7 +7830,7 @@
     <row r="124">
       <c r="A124" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B124" s="27" t="inlineStr">
@@ -7850,17 +7850,17 @@
       </c>
       <c r="E124" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F124" s="29" t="inlineStr">
         <is>
-          <t>update_status: 전이 시 updated_at 갱신</t>
+          <t>create_application: 진행 중 동일 알고리즘 중복 신청</t>
         </is>
       </c>
       <c r="G124" s="29" t="inlineStr">
         <is>
-          <t>updated_at 이 이전보다 이후</t>
+          <t>DuplicateApplicationError (submitted/reviewing 모두)</t>
         </is>
       </c>
       <c r="H124" s="28" t="inlineStr">
@@ -7877,7 +7877,7 @@
     <row r="125">
       <c r="A125" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B125" s="27" t="inlineStr">
@@ -7897,17 +7897,17 @@
       </c>
       <c r="E125" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F125" s="29" t="inlineStr">
         <is>
-          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
+          <t>create_application: 종료(approved/rejected) 후 재신청 및 타 알고리즘/타 사용자 신청</t>
         </is>
       </c>
       <c r="G125" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError, 상태 불변</t>
+          <t>허용</t>
         </is>
       </c>
       <c r="H125" s="28" t="inlineStr">
@@ -7924,7 +7924,7 @@
     <row r="126">
       <c r="A126" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B126" s="27" t="inlineStr">
@@ -7944,17 +7944,17 @@
       </c>
       <c r="E126" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F126" s="29" t="inlineStr">
         <is>
-          <t>update_status: 없는 신청/없는 사용자</t>
+          <t>update_status: 허용 전이 3종</t>
         </is>
       </c>
       <c r="G126" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>submitted→reviewing, reviewing→approved, reviewing→rejected</t>
         </is>
       </c>
       <c r="H126" s="28" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="127">
       <c r="A127" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B127" s="27" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="E127" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F127" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 본인 신청만, 최신순</t>
+          <t>update_status: 허용되지 않는 전이 전수(허용 3개 제외 13개)</t>
         </is>
       </c>
       <c r="G127" s="29" t="inlineStr">
         <is>
-          <t>타인 신청 제외, submitted_at 내림차순</t>
+          <t>InvalidTransitionError, 상태 불변</t>
         </is>
       </c>
       <c r="H127" s="28" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="128">
       <c r="A128" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B128" s="27" t="inlineStr">
@@ -8038,17 +8038,17 @@
       </c>
       <c r="E128" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F128" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 상태 필터</t>
+          <t>update_status: 존재하지 않는 상태값</t>
         </is>
       </c>
       <c r="G128" s="29" t="inlineStr">
         <is>
-          <t>해당 상태만 반환, total 도 필터 기준</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H128" s="28" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="129">
       <c r="A129" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B129" s="27" t="inlineStr">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="E129" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F129" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 잘못된 상태 필터</t>
+          <t>update_status: 전이 시 updated_at 갱신</t>
         </is>
       </c>
       <c r="G129" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>updated_at 이 이전보다 이후</t>
         </is>
       </c>
       <c r="H129" s="28" t="inlineStr">
@@ -8112,7 +8112,7 @@
     <row r="130">
       <c r="A130" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B130" s="27" t="inlineStr">
@@ -8132,17 +8132,17 @@
       </c>
       <c r="E130" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F130" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
+          <t>update_status: institution 이 아닌 사용자는 상태 변경 불가</t>
         </is>
       </c>
       <c r="G130" s="29" t="inlineStr">
         <is>
-          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
+          <t>PermissionDeniedError, 상태 불변</t>
         </is>
       </c>
       <c r="H130" s="28" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="131">
       <c r="A131" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B131" s="27" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="E131" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F131" s="29" t="inlineStr">
         <is>
-          <t>list_applications: page/per_page 경계값</t>
+          <t>update_status: 없는 신청/없는 사용자</t>
         </is>
       </c>
       <c r="G131" s="29" t="inlineStr">
         <is>
-          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H131" s="28" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="132">
       <c r="A132" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B132" s="27" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="F132" s="29" t="inlineStr">
         <is>
-          <t>list_applications: 신청이 없으면 빈 목록</t>
+          <t>list_applications: 본인 신청만, 최신순</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
         <is>
-          <t>items=[], total=0</t>
+          <t>타인 신청 제외, submitted_at 내림차순</t>
         </is>
       </c>
       <c r="H132" s="28" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="133">
       <c r="A133" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B133" s="27" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="F133" s="29" t="inlineStr">
         <is>
-          <t>get_application: 본인 / 타인 / 없는 id</t>
+          <t>list_applications: 상태 필터</t>
         </is>
       </c>
       <c r="G133" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>해당 상태만 반환, total 도 필터 기준</t>
         </is>
       </c>
       <c r="H133" s="28" t="inlineStr">
@@ -8300,7 +8300,7 @@
     <row r="134">
       <c r="A134" s="27" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B134" s="27" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="E134" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F134" s="29" t="inlineStr">
         <is>
-          <t>get_application: institution 은 모든 신청 조회 가능</t>
+          <t>list_applications: 잘못된 상태 필터</t>
         </is>
       </c>
       <c r="G134" s="29" t="inlineStr">
         <is>
-          <t>타인 신청도 반환</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H134" s="28" t="inlineStr">
@@ -8347,7 +8347,7 @@
     <row r="135">
       <c r="A135" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B135" s="27" t="inlineStr">
@@ -8357,32 +8357,32 @@
       </c>
       <c r="C135" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D135" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E135" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F135" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: SHA-256 hex</t>
+          <t>list_applications: 페이지네이션 (25건, per_page=10)</t>
         </is>
       </c>
       <c r="G135" s="29" t="inlineStr">
         <is>
-          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
+          <t>1p 10건, 2p 10건, 3p 5건, 4p 0건, total=25</t>
         </is>
       </c>
       <c r="H135" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I135" s="30" t="n"/>
@@ -8394,7 +8394,7 @@
     <row r="136">
       <c r="A136" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B136" s="27" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="C136" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D136" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E136" s="27" t="inlineStr">
@@ -8419,17 +8419,17 @@
       </c>
       <c r="F136" s="29" t="inlineStr">
         <is>
-          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
+          <t>list_applications: page/per_page 경계값</t>
         </is>
       </c>
       <c r="G136" s="29" t="inlineStr">
         <is>
-          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
+          <t>page 0·per_page 0/51 → ValidationError, per_page 1/50 허용</t>
         </is>
       </c>
       <c r="H136" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I136" s="30" t="n"/>
@@ -8441,7 +8441,7 @@
     <row r="137">
       <c r="A137" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B137" s="27" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="C137" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D137" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E137" s="27" t="inlineStr">
@@ -8466,17 +8466,17 @@
       </c>
       <c r="F137" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 동일 해시</t>
+          <t>list_applications: 신청이 없으면 빈 목록</t>
         </is>
       </c>
       <c r="G137" s="29" t="inlineStr">
         <is>
-          <t>'normal'</t>
+          <t>items=[], total=0</t>
         </is>
       </c>
       <c r="H137" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I137" s="30" t="n"/>
@@ -8488,7 +8488,7 @@
     <row r="138">
       <c r="A138" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B138" s="27" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="C138" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D138" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E138" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F138" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 상이한 해시</t>
+          <t>get_application: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G138" s="29" t="inlineStr">
         <is>
-          <t>'suspected'</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H138" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I138" s="30" t="n"/>
@@ -8535,7 +8535,7 @@
     <row r="139">
       <c r="A139" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B139" s="27" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="C139" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D139" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E139" s="27" t="inlineStr">
@@ -8560,17 +8560,17 @@
       </c>
       <c r="F139" s="29" t="inlineStr">
         <is>
-          <t>compare_hash: 대소문자만 다른 hex</t>
+          <t>get_application: institution 은 모든 신청 조회 가능</t>
         </is>
       </c>
       <c r="G139" s="29" t="inlineStr">
         <is>
-          <t>동일 값으로 보고 'normal'</t>
+          <t>타인 신청도 반환</t>
         </is>
       </c>
       <c r="H139" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I139" s="30" t="n"/>
@@ -8582,7 +8582,7 @@
     <row r="140">
       <c r="A140" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B140" s="27" t="inlineStr">
@@ -8592,12 +8592,12 @@
       </c>
       <c r="C140" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D140" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E140" s="27" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="F140" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인된 신청에 발급</t>
+          <t>compute_hash: SHA-256 hex</t>
         </is>
       </c>
       <c r="G140" s="29" t="inlineStr">
         <is>
-          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
+          <t>표준 SHA-256 과 동일한 64자 소문자 hex</t>
         </is>
       </c>
       <c r="H140" s="28" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="141">
       <c r="A141" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B141" s="27" t="inlineStr">
@@ -8639,27 +8639,27 @@
       </c>
       <c r="C141" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D141" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E141" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F141" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 승인 이전/반려 상태</t>
+          <t>compute_hash: 1바이트 차이 / 빈 입력</t>
         </is>
       </c>
       <c r="G141" s="29" t="inlineStr">
         <is>
-          <t>InvalidTransitionError, 검증서 미생성</t>
+          <t>1바이트만 달라도 해시 상이, 빈 바이트도 처리</t>
         </is>
       </c>
       <c r="H141" s="28" t="inlineStr">
@@ -8676,7 +8676,7 @@
     <row r="142">
       <c r="A142" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B142" s="27" t="inlineStr">
@@ -8686,27 +8686,27 @@
       </c>
       <c r="C142" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D142" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E142" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F142" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 신청당 1건(중복 발급)</t>
+          <t>compare_hash: 동일 해시</t>
         </is>
       </c>
       <c r="G142" s="29" t="inlineStr">
         <is>
-          <t>DuplicateApplicationError</t>
+          <t>'normal'</t>
         </is>
       </c>
       <c r="H142" s="28" t="inlineStr">
@@ -8723,7 +8723,7 @@
     <row r="143">
       <c r="A143" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B143" s="27" t="inlineStr">
@@ -8733,27 +8733,27 @@
       </c>
       <c r="C143" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D143" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E143" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F143" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: institution 이 아니면 발급 불가</t>
+          <t>compare_hash: 상이한 해시</t>
         </is>
       </c>
       <c r="G143" s="29" t="inlineStr">
         <is>
-          <t>PermissionDeniedError</t>
+          <t>'suspected'</t>
         </is>
       </c>
       <c r="H143" s="28" t="inlineStr">
@@ -8770,7 +8770,7 @@
     <row r="144">
       <c r="A144" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B144" s="27" t="inlineStr">
@@ -8780,27 +8780,27 @@
       </c>
       <c r="C144" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D144" s="28" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E144" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F144" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
+          <t>compare_hash: 대소문자만 다른 hex</t>
         </is>
       </c>
       <c r="G144" s="29" t="inlineStr">
         <is>
-          <t>ValidationError / ValidationError / NotFoundError</t>
+          <t>동일 값으로 보고 'normal'</t>
         </is>
       </c>
       <c r="H144" s="28" t="inlineStr">
@@ -8817,7 +8817,7 @@
     <row r="145">
       <c r="A145" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B145" s="27" t="inlineStr">
@@ -8837,17 +8837,17 @@
       </c>
       <c r="E145" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F145" s="29" t="inlineStr">
         <is>
-          <t>issue_certificate: KCMVP 유형도 발급</t>
+          <t>issue_certificate: 승인된 신청에 발급</t>
         </is>
       </c>
       <c r="G145" s="29" t="inlineStr">
         <is>
-          <t>cert_type='KCMVP'</t>
+          <t>integrity_hash=SHA-256(내용), tamper_status='normal', 파일 저장</t>
         </is>
       </c>
       <c r="H145" s="28" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="146">
       <c r="A146" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B146" s="27" t="inlineStr">
@@ -8884,17 +8884,17 @@
       </c>
       <c r="E146" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F146" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
+          <t>issue_certificate: 승인 이전/반려 상태</t>
         </is>
       </c>
       <c r="G146" s="29" t="inlineStr">
         <is>
-          <t>타인 검증서 제외, issued_at 내림차순</t>
+          <t>InvalidTransitionError, 검증서 미생성</t>
         </is>
       </c>
       <c r="H146" s="28" t="inlineStr">
@@ -8911,7 +8911,7 @@
     <row r="147">
       <c r="A147" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B147" s="27" t="inlineStr">
@@ -8931,17 +8931,17 @@
       </c>
       <c r="E147" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F147" s="29" t="inlineStr">
         <is>
-          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
+          <t>issue_certificate: 신청당 1건(중복 발급)</t>
         </is>
       </c>
       <c r="G147" s="29" t="inlineStr">
         <is>
-          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
+          <t>DuplicateApplicationError</t>
         </is>
       </c>
       <c r="H147" s="28" t="inlineStr">
@@ -8958,7 +8958,7 @@
     <row r="148">
       <c r="A148" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B148" s="27" t="inlineStr">
@@ -8978,17 +8978,17 @@
       </c>
       <c r="E148" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F148" s="29" t="inlineStr">
         <is>
-          <t>get_certificate: 본인 / 타인 / 없는 id</t>
+          <t>issue_certificate: institution 이 아니면 발급 불가</t>
         </is>
       </c>
       <c r="G148" s="29" t="inlineStr">
         <is>
-          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
+          <t>PermissionDeniedError</t>
         </is>
       </c>
       <c r="H148" s="28" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="149">
       <c r="A149" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B149" s="27" t="inlineStr">
@@ -9015,27 +9015,27 @@
       </c>
       <c r="C149" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D149" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E149" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F149" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 무결 → normal</t>
+          <t>issue_certificate: 잘못된 cert_type / 빈 내용 / 없는 신청</t>
         </is>
       </c>
       <c r="G149" s="29" t="inlineStr">
         <is>
-          <t>tamper_status='normal'</t>
+          <t>ValidationError / ValidationError / NotFoundError</t>
         </is>
       </c>
       <c r="H149" s="28" t="inlineStr">
@@ -9052,7 +9052,7 @@
     <row r="150">
       <c r="A150" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B150" s="27" t="inlineStr">
@@ -9062,27 +9062,27 @@
       </c>
       <c r="C150" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D150" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E150" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F150" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
+          <t>issue_certificate: KCMVP 유형도 발급</t>
         </is>
       </c>
       <c r="G150" s="29" t="inlineStr">
         <is>
-          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
+          <t>cert_type='KCMVP'</t>
         </is>
       </c>
       <c r="H150" s="28" t="inlineStr">
@@ -9099,7 +9099,7 @@
     <row r="151">
       <c r="A151" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B151" s="27" t="inlineStr">
@@ -9109,27 +9109,27 @@
       </c>
       <c r="C151" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D151" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E151" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F151" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
+          <t>list_certificates: 본인 신청 소속만, 최신 발급순</t>
         </is>
       </c>
       <c r="G151" s="29" t="inlineStr">
         <is>
-          <t>'suspected' (예외 아님)</t>
+          <t>타인 검증서 제외, issued_at 내림차순</t>
         </is>
       </c>
       <c r="H151" s="28" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="152">
       <c r="A152" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B152" s="27" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="C152" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D152" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E152" s="27" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="F152" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 원복 후 재검증 시 normal</t>
+          <t>list_certificates: 페이지네이션/경계/빈 목록</t>
         </is>
       </c>
       <c r="G152" s="29" t="inlineStr">
         <is>
-          <t>변조 → suspected, 원복 → normal</t>
+          <t>per_page 1~50, page&gt;=1, 빈 목록은 total=0</t>
         </is>
       </c>
       <c r="H152" s="28" t="inlineStr">
@@ -9193,7 +9193,7 @@
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B153" s="27" t="inlineStr">
@@ -9203,27 +9203,27 @@
       </c>
       <c r="C153" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
         <is>
-          <t>SC-07</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E153" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F153" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 존재하지 않는 cert_id</t>
+          <t>get_certificate: 본인 / 타인 / 없는 id</t>
         </is>
       </c>
       <c r="G153" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>본인 반환, 타인 PermissionDeniedError, 없는 id NotFoundError</t>
         </is>
       </c>
       <c r="H153" s="28" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="154">
       <c r="A154" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B154" s="27" t="inlineStr">
@@ -9260,17 +9260,17 @@
       </c>
       <c r="E154" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F154" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
+          <t>verify_integrity: 파일 무결 → normal</t>
         </is>
       </c>
       <c r="G154" s="29" t="inlineStr">
         <is>
-          <t>검증 후에도 integrity_hash 불변</t>
+          <t>tamper_status='normal'</t>
         </is>
       </c>
       <c r="H154" s="28" t="inlineStr">
@@ -9287,7 +9287,7 @@
     <row r="155">
       <c r="A155" s="27" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B155" s="27" t="inlineStr">
@@ -9307,17 +9307,17 @@
       </c>
       <c r="E155" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F155" s="29" t="inlineStr">
         <is>
-          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
+          <t>verify_integrity: 파일 변조 → suspected(DB 에도 반영)</t>
         </is>
       </c>
       <c r="G155" s="29" t="inlineStr">
         <is>
-          <t>파일이 없으면 suspected 유지</t>
+          <t>반환값과 DB 의 tamper_status 모두 'suspected'</t>
         </is>
       </c>
       <c r="H155" s="28" t="inlineStr">
@@ -9334,7 +9334,7 @@
     <row r="156">
       <c r="A156" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-01</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B156" s="27" t="inlineStr">
@@ -9344,32 +9344,32 @@
       </c>
       <c r="C156" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D156" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E156" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F156" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 본인 신청만 집계</t>
+          <t>verify_integrity: 파일 삭제/누락 → suspected</t>
         </is>
       </c>
       <c r="G156" s="29" t="inlineStr">
         <is>
-          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
+          <t>'suspected' (예외 아님)</t>
         </is>
       </c>
       <c r="H156" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I156" s="30" t="n"/>
@@ -9381,7 +9381,7 @@
     <row r="157">
       <c r="A157" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-02</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B157" s="27" t="inlineStr">
@@ -9391,32 +9391,32 @@
       </c>
       <c r="C157" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D157" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E157" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F157" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
+          <t>verify_integrity: 원복 후 재검증 시 normal</t>
         </is>
       </c>
       <c r="G157" s="29" t="inlineStr">
         <is>
-          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
+          <t>변조 → suspected, 원복 → normal</t>
         </is>
       </c>
       <c r="H157" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I157" s="30" t="n"/>
@@ -9428,7 +9428,7 @@
     <row r="158">
       <c r="A158" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-03</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B158" s="27" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="C158" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D158" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E158" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F158" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
+          <t>verify_integrity: 존재하지 않는 cert_id</t>
         </is>
       </c>
       <c r="G158" s="29" t="inlineStr">
         <is>
-          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H158" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I158" s="30" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="159">
       <c r="A159" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-04</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B159" s="27" t="inlineStr">
@@ -9485,32 +9485,32 @@
       </c>
       <c r="C159" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D159" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E159" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F159" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
+          <t>verify_integrity: 저장된 integrity_hash 자체는 변경하지 않음</t>
         </is>
       </c>
       <c r="G159" s="29" t="inlineStr">
         <is>
-          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
+          <t>검증 후에도 integrity_hash 불변</t>
         </is>
       </c>
       <c r="H159" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I159" s="30" t="n"/>
@@ -9522,7 +9522,7 @@
     <row r="160">
       <c r="A160" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-05</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B160" s="27" t="inlineStr">
@@ -9532,32 +9532,32 @@
       </c>
       <c r="C160" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D160" s="28" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="E160" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F160" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 상태 라벨 매핑</t>
+          <t>verify_integrity: 시드처럼 이미 suspected 인 건(파일 없음)</t>
         </is>
       </c>
       <c r="G160" s="29" t="inlineStr">
         <is>
-          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
+          <t>파일이 없으면 suspected 유지</t>
         </is>
       </c>
       <c r="H160" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I160" s="30" t="n"/>
@@ -9569,7 +9569,7 @@
     <row r="161">
       <c r="A161" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-06</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B161" s="27" t="inlineStr">
@@ -9589,17 +9589,17 @@
       </c>
       <c r="E161" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F161" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 최근 7일 신규 신청 경계</t>
+          <t>get_summary: 본인 신청만 집계</t>
         </is>
       </c>
       <c r="G161" s="29" t="inlineStr">
         <is>
-          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
+          <t>타인 신청은 total·by_status 에 포함되지 않음</t>
         </is>
       </c>
       <c r="H161" s="28" t="inlineStr">
@@ -9616,7 +9616,7 @@
     <row r="162">
       <c r="A162" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-07</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B162" s="27" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C162" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D162" s="28" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F162" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
+          <t>get_summary: 진행 중 = 접수 대기 + 심사 중, by_status 는 4개 키 항상 존재</t>
         </is>
       </c>
       <c r="G162" s="29" t="inlineStr">
         <is>
-          <t>total·suspected 가 본인 건만 반영</t>
+          <t>in_progress 합산, 0건 상태도 0 으로 표기</t>
         </is>
       </c>
       <c r="H162" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I162" s="30" t="n"/>
@@ -9663,7 +9663,7 @@
     <row r="163">
       <c r="A163" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-08</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B163" s="27" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C163" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D163" s="28" t="inlineStr">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="E163" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F163" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 가명·익명 처리 상태</t>
+          <t>get_summary: 데이터가 전혀 없는 신규 사용자</t>
         </is>
       </c>
       <c r="G163" s="29" t="inlineStr">
         <is>
-          <t>처리 전 processed=False, 처리 후 level 반영</t>
+          <t>모든 수치 0, 목록·알림 빈 배열, 가명처리 미처리</t>
         </is>
       </c>
       <c r="H163" s="28" t="inlineStr">
@@ -9710,7 +9710,7 @@
     <row r="164">
       <c r="A164" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-09</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B164" s="27" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="C164" s="27" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D164" s="28" t="inlineStr">
@@ -9735,17 +9735,17 @@
       </c>
       <c r="F164" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 위변조 의심 알림이 최우선</t>
+          <t>get_summary: 최근 신청은 최신순 최대 3건</t>
         </is>
       </c>
       <c r="G164" s="29" t="inlineStr">
         <is>
-          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
+          <t>5건 중 최신 3건, 필드 id/algorithm_type/status/status_label/submitted_at(YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="H164" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I164" s="30" t="n"/>
@@ -9757,7 +9757,7 @@
     <row r="165">
       <c r="A165" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-10</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B165" s="27" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="F165" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 신청 진행/결과 알림 문구</t>
+          <t>get_summary: 상태 라벨 매핑</t>
         </is>
       </c>
       <c r="G165" s="29" t="inlineStr">
         <is>
-          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
+          <t>submitted 접수 대기 / reviewing 시험 진행중 / approved 시험 완료 / rejected 반려</t>
         </is>
       </c>
       <c r="H165" s="28" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="166">
       <c r="A166" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-11</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B166" s="27" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="F166" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 알림은 최대 5건</t>
+          <t>get_summary: 최근 7일 신규 신청 경계</t>
         </is>
       </c>
       <c r="G166" s="29" t="inlineStr">
         <is>
-          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
+          <t>정확히 7일 전은 포함, 7일 1분 초과는 제외</t>
         </is>
       </c>
       <c r="H166" s="28" t="inlineStr">
@@ -9851,7 +9851,7 @@
     <row r="167">
       <c r="A167" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-12</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B167" s="27" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F167" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
+          <t>get_summary: 검증서 집계(본인 신청 소속만, 위변조 의심 별도)</t>
         </is>
       </c>
       <c r="G167" s="29" t="inlineStr">
         <is>
-          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
+          <t>total·suspected 가 본인 건만 반영</t>
         </is>
       </c>
       <c r="H167" s="28" t="inlineStr">
@@ -9898,7 +9898,7 @@
     <row r="168">
       <c r="A168" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-13</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B168" s="27" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="C168" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D168" s="28" t="inlineStr">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="F168" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
+          <t>get_summary: 가명·익명 처리 상태</t>
         </is>
       </c>
       <c r="G168" s="29" t="inlineStr">
         <is>
-          <t>scope='own'</t>
+          <t>처리 전 processed=False, 처리 후 level 반영</t>
         </is>
       </c>
       <c r="H168" s="28" t="inlineStr">
@@ -9945,7 +9945,7 @@
     <row r="169">
       <c r="A169" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-14</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B169" s="27" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="C169" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="D169" s="28" t="inlineStr">
@@ -9965,22 +9965,22 @@
       </c>
       <c r="E169" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F169" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 없는 사용자</t>
+          <t>get_summary: 위변조 의심 알림이 최우선</t>
         </is>
       </c>
       <c r="G169" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError</t>
+          <t>첫 알림이 warning, 메시지에 CV-0000 형식 번호 포함</t>
         </is>
       </c>
       <c r="H169" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I169" s="30" t="n"/>
@@ -9992,7 +9992,7 @@
     <row r="170">
       <c r="A170" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-15</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B170" s="27" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="C170" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D170" s="28" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="E170" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F170" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
+          <t>get_summary: 신청 진행/결과 알림 문구</t>
         </is>
       </c>
       <c r="G170" s="29" t="inlineStr">
         <is>
-          <t>결과 전체에 password/hash 키 없음</t>
+          <t>reviewing 심사 중 / approved 승인 / rejected 반려, submitted 는 알림 없음</t>
         </is>
       </c>
       <c r="H170" s="28" t="inlineStr">
@@ -10039,7 +10039,7 @@
     <row r="171">
       <c r="A171" s="27" t="inlineStr">
         <is>
-          <t>UT-DASH-16</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B171" s="27" t="inlineStr">
@@ -10059,17 +10059,17 @@
       </c>
       <c r="E171" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F171" s="29" t="inlineStr">
         <is>
-          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
+          <t>get_summary: 알림은 최대 5건</t>
         </is>
       </c>
       <c r="G171" s="29" t="inlineStr">
         <is>
-          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
+          <t>8건 발생해도 5건만, 위변조 경고가 잘리지 않음</t>
         </is>
       </c>
       <c r="H171" s="28" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="172">
       <c r="A172" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B172" s="27" t="inlineStr">
@@ -10096,12 +10096,12 @@
       </c>
       <c r="C172" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-04</t>
         </is>
       </c>
       <c r="D172" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E172" s="27" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="F172" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
+          <t>get_summary: 기관(institution) 사용자는 전체 집계</t>
         </is>
       </c>
       <c r="G172" s="29" t="inlineStr">
         <is>
-          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
+          <t>scope='all', 타인 신청·검증서 포함, 가명처리는 본인 기준</t>
         </is>
       </c>
       <c r="H172" s="28" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="I172" s="30" t="n"/>
@@ -10133,7 +10133,7 @@
     <row r="173">
       <c r="A173" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B173" s="27" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="C173" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D173" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E173" s="27" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="F173" s="29" t="inlineStr">
         <is>
-          <t>issue_pseudonym_id: 호출마다 다른 값</t>
+          <t>get_summary: 기업 사용자는 개인과 동일하게 본인 범위</t>
         </is>
       </c>
       <c r="G173" s="29" t="inlineStr">
         <is>
-          <t>1000회 호출 모두 유일</t>
+          <t>scope='own'</t>
         </is>
       </c>
       <c r="H173" s="28" t="inlineStr">
@@ -10180,7 +10180,7 @@
     <row r="174">
       <c r="A174" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B174" s="27" t="inlineStr">
@@ -10190,27 +10190,27 @@
       </c>
       <c r="C174" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D174" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E174" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F174" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 길이별 마스킹 규칙</t>
+          <t>get_summary: 없는 사용자</t>
         </is>
       </c>
       <c r="G174" s="29" t="inlineStr">
         <is>
-          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
+          <t>NotFoundError</t>
         </is>
       </c>
       <c r="H174" s="28" t="inlineStr">
@@ -10227,7 +10227,7 @@
     <row r="175">
       <c r="A175" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B175" s="27" t="inlineStr">
@@ -10237,27 +10237,27 @@
       </c>
       <c r="C175" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="D175" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E175" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F175" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 빈 값/공백만</t>
+          <t>get_summary: 사용자 정보에 username/user_type 만, 민감 필드 없음</t>
         </is>
       </c>
       <c r="G175" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>결과 전체에 password/hash 키 없음</t>
         </is>
       </c>
       <c r="H175" s="28" t="inlineStr">
@@ -10274,7 +10274,7 @@
     <row r="176">
       <c r="A176" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B176" s="27" t="inlineStr">
@@ -10284,27 +10284,27 @@
       </c>
       <c r="C176" s="27" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="D176" s="28" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E176" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F176" s="29" t="inlineStr">
         <is>
-          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
+          <t>get_summary: 타인 신청이 최근 목록·알림에 노출되지 않음</t>
         </is>
       </c>
       <c r="G176" s="29" t="inlineStr">
         <is>
-          <t>' 홍길동 ' → '홍*동'</t>
+          <t>타인 신청의 알고리즘/상태가 결과에 없음</t>
         </is>
       </c>
       <c r="H176" s="28" t="inlineStr">
@@ -10321,7 +10321,7 @@
     <row r="177">
       <c r="A177" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B177" s="27" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="F177" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 하이픈 유/무 입력</t>
+          <t>issue_pseudonym_id: 형식 'PSN-'+16hex</t>
         </is>
       </c>
       <c r="G177" s="29" t="inlineStr">
         <is>
-          <t>모두 '010-****-5678'</t>
+          <t>정규식 ^PSN-[0-9a-f]{16}$ 일치</t>
         </is>
       </c>
       <c r="H177" s="28" t="inlineStr">
@@ -10368,7 +10368,7 @@
     <row r="178">
       <c r="A178" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B178" s="27" t="inlineStr">
@@ -10388,17 +10388,17 @@
       </c>
       <c r="E178" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F178" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
+          <t>issue_pseudonym_id: 호출마다 다른 값</t>
         </is>
       </c>
       <c r="G178" s="29" t="inlineStr">
         <is>
-          <t>'010-***-4567'</t>
+          <t>1000회 호출 모두 유일</t>
         </is>
       </c>
       <c r="H178" s="28" t="inlineStr">
@@ -10415,7 +10415,7 @@
     <row r="179">
       <c r="A179" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-PRIV-03</t>
         </is>
       </c>
       <c r="B179" s="27" t="inlineStr">
@@ -10435,17 +10435,17 @@
       </c>
       <c r="E179" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F179" s="29" t="inlineStr">
         <is>
-          <t>mask_phone: 형식 오류</t>
+          <t>mask_name: 길이별 마스킹 규칙</t>
         </is>
       </c>
       <c r="G179" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>홍길동→홍*동, 남궁민수→남**수, 홍길→홍*, 홍→*, John→J**n</t>
         </is>
       </c>
       <c r="H179" s="28" t="inlineStr">
@@ -10462,7 +10462,7 @@
     <row r="180">
       <c r="A180" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-PRIV-04</t>
         </is>
       </c>
       <c r="B180" s="27" t="inlineStr">
@@ -10482,17 +10482,17 @@
       </c>
       <c r="E180" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F180" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 대표 연령대</t>
+          <t>mask_name: 빈 값/공백만</t>
         </is>
       </c>
       <c r="G180" s="29" t="inlineStr">
         <is>
-          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H180" s="28" t="inlineStr">
@@ -10509,7 +10509,7 @@
     <row r="181">
       <c r="A181" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-PRIV-05</t>
         </is>
       </c>
       <c r="B181" s="27" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="F181" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
+          <t>mask_name: 앞뒤 공백은 제거 후 마스킹</t>
         </is>
       </c>
       <c r="G181" s="29" t="inlineStr">
         <is>
-          <t>생일 당일부터 다음 연령대</t>
+          <t>' 홍길동 ' → '홍*동'</t>
         </is>
       </c>
       <c r="H181" s="28" t="inlineStr">
@@ -10556,7 +10556,7 @@
     <row r="182">
       <c r="A182" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-PRIV-06</t>
         </is>
       </c>
       <c r="B182" s="27" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="E182" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F182" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
+          <t>mask_phone: 하이픈 유/무 입력</t>
         </is>
       </c>
       <c r="G182" s="29" t="inlineStr">
         <is>
-          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
+          <t>모두 '010-****-5678'</t>
         </is>
       </c>
       <c r="H182" s="28" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="183">
       <c r="A183" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-PRIV-07</t>
         </is>
       </c>
       <c r="B183" s="27" t="inlineStr">
@@ -10623,17 +10623,17 @@
       </c>
       <c r="E183" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F183" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 미래 날짜</t>
+          <t>mask_phone: 3자리 국번 형식(010-123-4567)</t>
         </is>
       </c>
       <c r="G183" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>'010-***-4567'</t>
         </is>
       </c>
       <c r="H183" s="28" t="inlineStr">
@@ -10650,7 +10650,7 @@
     <row r="184">
       <c r="A184" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-PRIV-08</t>
         </is>
       </c>
       <c r="B184" s="27" t="inlineStr">
@@ -10670,17 +10670,17 @@
       </c>
       <c r="E184" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F184" s="29" t="inlineStr">
         <is>
-          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
+          <t>mask_phone: 형식 오류</t>
         </is>
       </c>
       <c r="G184" s="29" t="inlineStr">
         <is>
-          <t>연·월·일 숫자열이 결과에 없음</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H184" s="28" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="185">
       <c r="A185" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-PRIV-09</t>
         </is>
       </c>
       <c r="B185" s="27" t="inlineStr">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="F185" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 결과 객체</t>
+          <t>anonymize_birthdate: 대표 연령대</t>
         </is>
       </c>
       <c r="G185" s="29" t="inlineStr">
         <is>
-          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
+          <t>1990-04-12 → '30대' (기준일 2026-10-02)</t>
         </is>
       </c>
       <c r="H185" s="28" t="inlineStr">
@@ -10744,7 +10744,7 @@
     <row r="186">
       <c r="A186" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-PRIV-10</t>
         </is>
       </c>
       <c r="B186" s="27" t="inlineStr">
@@ -10764,17 +10764,17 @@
       </c>
       <c r="E186" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F186" s="29" t="inlineStr">
         <is>
-          <t>process(anonymous): 식별자 없음</t>
+          <t>anonymize_birthdate: 생일 전/후 경계(만 나이)</t>
         </is>
       </c>
       <c r="G186" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
+          <t>생일 당일부터 다음 연령대</t>
         </is>
       </c>
       <c r="H186" s="28" t="inlineStr">
@@ -10791,7 +10791,7 @@
     <row r="187">
       <c r="A187" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-PRIV-11</t>
         </is>
       </c>
       <c r="B187" s="27" t="inlineStr">
@@ -10811,17 +10811,17 @@
       </c>
       <c r="E187" s="27" t="inlineStr">
         <is>
-          <t>비정상</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="F187" s="29" t="inlineStr">
         <is>
-          <t>process: 허용되지 않는 mode</t>
+          <t>anonymize_birthdate: 윤일(2/29) 생일</t>
         </is>
       </c>
       <c r="G187" s="29" t="inlineStr">
         <is>
-          <t>ValidationError</t>
+          <t>평년 2/28 에는 아직 생일 전, 3/1 부터 생일 후</t>
         </is>
       </c>
       <c r="H187" s="28" t="inlineStr">
@@ -10838,7 +10838,7 @@
     <row r="188">
       <c r="A188" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-PRIV-12</t>
         </is>
       </c>
       <c r="B188" s="27" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F188" s="29" t="inlineStr">
         <is>
-          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
+          <t>anonymize_birthdate: 미래 날짜</t>
         </is>
       </c>
       <c r="G188" s="29" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="189">
       <c r="A189" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-PRIV-13</t>
         </is>
       </c>
       <c r="B189" s="27" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="F189" s="29" t="inlineStr">
         <is>
-          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
+          <t>anonymize_birthdate: 결과에 원본 생년월일 미포함</t>
         </is>
       </c>
       <c r="G189" s="29" t="inlineStr">
         <is>
-          <t>표시값/식별자에 '홍길동' 미포함</t>
+          <t>연·월·일 숫자열이 결과에 없음</t>
         </is>
       </c>
       <c r="H189" s="28" t="inlineStr">
@@ -10932,7 +10932,7 @@
     <row r="190">
       <c r="A190" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-PRIV-14</t>
         </is>
       </c>
       <c r="B190" s="27" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="F190" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: personal_info 저장</t>
+          <t>process(pseudonym): 결과 객체</t>
         </is>
       </c>
       <c r="G190" s="29" t="inlineStr">
         <is>
-          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
+          <t>level='pseudonym', pseudonym_id 형식 일치, 표시값 '홍*동 (30대)'</t>
         </is>
       </c>
       <c r="H190" s="28" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="191">
       <c r="A191" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-PRIV-15</t>
         </is>
       </c>
       <c r="B191" s="27" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F191" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
+          <t>process(anonymous): 식별자 없음</t>
         </is>
       </c>
       <c r="G191" s="29" t="inlineStr">
         <is>
-          <t>행 1건, pseudonym_id 동일</t>
+          <t>level='anonymous', pseudonym_id=None, 표시값 '익명'</t>
         </is>
       </c>
       <c r="H191" s="28" t="inlineStr">
@@ -11026,7 +11026,7 @@
     <row r="192">
       <c r="A192" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-PRIV-16</t>
         </is>
       </c>
       <c r="B192" s="27" t="inlineStr">
@@ -11046,17 +11046,17 @@
       </c>
       <c r="E192" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F192" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
+          <t>process: 허용되지 않는 mode</t>
         </is>
       </c>
       <c r="G192" s="29" t="inlineStr">
         <is>
-          <t>level='anonymous', pseudonym_id=None</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H192" s="28" t="inlineStr">
@@ -11073,7 +11073,7 @@
     <row r="193">
       <c r="A193" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-PRIV-17</t>
         </is>
       </c>
       <c r="B193" s="27" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="F193" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 없는 사용자</t>
+          <t>process(pseudonym): 잘못된 이름/미래 생년월일</t>
         </is>
       </c>
       <c r="G193" s="29" t="inlineStr">
         <is>
-          <t>NotFoundError, 행 미생성</t>
+          <t>ValidationError</t>
         </is>
       </c>
       <c r="H193" s="28" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="194">
       <c r="A194" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-PRIV-18</t>
         </is>
       </c>
       <c r="B194" s="27" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="F194" s="29" t="inlineStr">
         <is>
-          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
+          <t>process: 어떤 결과 필드에도 원본 이름이 그대로 없음</t>
         </is>
       </c>
       <c r="G194" s="29" t="inlineStr">
         <is>
-          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
+          <t>표시값/식별자에 '홍길동' 미포함</t>
         </is>
       </c>
       <c r="H194" s="28" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="195">
       <c r="A195" s="27" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-PRIV-19</t>
         </is>
       </c>
       <c r="B195" s="27" t="inlineStr">
@@ -11192,12 +11192,12 @@
       </c>
       <c r="F195" s="29" t="inlineStr">
         <is>
-          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
+          <t>process_and_store: personal_info 저장</t>
         </is>
       </c>
       <c r="G195" s="29" t="inlineStr">
         <is>
-          <t>저장된 행 반환, 없으면 NotFoundError</t>
+          <t>level·pseudonym_id·masked_display_value 가 처리 결과와 일치, user_id 당 1건</t>
         </is>
       </c>
       <c r="H195" s="28" t="inlineStr">
@@ -11214,7 +11214,7 @@
     <row r="196">
       <c r="A196" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-PRIV-20</t>
         </is>
       </c>
       <c r="B196" s="27" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="C196" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D196" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E196" s="27" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="F196" s="29" t="inlineStr">
         <is>
-          <t>seed: 사용자 3종 생성</t>
+          <t>process_and_store: 재처리는 갱신(중복 행 없음), 기존 pseudonym_id 유지</t>
         </is>
       </c>
       <c r="G196" s="29" t="inlineStr">
         <is>
-          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
+          <t>행 1건, pseudonym_id 동일</t>
         </is>
       </c>
       <c r="H196" s="28" t="inlineStr">
@@ -11261,7 +11261,7 @@
     <row r="197">
       <c r="A197" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-PRIV-21</t>
         </is>
       </c>
       <c r="B197" s="27" t="inlineStr">
@@ -11271,27 +11271,27 @@
       </c>
       <c r="C197" s="27" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D197" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E197" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F197" s="29" t="inlineStr">
         <is>
-          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+          <t>process_and_store: 가명→익명 전환 시 pseudonym_id 제거</t>
         </is>
       </c>
       <c r="G197" s="29" t="inlineStr">
         <is>
-          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+          <t>level='anonymous', pseudonym_id=None</t>
         </is>
       </c>
       <c r="H197" s="28" t="inlineStr">
@@ -11308,7 +11308,7 @@
     <row r="198">
       <c r="A198" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-PRIV-22</t>
         </is>
       </c>
       <c r="B198" s="27" t="inlineStr">
@@ -11318,27 +11318,27 @@
       </c>
       <c r="C198" s="27" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D198" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E198" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>비정상</t>
         </is>
       </c>
       <c r="F198" s="29" t="inlineStr">
         <is>
-          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+          <t>process_and_store: 없는 사용자</t>
         </is>
       </c>
       <c r="G198" s="29" t="inlineStr">
         <is>
-          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+          <t>NotFoundError, 행 미생성</t>
         </is>
       </c>
       <c r="H198" s="28" t="inlineStr">
@@ -11355,7 +11355,7 @@
     <row r="199">
       <c r="A199" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-PRIV-23</t>
         </is>
       </c>
       <c r="B199" s="27" t="inlineStr">
@@ -11365,32 +11365,32 @@
       </c>
       <c r="C199" s="27" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="D199" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E199" s="27" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="F199" s="29" t="inlineStr">
         <is>
-          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+          <t>process_and_store: 원본 이름·생년월일이 DB 어느 테이블에도 저장되지 않음</t>
         </is>
       </c>
       <c r="G199" s="29" t="inlineStr">
         <is>
-          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+          <t>전 테이블 덤프에 '홍길동'/'1990-04-12' 없음</t>
         </is>
       </c>
       <c r="H199" s="28" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I199" s="30" t="n"/>
@@ -11402,7 +11402,7 @@
     <row r="200">
       <c r="A200" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-24</t>
         </is>
       </c>
       <c r="B200" s="27" t="inlineStr">
@@ -11417,22 +11417,22 @@
       </c>
       <c r="D200" s="28" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E200" s="27" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F200" s="29" t="inlineStr">
         <is>
-          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+          <t>get_privacy_info: 저장 후 조회 / 미처리 사용자</t>
         </is>
       </c>
       <c r="G200" s="29" t="inlineStr">
         <is>
-          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+          <t>저장된 행 반환, 없으면 NotFoundError</t>
         </is>
       </c>
       <c r="H200" s="28" t="inlineStr">
@@ -11449,7 +11449,7 @@
     <row r="201">
       <c r="A201" s="27" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-SEED-01</t>
         </is>
       </c>
       <c r="B201" s="27" t="inlineStr">
@@ -11469,17 +11469,17 @@
       </c>
       <c r="E201" s="27" t="inlineStr">
         <is>
-          <t>경계</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="F201" s="29" t="inlineStr">
         <is>
-          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+          <t>seed: 사용자 3종 생성</t>
         </is>
       </c>
       <c r="G201" s="29" t="inlineStr">
         <is>
-          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+          <t>individual/company/institution 각 1명, 기업·기관은 org_code 보유</t>
         </is>
       </c>
       <c r="H201" s="28" t="inlineStr">
@@ -11493,9 +11493,244 @@
         <v/>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B202" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C202" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D202" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E202" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F202" s="29" t="inlineStr">
+        <is>
+          <t>seed: 데모 계정 비밀번호는 해시로 저장되고 로그인 가능</t>
+        </is>
+      </c>
+      <c r="G202" s="29" t="inlineStr">
+        <is>
+          <t>평문 미저장, login('demo_individual','Demo1234') 성공</t>
+        </is>
+      </c>
+      <c r="H202" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I202" s="30" t="n"/>
+      <c r="J202" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A202,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B203" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C203" s="27" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="D203" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E203" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F203" s="29" t="inlineStr">
+        <is>
+          <t>seed: 신청 4건 이상, 4개 상태 모두 포함</t>
+        </is>
+      </c>
+      <c r="G203" s="29" t="inlineStr">
+        <is>
+          <t>submitted/reviewing/approved/rejected 각 1건 이상</t>
+        </is>
+      </c>
+      <c r="H203" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I203" s="30" t="n"/>
+      <c r="J203" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A203,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B204" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C204" s="27" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="D204" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E204" s="27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="F204" s="29" t="inlineStr">
+        <is>
+          <t>seed: 검증서 3건 중 1건은 위변조 의심</t>
+        </is>
+      </c>
+      <c r="G204" s="29" t="inlineStr">
+        <is>
+          <t>certificates=3, tamper_status='suspected' 정확히 1건</t>
+        </is>
+      </c>
+      <c r="H204" s="28" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="I204" s="30" t="n"/>
+      <c r="J204" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A204,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B205" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C205" s="27" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D205" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E205" s="27" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="F205" s="29" t="inlineStr">
+        <is>
+          <t>seed: 개인정보는 가명/익명 처리값만 적재</t>
+        </is>
+      </c>
+      <c r="G205" s="29" t="inlineStr">
+        <is>
+          <t>personal_info 가 존재하고 원본 이름 형태(마스킹 없는 값) 없음</t>
+        </is>
+      </c>
+      <c r="H205" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I205" s="30" t="n"/>
+      <c r="J205" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A205,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="27" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B206" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C206" s="27" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D206" s="28" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E206" s="27" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F206" s="29" t="inlineStr">
+        <is>
+          <t>seed: 멱등 — 두 번 실행해도 건수 불변</t>
+        </is>
+      </c>
+      <c r="G206" s="29" t="inlineStr">
+        <is>
+          <t>2회 실행 후 건수 동일, 반환 dict 의 건수와 실제 건수 일치</t>
+        </is>
+      </c>
+      <c r="H206" s="28" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I206" s="30" t="n"/>
+      <c r="J206" s="31">
+        <f>IFERROR(INDEX('케이스별결과'!$B$4:$B$600,MATCH($A206,'케이스별결과'!$A$4:$A$600,0)),"미실행")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J201"/>
-  <conditionalFormatting sqref="J5:J201">
+  <autoFilter ref="A4:J206"/>
+  <conditionalFormatting sqref="J5:J206">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -11531,7 +11766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13927,7 +14162,7 @@
     <row r="87">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>UT-ATK-01</t>
+          <t>IT-ATK-21</t>
         </is>
       </c>
       <c r="B87" s="32">
@@ -13955,7 +14190,7 @@
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>UT-ATK-02</t>
+          <t>IT-ATK-22</t>
         </is>
       </c>
       <c r="B88" s="32">
@@ -13983,7 +14218,7 @@
     <row r="89">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>UT-ATK-03</t>
+          <t>IT-ATK-23</t>
         </is>
       </c>
       <c r="B89" s="32">
@@ -14011,7 +14246,7 @@
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-01</t>
+          <t>IT-ATK-24</t>
         </is>
       </c>
       <c r="B90" s="32">
@@ -14039,7 +14274,7 @@
     <row r="91">
       <c r="A91" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-02</t>
+          <t>UT-ATK-01</t>
         </is>
       </c>
       <c r="B91" s="32">
@@ -14067,7 +14302,7 @@
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-03</t>
+          <t>UT-ATK-02</t>
         </is>
       </c>
       <c r="B92" s="32">
@@ -14095,7 +14330,7 @@
     <row r="93">
       <c r="A93" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-04</t>
+          <t>UT-ATK-03</t>
         </is>
       </c>
       <c r="B93" s="32">
@@ -14123,7 +14358,7 @@
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-05</t>
+          <t>UT-ATK-04</t>
         </is>
       </c>
       <c r="B94" s="32">
@@ -14151,7 +14386,7 @@
     <row r="95">
       <c r="A95" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-06</t>
+          <t>UT-AUTH-01</t>
         </is>
       </c>
       <c r="B95" s="32">
@@ -14163,7 +14398,7 @@
         <v/>
       </c>
       <c r="D95" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" s="23" t="n">
         <v>0</v>
@@ -14179,7 +14414,7 @@
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-07</t>
+          <t>UT-AUTH-02</t>
         </is>
       </c>
       <c r="B96" s="32">
@@ -14207,7 +14442,7 @@
     <row r="97">
       <c r="A97" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-08</t>
+          <t>UT-AUTH-03</t>
         </is>
       </c>
       <c r="B97" s="32">
@@ -14235,7 +14470,7 @@
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-09</t>
+          <t>UT-AUTH-04</t>
         </is>
       </c>
       <c r="B98" s="32">
@@ -14247,7 +14482,7 @@
         <v/>
       </c>
       <c r="D98" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="23" t="n">
         <v>0</v>
@@ -14263,7 +14498,7 @@
     <row r="99">
       <c r="A99" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-10</t>
+          <t>UT-AUTH-05</t>
         </is>
       </c>
       <c r="B99" s="32">
@@ -14275,7 +14510,7 @@
         <v/>
       </c>
       <c r="D99" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E99" s="23" t="n">
         <v>0</v>
@@ -14291,7 +14526,7 @@
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-11</t>
+          <t>UT-AUTH-06</t>
         </is>
       </c>
       <c r="B100" s="32">
@@ -14303,7 +14538,7 @@
         <v/>
       </c>
       <c r="D100" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E100" s="23" t="n">
         <v>0</v>
@@ -14319,7 +14554,7 @@
     <row r="101">
       <c r="A101" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-12</t>
+          <t>UT-AUTH-07</t>
         </is>
       </c>
       <c r="B101" s="32">
@@ -14347,7 +14582,7 @@
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-13</t>
+          <t>UT-AUTH-08</t>
         </is>
       </c>
       <c r="B102" s="32">
@@ -14375,7 +14610,7 @@
     <row r="103">
       <c r="A103" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-14</t>
+          <t>UT-AUTH-09</t>
         </is>
       </c>
       <c r="B103" s="32">
@@ -14387,7 +14622,7 @@
         <v/>
       </c>
       <c r="D103" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E103" s="23" t="n">
         <v>0</v>
@@ -14403,7 +14638,7 @@
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-15</t>
+          <t>UT-AUTH-10</t>
         </is>
       </c>
       <c r="B104" s="32">
@@ -14415,7 +14650,7 @@
         <v/>
       </c>
       <c r="D104" s="23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E104" s="23" t="n">
         <v>0</v>
@@ -14431,7 +14666,7 @@
     <row r="105">
       <c r="A105" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-16</t>
+          <t>UT-AUTH-11</t>
         </is>
       </c>
       <c r="B105" s="32">
@@ -14443,7 +14678,7 @@
         <v/>
       </c>
       <c r="D105" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E105" s="23" t="n">
         <v>0</v>
@@ -14459,7 +14694,7 @@
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-17</t>
+          <t>UT-AUTH-12</t>
         </is>
       </c>
       <c r="B106" s="32">
@@ -14471,7 +14706,7 @@
         <v/>
       </c>
       <c r="D106" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E106" s="23" t="n">
         <v>0</v>
@@ -14487,7 +14722,7 @@
     <row r="107">
       <c r="A107" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-18</t>
+          <t>UT-AUTH-13</t>
         </is>
       </c>
       <c r="B107" s="32">
@@ -14499,7 +14734,7 @@
         <v/>
       </c>
       <c r="D107" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" s="23" t="n">
         <v>0</v>
@@ -14515,7 +14750,7 @@
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-19</t>
+          <t>UT-AUTH-14</t>
         </is>
       </c>
       <c r="B108" s="32">
@@ -14527,7 +14762,7 @@
         <v/>
       </c>
       <c r="D108" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E108" s="23" t="n">
         <v>0</v>
@@ -14543,7 +14778,7 @@
     <row r="109">
       <c r="A109" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-20</t>
+          <t>UT-AUTH-15</t>
         </is>
       </c>
       <c r="B109" s="32">
@@ -14555,7 +14790,7 @@
         <v/>
       </c>
       <c r="D109" s="23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E109" s="23" t="n">
         <v>0</v>
@@ -14571,7 +14806,7 @@
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-21</t>
+          <t>UT-AUTH-16</t>
         </is>
       </c>
       <c r="B110" s="32">
@@ -14583,7 +14818,7 @@
         <v/>
       </c>
       <c r="D110" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E110" s="23" t="n">
         <v>0</v>
@@ -14599,7 +14834,7 @@
     <row r="111">
       <c r="A111" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-22</t>
+          <t>UT-AUTH-17</t>
         </is>
       </c>
       <c r="B111" s="32">
@@ -14611,7 +14846,7 @@
         <v/>
       </c>
       <c r="D111" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E111" s="23" t="n">
         <v>0</v>
@@ -14627,7 +14862,7 @@
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-23</t>
+          <t>UT-AUTH-18</t>
         </is>
       </c>
       <c r="B112" s="32">
@@ -14639,7 +14874,7 @@
         <v/>
       </c>
       <c r="D112" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E112" s="23" t="n">
         <v>0</v>
@@ -14655,7 +14890,7 @@
     <row r="113">
       <c r="A113" s="22" t="inlineStr">
         <is>
-          <t>UT-AUTH-24</t>
+          <t>UT-AUTH-19</t>
         </is>
       </c>
       <c r="B113" s="32">
@@ -14683,7 +14918,7 @@
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-01</t>
+          <t>UT-AUTH-20</t>
         </is>
       </c>
       <c r="B114" s="32">
@@ -14711,7 +14946,7 @@
     <row r="115">
       <c r="A115" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-02</t>
+          <t>UT-AUTH-21</t>
         </is>
       </c>
       <c r="B115" s="32">
@@ -14723,7 +14958,7 @@
         <v/>
       </c>
       <c r="D115" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E115" s="23" t="n">
         <v>0</v>
@@ -14739,7 +14974,7 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-03</t>
+          <t>UT-AUTH-22</t>
         </is>
       </c>
       <c r="B116" s="32">
@@ -14751,7 +14986,7 @@
         <v/>
       </c>
       <c r="D116" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E116" s="23" t="n">
         <v>0</v>
@@ -14767,7 +15002,7 @@
     <row r="117">
       <c r="A117" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-04</t>
+          <t>UT-AUTH-23</t>
         </is>
       </c>
       <c r="B117" s="32">
@@ -14779,7 +15014,7 @@
         <v/>
       </c>
       <c r="D117" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E117" s="23" t="n">
         <v>0</v>
@@ -14795,7 +15030,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-05</t>
+          <t>UT-AUTH-24</t>
         </is>
       </c>
       <c r="B118" s="32">
@@ -14807,7 +15042,7 @@
         <v/>
       </c>
       <c r="D118" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="23" t="n">
         <v>0</v>
@@ -14823,7 +15058,7 @@
     <row r="119">
       <c r="A119" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-06</t>
+          <t>UT-CAVP-01</t>
         </is>
       </c>
       <c r="B119" s="32">
@@ -14835,7 +15070,7 @@
         <v/>
       </c>
       <c r="D119" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="23" t="n">
         <v>0</v>
@@ -14851,7 +15086,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-07</t>
+          <t>UT-CAVP-02</t>
         </is>
       </c>
       <c r="B120" s="32">
@@ -14863,7 +15098,7 @@
         <v/>
       </c>
       <c r="D120" s="23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E120" s="23" t="n">
         <v>0</v>
@@ -14879,7 +15114,7 @@
     <row r="121">
       <c r="A121" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-08</t>
+          <t>UT-CAVP-03</t>
         </is>
       </c>
       <c r="B121" s="32">
@@ -14891,7 +15126,7 @@
         <v/>
       </c>
       <c r="D121" s="23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E121" s="23" t="n">
         <v>0</v>
@@ -14900,14 +15135,14 @@
         <v>0</v>
       </c>
       <c r="G121" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H121" s="22" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-09</t>
+          <t>UT-CAVP-04</t>
         </is>
       </c>
       <c r="B122" s="32">
@@ -14919,7 +15154,7 @@
         <v/>
       </c>
       <c r="D122" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122" s="23" t="n">
         <v>0</v>
@@ -14935,7 +15170,7 @@
     <row r="123">
       <c r="A123" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-10</t>
+          <t>UT-CAVP-05</t>
         </is>
       </c>
       <c r="B123" s="32">
@@ -14947,7 +15182,7 @@
         <v/>
       </c>
       <c r="D123" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="23" t="n">
         <v>0</v>
@@ -14963,7 +15198,7 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-11</t>
+          <t>UT-CAVP-06</t>
         </is>
       </c>
       <c r="B124" s="32">
@@ -14991,7 +15226,7 @@
     <row r="125">
       <c r="A125" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-12</t>
+          <t>UT-CAVP-07</t>
         </is>
       </c>
       <c r="B125" s="32">
@@ -15003,7 +15238,7 @@
         <v/>
       </c>
       <c r="D125" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" s="23" t="n">
         <v>0</v>
@@ -15019,7 +15254,7 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-13</t>
+          <t>UT-CAVP-08</t>
         </is>
       </c>
       <c r="B126" s="32">
@@ -15031,7 +15266,7 @@
         <v/>
       </c>
       <c r="D126" s="23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E126" s="23" t="n">
         <v>0</v>
@@ -15040,14 +15275,14 @@
         <v>0</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H126" s="22" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-14</t>
+          <t>UT-CAVP-09</t>
         </is>
       </c>
       <c r="B127" s="32">
@@ -15059,7 +15294,7 @@
         <v/>
       </c>
       <c r="D127" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E127" s="23" t="n">
         <v>0</v>
@@ -15075,7 +15310,7 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-15</t>
+          <t>UT-CAVP-10</t>
         </is>
       </c>
       <c r="B128" s="32">
@@ -15103,7 +15338,7 @@
     <row r="129">
       <c r="A129" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-16</t>
+          <t>UT-CAVP-11</t>
         </is>
       </c>
       <c r="B129" s="32">
@@ -15115,7 +15350,7 @@
         <v/>
       </c>
       <c r="D129" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="23" t="n">
         <v>0</v>
@@ -15131,7 +15366,7 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-17</t>
+          <t>UT-CAVP-12</t>
         </is>
       </c>
       <c r="B130" s="32">
@@ -15143,7 +15378,7 @@
         <v/>
       </c>
       <c r="D130" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E130" s="23" t="n">
         <v>0</v>
@@ -15159,7 +15394,7 @@
     <row r="131">
       <c r="A131" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-18</t>
+          <t>UT-CAVP-13</t>
         </is>
       </c>
       <c r="B131" s="32">
@@ -15187,7 +15422,7 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-19</t>
+          <t>UT-CAVP-14</t>
         </is>
       </c>
       <c r="B132" s="32">
@@ -15215,7 +15450,7 @@
     <row r="133">
       <c r="A133" s="22" t="inlineStr">
         <is>
-          <t>UT-CAVP-20</t>
+          <t>UT-CAVP-15</t>
         </is>
       </c>
       <c r="B133" s="32">
@@ -15243,7 +15478,7 @@
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-01</t>
+          <t>UT-CAVP-16</t>
         </is>
       </c>
       <c r="B134" s="32">
@@ -15255,13 +15490,13 @@
         <v/>
       </c>
       <c r="D134" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" s="23" t="n">
         <v>0</v>
@@ -15271,7 +15506,7 @@
     <row r="135">
       <c r="A135" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-02</t>
+          <t>UT-CAVP-17</t>
         </is>
       </c>
       <c r="B135" s="32">
@@ -15283,13 +15518,13 @@
         <v/>
       </c>
       <c r="D135" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E135" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" s="23" t="n">
         <v>0</v>
@@ -15299,7 +15534,7 @@
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-03</t>
+          <t>UT-CAVP-18</t>
         </is>
       </c>
       <c r="B136" s="32">
@@ -15311,13 +15546,13 @@
         <v/>
       </c>
       <c r="D136" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="23" t="n">
         <v>0</v>
@@ -15327,7 +15562,7 @@
     <row r="137">
       <c r="A137" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-04</t>
+          <t>UT-CAVP-19</t>
         </is>
       </c>
       <c r="B137" s="32">
@@ -15339,13 +15574,13 @@
         <v/>
       </c>
       <c r="D137" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="23" t="n">
         <v>0</v>
@@ -15355,7 +15590,7 @@
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-05</t>
+          <t>UT-CAVP-20</t>
         </is>
       </c>
       <c r="B138" s="32">
@@ -15367,13 +15602,13 @@
         <v/>
       </c>
       <c r="D138" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="23" t="n">
         <v>0</v>
@@ -15383,7 +15618,7 @@
     <row r="139">
       <c r="A139" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-06</t>
+          <t>UT-CERT-01</t>
         </is>
       </c>
       <c r="B139" s="32">
@@ -15411,7 +15646,7 @@
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-07</t>
+          <t>UT-CERT-02</t>
         </is>
       </c>
       <c r="B140" s="32">
@@ -15429,7 +15664,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140" s="23" t="n">
         <v>0</v>
@@ -15439,7 +15674,7 @@
     <row r="141">
       <c r="A141" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-08</t>
+          <t>UT-CERT-03</t>
         </is>
       </c>
       <c r="B141" s="32">
@@ -15467,7 +15702,7 @@
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-09</t>
+          <t>UT-CERT-04</t>
         </is>
       </c>
       <c r="B142" s="32">
@@ -15485,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="F142" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G142" s="23" t="n">
         <v>0</v>
@@ -15495,7 +15730,7 @@
     <row r="143">
       <c r="A143" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-10</t>
+          <t>UT-CERT-05</t>
         </is>
       </c>
       <c r="B143" s="32">
@@ -15523,7 +15758,7 @@
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-11</t>
+          <t>UT-CERT-06</t>
         </is>
       </c>
       <c r="B144" s="32">
@@ -15551,7 +15786,7 @@
     <row r="145">
       <c r="A145" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-12</t>
+          <t>UT-CERT-07</t>
         </is>
       </c>
       <c r="B145" s="32">
@@ -15569,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G145" s="23" t="n">
         <v>0</v>
@@ -15579,7 +15814,7 @@
     <row r="146">
       <c r="A146" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-13</t>
+          <t>UT-CERT-08</t>
         </is>
       </c>
       <c r="B146" s="32">
@@ -15607,7 +15842,7 @@
     <row r="147">
       <c r="A147" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-14</t>
+          <t>UT-CERT-09</t>
         </is>
       </c>
       <c r="B147" s="32">
@@ -15625,7 +15860,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G147" s="23" t="n">
         <v>0</v>
@@ -15635,7 +15870,7 @@
     <row r="148">
       <c r="A148" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-15</t>
+          <t>UT-CERT-10</t>
         </is>
       </c>
       <c r="B148" s="32">
@@ -15663,7 +15898,7 @@
     <row r="149">
       <c r="A149" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-16</t>
+          <t>UT-CERT-11</t>
         </is>
       </c>
       <c r="B149" s="32">
@@ -15691,7 +15926,7 @@
     <row r="150">
       <c r="A150" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-17</t>
+          <t>UT-CERT-12</t>
         </is>
       </c>
       <c r="B150" s="32">
@@ -15719,7 +15954,7 @@
     <row r="151">
       <c r="A151" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-18</t>
+          <t>UT-CERT-13</t>
         </is>
       </c>
       <c r="B151" s="32">
@@ -15747,7 +15982,7 @@
     <row r="152">
       <c r="A152" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-19</t>
+          <t>UT-CERT-14</t>
         </is>
       </c>
       <c r="B152" s="32">
@@ -15775,7 +16010,7 @@
     <row r="153">
       <c r="A153" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-20</t>
+          <t>UT-CERT-15</t>
         </is>
       </c>
       <c r="B153" s="32">
@@ -15803,7 +16038,7 @@
     <row r="154">
       <c r="A154" s="22" t="inlineStr">
         <is>
-          <t>UT-CERT-21</t>
+          <t>UT-CERT-16</t>
         </is>
       </c>
       <c r="B154" s="32">
@@ -15831,7 +16066,7 @@
     <row r="155">
       <c r="A155" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-01</t>
+          <t>UT-CERT-17</t>
         </is>
       </c>
       <c r="B155" s="32">
@@ -15843,13 +16078,13 @@
         <v/>
       </c>
       <c r="D155" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E155" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G155" s="23" t="n">
         <v>0</v>
@@ -15859,7 +16094,7 @@
     <row r="156">
       <c r="A156" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-02</t>
+          <t>UT-CERT-18</t>
         </is>
       </c>
       <c r="B156" s="32">
@@ -15871,13 +16106,13 @@
         <v/>
       </c>
       <c r="D156" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E156" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G156" s="23" t="n">
         <v>0</v>
@@ -15887,7 +16122,7 @@
     <row r="157">
       <c r="A157" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-03</t>
+          <t>UT-CERT-19</t>
         </is>
       </c>
       <c r="B157" s="32">
@@ -15899,13 +16134,13 @@
         <v/>
       </c>
       <c r="D157" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E157" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G157" s="23" t="n">
         <v>0</v>
@@ -15915,7 +16150,7 @@
     <row r="158">
       <c r="A158" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-04</t>
+          <t>UT-CERT-20</t>
         </is>
       </c>
       <c r="B158" s="32">
@@ -15927,13 +16162,13 @@
         <v/>
       </c>
       <c r="D158" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="E158" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="G158" s="23" t="n">
         <v>0</v>
@@ -15943,7 +16178,7 @@
     <row r="159">
       <c r="A159" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-05</t>
+          <t>UT-CERT-21</t>
         </is>
       </c>
       <c r="B159" s="32">
@@ -15955,13 +16190,13 @@
         <v/>
       </c>
       <c r="D159" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E159" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" s="23" t="n">
         <v>0</v>
@@ -15971,7 +16206,7 @@
     <row r="160">
       <c r="A160" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-06</t>
+          <t>UT-DASH-01</t>
         </is>
       </c>
       <c r="B160" s="32">
@@ -15999,7 +16234,7 @@
     <row r="161">
       <c r="A161" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-07</t>
+          <t>UT-DASH-02</t>
         </is>
       </c>
       <c r="B161" s="32">
@@ -16027,7 +16262,7 @@
     <row r="162">
       <c r="A162" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-08</t>
+          <t>UT-DASH-03</t>
         </is>
       </c>
       <c r="B162" s="32">
@@ -16039,7 +16274,7 @@
         <v/>
       </c>
       <c r="D162" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="23" t="n">
         <v>0</v>
@@ -16055,7 +16290,7 @@
     <row r="163">
       <c r="A163" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-09</t>
+          <t>UT-DASH-04</t>
         </is>
       </c>
       <c r="B163" s="32">
@@ -16083,7 +16318,7 @@
     <row r="164">
       <c r="A164" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-10</t>
+          <t>UT-DASH-05</t>
         </is>
       </c>
       <c r="B164" s="32">
@@ -16095,7 +16330,7 @@
         <v/>
       </c>
       <c r="D164" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E164" s="23" t="n">
         <v>0</v>
@@ -16111,7 +16346,7 @@
     <row r="165">
       <c r="A165" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-11</t>
+          <t>UT-DASH-06</t>
         </is>
       </c>
       <c r="B165" s="32">
@@ -16139,7 +16374,7 @@
     <row r="166">
       <c r="A166" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-12</t>
+          <t>UT-DASH-07</t>
         </is>
       </c>
       <c r="B166" s="32">
@@ -16167,7 +16402,7 @@
     <row r="167">
       <c r="A167" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-13</t>
+          <t>UT-DASH-08</t>
         </is>
       </c>
       <c r="B167" s="32">
@@ -16179,7 +16414,7 @@
         <v/>
       </c>
       <c r="D167" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="23" t="n">
         <v>0</v>
@@ -16195,7 +16430,7 @@
     <row r="168">
       <c r="A168" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-14</t>
+          <t>UT-DASH-09</t>
         </is>
       </c>
       <c r="B168" s="32">
@@ -16223,7 +16458,7 @@
     <row r="169">
       <c r="A169" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-15</t>
+          <t>UT-DASH-10</t>
         </is>
       </c>
       <c r="B169" s="32">
@@ -16251,7 +16486,7 @@
     <row r="170">
       <c r="A170" s="22" t="inlineStr">
         <is>
-          <t>UT-DASH-16</t>
+          <t>UT-DASH-11</t>
         </is>
       </c>
       <c r="B170" s="32">
@@ -16279,7 +16514,7 @@
     <row r="171">
       <c r="A171" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-01</t>
+          <t>UT-DASH-12</t>
         </is>
       </c>
       <c r="B171" s="32">
@@ -16291,13 +16526,13 @@
         <v/>
       </c>
       <c r="D171" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" s="23" t="n">
         <v>0</v>
@@ -16307,7 +16542,7 @@
     <row r="172">
       <c r="A172" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-02</t>
+          <t>UT-DASH-13</t>
         </is>
       </c>
       <c r="B172" s="32">
@@ -16319,13 +16554,13 @@
         <v/>
       </c>
       <c r="D172" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F172" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" s="23" t="n">
         <v>0</v>
@@ -16335,7 +16570,7 @@
     <row r="173">
       <c r="A173" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-03</t>
+          <t>UT-DASH-14</t>
         </is>
       </c>
       <c r="B173" s="32">
@@ -16347,13 +16582,13 @@
         <v/>
       </c>
       <c r="D173" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F173" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G173" s="23" t="n">
         <v>0</v>
@@ -16363,7 +16598,7 @@
     <row r="174">
       <c r="A174" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-04</t>
+          <t>UT-DASH-15</t>
         </is>
       </c>
       <c r="B174" s="32">
@@ -16375,13 +16610,13 @@
         <v/>
       </c>
       <c r="D174" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F174" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G174" s="23" t="n">
         <v>0</v>
@@ -16391,7 +16626,7 @@
     <row r="175">
       <c r="A175" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-05</t>
+          <t>UT-DASH-16</t>
         </is>
       </c>
       <c r="B175" s="32">
@@ -16403,13 +16638,13 @@
         <v/>
       </c>
       <c r="D175" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E175" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F175" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" s="23" t="n">
         <v>0</v>
@@ -16419,7 +16654,7 @@
     <row r="176">
       <c r="A176" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-06</t>
+          <t>UT-PRIV-01</t>
         </is>
       </c>
       <c r="B176" s="32">
@@ -16437,7 +16672,7 @@
         <v>0</v>
       </c>
       <c r="F176" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G176" s="23" t="n">
         <v>0</v>
@@ -16447,7 +16682,7 @@
     <row r="177">
       <c r="A177" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-07</t>
+          <t>UT-PRIV-02</t>
         </is>
       </c>
       <c r="B177" s="32">
@@ -16475,7 +16710,7 @@
     <row r="178">
       <c r="A178" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-08</t>
+          <t>UT-PRIV-03</t>
         </is>
       </c>
       <c r="B178" s="32">
@@ -16493,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="F178" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G178" s="23" t="n">
         <v>0</v>
@@ -16503,7 +16738,7 @@
     <row r="179">
       <c r="A179" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-09</t>
+          <t>UT-PRIV-04</t>
         </is>
       </c>
       <c r="B179" s="32">
@@ -16521,7 +16756,7 @@
         <v>0</v>
       </c>
       <c r="F179" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G179" s="23" t="n">
         <v>0</v>
@@ -16531,7 +16766,7 @@
     <row r="180">
       <c r="A180" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-10</t>
+          <t>UT-PRIV-05</t>
         </is>
       </c>
       <c r="B180" s="32">
@@ -16549,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="F180" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G180" s="23" t="n">
         <v>0</v>
@@ -16559,7 +16794,7 @@
     <row r="181">
       <c r="A181" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-11</t>
+          <t>UT-PRIV-06</t>
         </is>
       </c>
       <c r="B181" s="32">
@@ -16577,7 +16812,7 @@
         <v>0</v>
       </c>
       <c r="F181" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G181" s="23" t="n">
         <v>0</v>
@@ -16587,7 +16822,7 @@
     <row r="182">
       <c r="A182" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-12</t>
+          <t>UT-PRIV-07</t>
         </is>
       </c>
       <c r="B182" s="32">
@@ -16615,7 +16850,7 @@
     <row r="183">
       <c r="A183" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-13</t>
+          <t>UT-PRIV-08</t>
         </is>
       </c>
       <c r="B183" s="32">
@@ -16633,7 +16868,7 @@
         <v>0</v>
       </c>
       <c r="F183" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G183" s="23" t="n">
         <v>0</v>
@@ -16643,7 +16878,7 @@
     <row r="184">
       <c r="A184" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-14</t>
+          <t>UT-PRIV-09</t>
         </is>
       </c>
       <c r="B184" s="32">
@@ -16671,7 +16906,7 @@
     <row r="185">
       <c r="A185" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-15</t>
+          <t>UT-PRIV-10</t>
         </is>
       </c>
       <c r="B185" s="32">
@@ -16689,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="F185" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G185" s="23" t="n">
         <v>0</v>
@@ -16699,7 +16934,7 @@
     <row r="186">
       <c r="A186" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-16</t>
+          <t>UT-PRIV-11</t>
         </is>
       </c>
       <c r="B186" s="32">
@@ -16717,7 +16952,7 @@
         <v>0</v>
       </c>
       <c r="F186" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G186" s="23" t="n">
         <v>0</v>
@@ -16727,7 +16962,7 @@
     <row r="187">
       <c r="A187" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-17</t>
+          <t>UT-PRIV-12</t>
         </is>
       </c>
       <c r="B187" s="32">
@@ -16755,7 +16990,7 @@
     <row r="188">
       <c r="A188" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-18</t>
+          <t>UT-PRIV-13</t>
         </is>
       </c>
       <c r="B188" s="32">
@@ -16773,7 +17008,7 @@
         <v>0</v>
       </c>
       <c r="F188" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G188" s="23" t="n">
         <v>0</v>
@@ -16783,7 +17018,7 @@
     <row r="189">
       <c r="A189" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-19</t>
+          <t>UT-PRIV-14</t>
         </is>
       </c>
       <c r="B189" s="32">
@@ -16811,7 +17046,7 @@
     <row r="190">
       <c r="A190" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-20</t>
+          <t>UT-PRIV-15</t>
         </is>
       </c>
       <c r="B190" s="32">
@@ -16839,7 +17074,7 @@
     <row r="191">
       <c r="A191" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-21</t>
+          <t>UT-PRIV-16</t>
         </is>
       </c>
       <c r="B191" s="32">
@@ -16857,7 +17092,7 @@
         <v>0</v>
       </c>
       <c r="F191" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G191" s="23" t="n">
         <v>0</v>
@@ -16867,7 +17102,7 @@
     <row r="192">
       <c r="A192" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-22</t>
+          <t>UT-PRIV-17</t>
         </is>
       </c>
       <c r="B192" s="32">
@@ -16895,7 +17130,7 @@
     <row r="193">
       <c r="A193" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-23</t>
+          <t>UT-PRIV-18</t>
         </is>
       </c>
       <c r="B193" s="32">
@@ -16913,7 +17148,7 @@
         <v>0</v>
       </c>
       <c r="F193" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G193" s="23" t="n">
         <v>0</v>
@@ -16923,7 +17158,7 @@
     <row r="194">
       <c r="A194" s="22" t="inlineStr">
         <is>
-          <t>UT-PRIV-24</t>
+          <t>UT-PRIV-19</t>
         </is>
       </c>
       <c r="B194" s="32">
@@ -16951,7 +17186,7 @@
     <row r="195">
       <c r="A195" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-01</t>
+          <t>UT-PRIV-20</t>
         </is>
       </c>
       <c r="B195" s="32">
@@ -16979,7 +17214,7 @@
     <row r="196">
       <c r="A196" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-02</t>
+          <t>UT-PRIV-21</t>
         </is>
       </c>
       <c r="B196" s="32">
@@ -17007,7 +17242,7 @@
     <row r="197">
       <c r="A197" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-03</t>
+          <t>UT-PRIV-22</t>
         </is>
       </c>
       <c r="B197" s="32">
@@ -17035,7 +17270,7 @@
     <row r="198">
       <c r="A198" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-04</t>
+          <t>UT-PRIV-23</t>
         </is>
       </c>
       <c r="B198" s="32">
@@ -17063,7 +17298,7 @@
     <row r="199">
       <c r="A199" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-05</t>
+          <t>UT-PRIV-24</t>
         </is>
       </c>
       <c r="B199" s="32">
@@ -17091,7 +17326,7 @@
     <row r="200">
       <c r="A200" s="22" t="inlineStr">
         <is>
-          <t>UT-SEED-06</t>
+          <t>UT-SEED-01</t>
         </is>
       </c>
       <c r="B200" s="32">
@@ -17115,6 +17350,146 @@
         <v>0</v>
       </c>
       <c r="H200" s="22" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-02</t>
+        </is>
+      </c>
+      <c r="B201" s="32">
+        <f>IF(E201&gt;0,"FAIL",IF(F201&gt;0,"RED",IF(D201&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C201" s="23">
+        <f>SUM(D201:G201)</f>
+        <v/>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="22" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-03</t>
+        </is>
+      </c>
+      <c r="B202" s="32">
+        <f>IF(E202&gt;0,"FAIL",IF(F202&gt;0,"RED",IF(D202&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C202" s="23">
+        <f>SUM(D202:G202)</f>
+        <v/>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="22" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-04</t>
+        </is>
+      </c>
+      <c r="B203" s="32">
+        <f>IF(E203&gt;0,"FAIL",IF(F203&gt;0,"RED",IF(D203&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C203" s="23">
+        <f>SUM(D203:G203)</f>
+        <v/>
+      </c>
+      <c r="D203" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" s="22" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-05</t>
+        </is>
+      </c>
+      <c r="B204" s="32">
+        <f>IF(E204&gt;0,"FAIL",IF(F204&gt;0,"RED",IF(D204&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C204" s="23">
+        <f>SUM(D204:G204)</f>
+        <v/>
+      </c>
+      <c r="D204" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="22" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="22" t="inlineStr">
+        <is>
+          <t>UT-SEED-06</t>
+        </is>
+      </c>
+      <c r="B205" s="32">
+        <f>IF(E205&gt;0,"FAIL",IF(F205&gt;0,"RED",IF(D205&gt;0,"PASS","SKIP")))</f>
+        <v/>
+      </c>
+      <c r="C205" s="23">
+        <f>SUM(D205:G205)</f>
+        <v/>
+      </c>
+      <c r="D205" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" s="22" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B600">
@@ -17145,7 +17520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18114,6 +18489,48 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:07</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>feature/store-layer</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>76da7fe</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>202</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>137</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>395</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="K25" s="36">
+        <f>IFERROR(E25/(E25+F25+G25),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$25</f>
+              <f>'실행이력'!$A$4:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$25</f>
+              <f>'실행이력'!$E$4:$E$26</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$25</f>
+              <f>'실행이력'!$A$4:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$25</f>
+              <f>'실행이력'!$F$4:$F$26</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$25</f>
+              <f>'실행이력'!$A$4:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$25</f>
+              <f>'실행이력'!$G$4:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -17520,7 +17520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18531,6 +18531,48 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:26</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>feature/dynamo-store</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>0f208f8</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="n">
+        <v>202</v>
+      </c>
+      <c r="E26" s="35" t="n">
+        <v>137</v>
+      </c>
+      <c r="F26" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>430</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="K26" s="36">
+        <f>IFERROR(E26/(E26+F26+G26),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$26</f>
+              <f>'실행이력'!$A$4:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$26</f>
+              <f>'실행이력'!$E$4:$E$27</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$26</f>
+              <f>'실행이력'!$A$4:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$26</f>
+              <f>'실행이력'!$F$4:$F$27</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$26</f>
+              <f>'실행이력'!$A$4:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$26</f>
+              <f>'실행이력'!$G$4:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -17520,7 +17520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18573,6 +18573,48 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:42</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>feature/lambda-deploy</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>8b6f0be</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="n">
+        <v>202</v>
+      </c>
+      <c r="E27" s="35" t="n">
+        <v>137</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>433</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K27" s="36">
+        <f>IFERROR(E27/(E27+F27+G27),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$27</f>
+              <f>'실행이력'!$A$4:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$27</f>
+              <f>'실행이력'!$E$4:$E$28</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$27</f>
+              <f>'실행이력'!$A$4:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$27</f>
+              <f>'실행이력'!$F$4:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$27</f>
+              <f>'실행이력'!$A$4:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$27</f>
+              <f>'실행이력'!$G$4:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -17520,7 +17520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18615,6 +18615,48 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:13</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>fix/deploy-doc-policy</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>23d9262</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="n">
+        <v>202</v>
+      </c>
+      <c r="E28" s="35" t="n">
+        <v>137</v>
+      </c>
+      <c r="F28" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>433</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>71</v>
+      </c>
+      <c r="K28" s="36">
+        <f>IFERROR(E28/(E28+F28+G28),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">

--- a/assets/tracker/test-tracker.xlsx
+++ b/assets/tracker/test-tracker.xlsx
@@ -721,12 +721,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$30</f>
+              <f>'실행이력'!$A$4:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$E$4:$E$30</f>
+              <f>'실행이력'!$E$4:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -763,12 +763,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$30</f>
+              <f>'실행이력'!$A$4:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$F$4:$F$30</f>
+              <f>'실행이력'!$F$4:$F$31</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +805,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'실행이력'!$A$4:$A$30</f>
+              <f>'실행이력'!$A$4:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'실행이력'!$G$4:$G$30</f>
+              <f>'실행이력'!$G$4:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -14172,10 +14172,10 @@
         <v/>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="23" t="n">
         <v>0</v>
@@ -14183,11 +14183,7 @@
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="22" t="inlineStr">
-        <is>
-          <t>AssertionError: assert '' != ''</t>
-        </is>
-      </c>
+      <c r="H30" s="22" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
@@ -20070,7 +20066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21291,6 +21287,48 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>2026-10-31 21:03</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>feature/sc06-certs</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>4ed2099</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="n">
+        <v>236</v>
+      </c>
+      <c r="E31" s="35" t="n">
+        <v>229</v>
+      </c>
+      <c r="F31" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="35" t="n">
+        <v>532</v>
+      </c>
+      <c r="J31" s="35" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K31" s="36">
+        <f>IFERROR(E31/(E31+F31+G31),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K4:K600">
     <cfRule type="dataBar" priority="1">
